--- a/Dienstplan_2026_neu.xlsx
+++ b/Dienstplan_2026_neu.xlsx
@@ -272,7 +272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -421,7 +421,58 @@
       </bottom>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
       <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="medium">
         <color rgb="00000000"/>
       </bottom>
     </border>
@@ -429,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,50 +626,57 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -677,6 +735,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -722,6 +783,8 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -17058,7 +17121,7 @@
       <c r="AD3" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="AE3" s="71" t="n">
+      <c r="AE3" s="70" t="n">
         <v>30</v>
       </c>
     </row>
@@ -17213,7 +17276,7 @@
           <t>Di</t>
         </is>
       </c>
-      <c r="AE4" s="72" t="inlineStr">
+      <c r="AE4" s="71" t="inlineStr">
         <is>
           <t>Mi</t>
         </is>
@@ -17264,7 +17327,7 @@
         <v>40</v>
       </c>
       <c r="AD5" s="37" t="n"/>
-      <c r="AE5" s="73" t="n"/>
+      <c r="AE5" s="72" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
@@ -17388,7 +17451,7 @@
         <f>IF(Dienstplan!AD159="","",Dienstplan!AD159)</f>
         <v/>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="73">
         <f>IF(Dienstplan!AE159="","",Dienstplan!AE159)</f>
         <v/>
       </c>
@@ -17515,7 +17578,7 @@
         <f>IF(Dienstplan!AD160="","",Dienstplan!AD160)</f>
         <v/>
       </c>
-      <c r="AE7" s="75">
+      <c r="AE7" s="74">
         <f>IF(Dienstplan!AE160="","",Dienstplan!AE160)</f>
         <v/>
       </c>
@@ -17642,7 +17705,7 @@
         <f>IF(Dienstplan!AD161="","",Dienstplan!AD161)</f>
         <v/>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="73">
         <f>IF(Dienstplan!AE161="","",Dienstplan!AE161)</f>
         <v/>
       </c>
@@ -17769,7 +17832,7 @@
         <f>IF(Dienstplan!AD162="","",Dienstplan!AD162)</f>
         <v/>
       </c>
-      <c r="AE9" s="75">
+      <c r="AE9" s="74">
         <f>IF(Dienstplan!AE162="","",Dienstplan!AE162)</f>
         <v/>
       </c>
@@ -17896,7 +17959,7 @@
         <f>IF(Dienstplan!AD163="","",Dienstplan!AD163)</f>
         <v/>
       </c>
-      <c r="AE10" s="74">
+      <c r="AE10" s="73">
         <f>IF(Dienstplan!AE163="","",Dienstplan!AE163)</f>
         <v/>
       </c>
@@ -18023,7 +18086,7 @@
         <f>IF(Dienstplan!AD164="","",Dienstplan!AD164)</f>
         <v/>
       </c>
-      <c r="AE11" s="75">
+      <c r="AE11" s="74">
         <f>IF(Dienstplan!AE164="","",Dienstplan!AE164)</f>
         <v/>
       </c>
@@ -18150,7 +18213,7 @@
         <f>IF(Dienstplan!AD165="","",Dienstplan!AD165)</f>
         <v/>
       </c>
-      <c r="AE12" s="74">
+      <c r="AE12" s="73">
         <f>IF(Dienstplan!AE165="","",Dienstplan!AE165)</f>
         <v/>
       </c>
@@ -18277,7 +18340,7 @@
         <f>IF(Dienstplan!AD166="","",Dienstplan!AD166)</f>
         <v/>
       </c>
-      <c r="AE13" s="75">
+      <c r="AE13" s="74">
         <f>IF(Dienstplan!AE166="","",Dienstplan!AE166)</f>
         <v/>
       </c>
@@ -18404,7 +18467,7 @@
         <f>IF(Dienstplan!AD167="","",Dienstplan!AD167)</f>
         <v/>
       </c>
-      <c r="AE14" s="74">
+      <c r="AE14" s="73">
         <f>IF(Dienstplan!AE167="","",Dienstplan!AE167)</f>
         <v/>
       </c>
@@ -18531,7 +18594,7 @@
         <f>IF(Dienstplan!AD168="","",Dienstplan!AD168)</f>
         <v/>
       </c>
-      <c r="AE15" s="75">
+      <c r="AE15" s="74">
         <f>IF(Dienstplan!AE168="","",Dienstplan!AE168)</f>
         <v/>
       </c>
@@ -18658,7 +18721,7 @@
         <f>IF(Dienstplan!AD169="","",Dienstplan!AD169)</f>
         <v/>
       </c>
-      <c r="AE16" s="74">
+      <c r="AE16" s="73">
         <f>IF(Dienstplan!AE169="","",Dienstplan!AE169)</f>
         <v/>
       </c>
@@ -18785,7 +18848,7 @@
         <f>IF(Dienstplan!AD170="","",Dienstplan!AD170)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="74">
         <f>IF(Dienstplan!AE170="","",Dienstplan!AE170)</f>
         <v/>
       </c>
@@ -18909,394 +18972,233 @@
           <t>!FI/SI</t>
         </is>
       </c>
-      <c r="AE18" s="77" t="inlineStr">
+      <c r="AE18" s="76" t="inlineStr">
         <is>
           <t>!FI/SI</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="X20" s="29" t="inlineStr">
+      <c r="X20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Y20" s="51" t="n"/>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="X21" s="58" t="inlineStr">
+      <c r="X21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Y21" s="54" t="n"/>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="X22" s="60" t="inlineStr"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="57" t="n"/>
+      <c r="X22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="X23" s="62" t="inlineStr">
+      <c r="X23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y23" s="54" t="n"/>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="X24" s="60" t="n"/>
-      <c r="Y24" s="54" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="57" t="n"/>
+      <c r="X24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="X25" s="58" t="inlineStr">
+      <c r="X25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Y25" s="54" t="n"/>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="X26" s="60" t="inlineStr"/>
-      <c r="Y26" s="54" t="n"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="57" t="n"/>
+      <c r="X26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="X27" s="65" t="inlineStr">
+      <c r="X27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y27" s="66" t="n"/>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="K23:N23"/>
@@ -19326,6 +19228,7 @@
     <mergeCell ref="K26:N26"/>
     <mergeCell ref="K21:N21"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="X24:AE24"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="X20:AE20"/>
     <mergeCell ref="H26:J26"/>
@@ -21444,387 +21347,226 @@
       <c r="AF18" s="50" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="Y20" s="29" t="inlineStr">
+      <c r="Y20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="51" t="n"/>
-      <c r="AF20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="Y21" s="58" t="inlineStr">
+      <c r="Y21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="Y22" s="60" t="inlineStr"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="57" t="n"/>
+      <c r="Y22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="Y23" s="62" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="57" t="n"/>
+      <c r="Y24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="Y25" s="58" t="inlineStr">
+      <c r="Y25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="Y26" s="60" t="inlineStr"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="57" t="n"/>
+      <c r="Y26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="Y27" s="65" t="inlineStr">
+      <c r="Y27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="66" t="n"/>
-      <c r="AF27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="D25:G25"/>
@@ -21832,6 +21574,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="Y24:AF24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="K28:N28"/>
@@ -22049,7 +21792,7 @@
       <c r="AD3" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="AE3" s="71" t="n">
+      <c r="AE3" s="70" t="n">
         <v>30</v>
       </c>
     </row>
@@ -22204,7 +21947,7 @@
           <t>So</t>
         </is>
       </c>
-      <c r="AE4" s="72" t="inlineStr">
+      <c r="AE4" s="71" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -22255,7 +21998,7 @@
       <c r="AB5" s="37" t="n"/>
       <c r="AC5" s="7" t="n"/>
       <c r="AD5" s="7" t="n"/>
-      <c r="AE5" s="78" t="n">
+      <c r="AE5" s="77" t="n">
         <v>49</v>
       </c>
     </row>
@@ -22381,7 +22124,7 @@
         <f>IF(Dienstplan!AD196="","",Dienstplan!AD196)</f>
         <v/>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="73">
         <f>IF(Dienstplan!AE196="","",Dienstplan!AE196)</f>
         <v/>
       </c>
@@ -22508,7 +22251,7 @@
         <f>IF(Dienstplan!AD197="","",Dienstplan!AD197)</f>
         <v/>
       </c>
-      <c r="AE7" s="75">
+      <c r="AE7" s="74">
         <f>IF(Dienstplan!AE197="","",Dienstplan!AE197)</f>
         <v/>
       </c>
@@ -22635,7 +22378,7 @@
         <f>IF(Dienstplan!AD198="","",Dienstplan!AD198)</f>
         <v/>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="73">
         <f>IF(Dienstplan!AE198="","",Dienstplan!AE198)</f>
         <v/>
       </c>
@@ -22762,7 +22505,7 @@
         <f>IF(Dienstplan!AD199="","",Dienstplan!AD199)</f>
         <v/>
       </c>
-      <c r="AE9" s="75">
+      <c r="AE9" s="74">
         <f>IF(Dienstplan!AE199="","",Dienstplan!AE199)</f>
         <v/>
       </c>
@@ -22889,7 +22632,7 @@
         <f>IF(Dienstplan!AD200="","",Dienstplan!AD200)</f>
         <v/>
       </c>
-      <c r="AE10" s="74">
+      <c r="AE10" s="73">
         <f>IF(Dienstplan!AE200="","",Dienstplan!AE200)</f>
         <v/>
       </c>
@@ -23016,7 +22759,7 @@
         <f>IF(Dienstplan!AD201="","",Dienstplan!AD201)</f>
         <v/>
       </c>
-      <c r="AE11" s="75">
+      <c r="AE11" s="74">
         <f>IF(Dienstplan!AE201="","",Dienstplan!AE201)</f>
         <v/>
       </c>
@@ -23143,7 +22886,7 @@
         <f>IF(Dienstplan!AD202="","",Dienstplan!AD202)</f>
         <v/>
       </c>
-      <c r="AE12" s="74">
+      <c r="AE12" s="73">
         <f>IF(Dienstplan!AE202="","",Dienstplan!AE202)</f>
         <v/>
       </c>
@@ -23270,7 +23013,7 @@
         <f>IF(Dienstplan!AD203="","",Dienstplan!AD203)</f>
         <v/>
       </c>
-      <c r="AE13" s="75">
+      <c r="AE13" s="74">
         <f>IF(Dienstplan!AE203="","",Dienstplan!AE203)</f>
         <v/>
       </c>
@@ -23397,7 +23140,7 @@
         <f>IF(Dienstplan!AD204="","",Dienstplan!AD204)</f>
         <v/>
       </c>
-      <c r="AE14" s="74">
+      <c r="AE14" s="73">
         <f>IF(Dienstplan!AE204="","",Dienstplan!AE204)</f>
         <v/>
       </c>
@@ -23524,7 +23267,7 @@
         <f>IF(Dienstplan!AD205="","",Dienstplan!AD205)</f>
         <v/>
       </c>
-      <c r="AE15" s="75">
+      <c r="AE15" s="74">
         <f>IF(Dienstplan!AE205="","",Dienstplan!AE205)</f>
         <v/>
       </c>
@@ -23651,7 +23394,7 @@
         <f>IF(Dienstplan!AD206="","",Dienstplan!AD206)</f>
         <v/>
       </c>
-      <c r="AE16" s="74">
+      <c r="AE16" s="73">
         <f>IF(Dienstplan!AE206="","",Dienstplan!AE206)</f>
         <v/>
       </c>
@@ -23778,7 +23521,7 @@
         <f>IF(Dienstplan!AD207="","",Dienstplan!AD207)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="74">
         <f>IF(Dienstplan!AE207="","",Dienstplan!AE207)</f>
         <v/>
       </c>
@@ -23898,394 +23641,233 @@
       </c>
       <c r="AC18" s="47" t="n"/>
       <c r="AD18" s="47" t="n"/>
-      <c r="AE18" s="77" t="inlineStr">
+      <c r="AE18" s="76" t="inlineStr">
         <is>
           <t>!FI/SI</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="X20" s="29" t="inlineStr">
+      <c r="X20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Y20" s="51" t="n"/>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="X21" s="58" t="inlineStr">
+      <c r="X21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Y21" s="54" t="n"/>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="X22" s="60" t="inlineStr"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="57" t="n"/>
+      <c r="X22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="X23" s="62" t="inlineStr">
+      <c r="X23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y23" s="54" t="n"/>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="X24" s="60" t="n"/>
-      <c r="Y24" s="54" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="57" t="n"/>
+      <c r="X24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="X25" s="58" t="inlineStr">
+      <c r="X25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Y25" s="54" t="n"/>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="X26" s="60" t="inlineStr"/>
-      <c r="Y26" s="54" t="n"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="57" t="n"/>
+      <c r="X26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="X27" s="65" t="inlineStr">
+      <c r="X27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y27" s="66" t="n"/>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="44">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="X21:AE21"/>
@@ -24314,6 +23896,7 @@
     <mergeCell ref="K26:N26"/>
     <mergeCell ref="K21:N21"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="X24:AE24"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="X20:AE20"/>
     <mergeCell ref="H26:J26"/>
@@ -24520,7 +24103,7 @@
       <c r="AE3" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="AF3" s="71" t="n">
+      <c r="AF3" s="70" t="n">
         <v>31</v>
       </c>
     </row>
@@ -24680,7 +24263,7 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="AF4" s="72" t="inlineStr">
+      <c r="AF4" s="71" t="inlineStr">
         <is>
           <t>Do</t>
         </is>
@@ -24732,7 +24315,7 @@
       </c>
       <c r="AD5" s="37" t="n"/>
       <c r="AE5" s="37" t="n"/>
-      <c r="AF5" s="73" t="n"/>
+      <c r="AF5" s="72" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
@@ -24860,7 +24443,7 @@
         <f>IF(Dienstplan!AE215="","",Dienstplan!AE215)</f>
         <v/>
       </c>
-      <c r="AF6" s="74">
+      <c r="AF6" s="73">
         <f>IF(Dienstplan!AF215="","",Dienstplan!AF215)</f>
         <v/>
       </c>
@@ -24991,7 +24574,7 @@
         <f>IF(Dienstplan!AE216="","",Dienstplan!AE216)</f>
         <v/>
       </c>
-      <c r="AF7" s="75">
+      <c r="AF7" s="74">
         <f>IF(Dienstplan!AF216="","",Dienstplan!AF216)</f>
         <v/>
       </c>
@@ -25122,7 +24705,7 @@
         <f>IF(Dienstplan!AE217="","",Dienstplan!AE217)</f>
         <v/>
       </c>
-      <c r="AF8" s="74">
+      <c r="AF8" s="73">
         <f>IF(Dienstplan!AF217="","",Dienstplan!AF217)</f>
         <v/>
       </c>
@@ -25253,7 +24836,7 @@
         <f>IF(Dienstplan!AE218="","",Dienstplan!AE218)</f>
         <v/>
       </c>
-      <c r="AF9" s="75">
+      <c r="AF9" s="74">
         <f>IF(Dienstplan!AF218="","",Dienstplan!AF218)</f>
         <v/>
       </c>
@@ -25384,7 +24967,7 @@
         <f>IF(Dienstplan!AE219="","",Dienstplan!AE219)</f>
         <v/>
       </c>
-      <c r="AF10" s="74">
+      <c r="AF10" s="73">
         <f>IF(Dienstplan!AF219="","",Dienstplan!AF219)</f>
         <v/>
       </c>
@@ -25515,7 +25098,7 @@
         <f>IF(Dienstplan!AE220="","",Dienstplan!AE220)</f>
         <v/>
       </c>
-      <c r="AF11" s="75">
+      <c r="AF11" s="74">
         <f>IF(Dienstplan!AF220="","",Dienstplan!AF220)</f>
         <v/>
       </c>
@@ -25646,7 +25229,7 @@
         <f>IF(Dienstplan!AE221="","",Dienstplan!AE221)</f>
         <v/>
       </c>
-      <c r="AF12" s="74">
+      <c r="AF12" s="73">
         <f>IF(Dienstplan!AF221="","",Dienstplan!AF221)</f>
         <v/>
       </c>
@@ -25777,7 +25360,7 @@
         <f>IF(Dienstplan!AE222="","",Dienstplan!AE222)</f>
         <v/>
       </c>
-      <c r="AF13" s="75">
+      <c r="AF13" s="74">
         <f>IF(Dienstplan!AF222="","",Dienstplan!AF222)</f>
         <v/>
       </c>
@@ -25908,7 +25491,7 @@
         <f>IF(Dienstplan!AE223="","",Dienstplan!AE223)</f>
         <v/>
       </c>
-      <c r="AF14" s="74">
+      <c r="AF14" s="73">
         <f>IF(Dienstplan!AF223="","",Dienstplan!AF223)</f>
         <v/>
       </c>
@@ -26039,7 +25622,7 @@
         <f>IF(Dienstplan!AE224="","",Dienstplan!AE224)</f>
         <v/>
       </c>
-      <c r="AF15" s="75">
+      <c r="AF15" s="74">
         <f>IF(Dienstplan!AF224="","",Dienstplan!AF224)</f>
         <v/>
       </c>
@@ -26170,7 +25753,7 @@
         <f>IF(Dienstplan!AE225="","",Dienstplan!AE225)</f>
         <v/>
       </c>
-      <c r="AF16" s="74">
+      <c r="AF16" s="73">
         <f>IF(Dienstplan!AF225="","",Dienstplan!AF225)</f>
         <v/>
       </c>
@@ -26301,7 +25884,7 @@
         <f>IF(Dienstplan!AE226="","",Dienstplan!AE226)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="74">
         <f>IF(Dienstplan!AF226="","",Dienstplan!AF226)</f>
         <v/>
       </c>
@@ -26426,394 +26009,233 @@
           <t>!FI/SI/NI</t>
         </is>
       </c>
-      <c r="AF18" s="77" t="inlineStr">
+      <c r="AF18" s="76" t="inlineStr">
         <is>
           <t>!FI/SI/NI</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="Y20" s="29" t="inlineStr">
+      <c r="Y20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="51" t="n"/>
-      <c r="AF20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="Y21" s="58" t="inlineStr">
+      <c r="Y21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="Y22" s="60" t="inlineStr"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="57" t="n"/>
+      <c r="Y22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="Y23" s="62" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="57" t="n"/>
+      <c r="Y24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="Y25" s="58" t="inlineStr">
+      <c r="Y25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="Y26" s="60" t="inlineStr"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="57" t="n"/>
+      <c r="Y26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="Y27" s="65" t="inlineStr">
+      <c r="Y27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="66" t="n"/>
-      <c r="AF27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="D25:G25"/>
@@ -26821,6 +26243,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="Y24:AF24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="K28:N28"/>
@@ -26929,642 +26352,642 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="79" t="inlineStr">
+      <c r="A3" s="78" t="inlineStr">
         <is>
           <t>Mitarbeiter</t>
         </is>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="79" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="C3" s="80" t="inlineStr">
+      <c r="C3" s="79" t="inlineStr">
         <is>
           <t>FII</t>
         </is>
       </c>
-      <c r="D3" s="80" t="inlineStr">
+      <c r="D3" s="79" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E3" s="80" t="inlineStr">
+      <c r="E3" s="79" t="inlineStr">
         <is>
           <t>NI</t>
         </is>
       </c>
-      <c r="F3" s="80" t="inlineStr">
+      <c r="F3" s="79" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="G3" s="80" t="inlineStr">
+      <c r="G3" s="79" t="inlineStr">
         <is>
           <t>DII</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr">
+      <c r="H3" s="79" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="I3" s="80" t="inlineStr">
+      <c r="I3" s="79" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="J3" s="80" t="inlineStr">
+      <c r="J3" s="79" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="K3" s="80" t="inlineStr">
+      <c r="K3" s="79" t="inlineStr">
         <is>
           <t>EH</t>
         </is>
       </c>
-      <c r="L3" s="80" t="inlineStr">
+      <c r="L3" s="79" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="M3" s="80" t="inlineStr">
+      <c r="M3" s="79" t="inlineStr">
         <is>
           <t>Sek</t>
         </is>
       </c>
-      <c r="N3" s="80" t="inlineStr">
+      <c r="N3" s="79" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="O3" s="80" t="inlineStr">
+      <c r="O3" s="79" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P3" s="80" t="inlineStr">
+      <c r="P3" s="79" t="inlineStr">
         <is>
           <t>Kur</t>
         </is>
       </c>
-      <c r="Q3" s="80" t="inlineStr">
+      <c r="Q3" s="79" t="inlineStr">
         <is>
           <t>FZC</t>
         </is>
       </c>
-      <c r="R3" s="80" t="inlineStr">
+      <c r="R3" s="79" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="S3" s="81" t="inlineStr">
+      <c r="S3" s="80" t="inlineStr">
         <is>
           <t>Gesamt</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
       </c>
-      <c r="B4" s="83" t="n">
+      <c r="B4" s="82" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="83" t="n">
+      <c r="C4" s="82" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="83" t="n">
+      <c r="D4" s="82" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="83" t="n">
+      <c r="E4" s="82" t="n">
         <v>44</v>
       </c>
-      <c r="F4" s="83" t="n">
+      <c r="F4" s="82" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="83" t="inlineStr"/>
-      <c r="H4" s="83" t="n">
+      <c r="G4" s="82" t="inlineStr"/>
+      <c r="H4" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="83" t="n">
+      <c r="I4" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="83" t="n">
+      <c r="J4" s="82" t="n">
         <v>33</v>
       </c>
-      <c r="K4" s="83" t="n">
+      <c r="K4" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="83" t="inlineStr"/>
-      <c r="M4" s="83" t="inlineStr"/>
-      <c r="N4" s="83" t="n">
+      <c r="L4" s="82" t="inlineStr"/>
+      <c r="M4" s="82" t="inlineStr"/>
+      <c r="N4" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="O4" s="83" t="inlineStr"/>
-      <c r="P4" s="83" t="inlineStr"/>
-      <c r="Q4" s="83" t="inlineStr"/>
-      <c r="R4" s="83" t="n">
+      <c r="O4" s="82" t="inlineStr"/>
+      <c r="P4" s="82" t="inlineStr"/>
+      <c r="Q4" s="82" t="inlineStr"/>
+      <c r="R4" s="82" t="n">
         <v>8</v>
       </c>
-      <c r="S4" s="84" t="n">
+      <c r="S4" s="83" t="n">
         <v>147</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="82" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
       </c>
-      <c r="B5" s="85" t="n">
+      <c r="B5" s="84" t="n">
         <v>11</v>
       </c>
-      <c r="C5" s="85" t="n">
+      <c r="C5" s="84" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="85" t="n">
+      <c r="D5" s="84" t="n">
         <v>29</v>
       </c>
-      <c r="E5" s="85" t="n">
+      <c r="E5" s="84" t="n">
         <v>49</v>
       </c>
-      <c r="F5" s="85" t="n">
+      <c r="F5" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="85" t="inlineStr"/>
-      <c r="H5" s="85" t="n">
+      <c r="G5" s="84" t="inlineStr"/>
+      <c r="H5" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="85" t="inlineStr"/>
-      <c r="J5" s="85" t="n">
+      <c r="I5" s="84" t="inlineStr"/>
+      <c r="J5" s="84" t="n">
         <v>42</v>
       </c>
-      <c r="K5" s="85" t="n">
+      <c r="K5" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="85" t="inlineStr"/>
-      <c r="M5" s="85" t="inlineStr"/>
-      <c r="N5" s="85" t="n">
+      <c r="L5" s="84" t="inlineStr"/>
+      <c r="M5" s="84" t="inlineStr"/>
+      <c r="N5" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="O5" s="85" t="inlineStr"/>
-      <c r="P5" s="85" t="inlineStr"/>
-      <c r="Q5" s="85" t="inlineStr"/>
-      <c r="R5" s="85" t="n">
+      <c r="O5" s="84" t="inlineStr"/>
+      <c r="P5" s="84" t="inlineStr"/>
+      <c r="Q5" s="84" t="inlineStr"/>
+      <c r="R5" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="S5" s="86" t="n">
+      <c r="S5" s="85" t="n">
         <v>157</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
       </c>
-      <c r="B6" s="83" t="inlineStr"/>
-      <c r="C6" s="83" t="inlineStr"/>
-      <c r="D6" s="83" t="inlineStr"/>
-      <c r="E6" s="83" t="inlineStr"/>
-      <c r="F6" s="83" t="inlineStr"/>
-      <c r="G6" s="83" t="inlineStr"/>
-      <c r="H6" s="83" t="inlineStr"/>
-      <c r="I6" s="83" t="inlineStr"/>
-      <c r="J6" s="83" t="inlineStr"/>
-      <c r="K6" s="83" t="inlineStr"/>
-      <c r="L6" s="83" t="inlineStr"/>
-      <c r="M6" s="83" t="inlineStr"/>
-      <c r="N6" s="83" t="inlineStr"/>
-      <c r="O6" s="83" t="inlineStr"/>
-      <c r="P6" s="83" t="inlineStr"/>
-      <c r="Q6" s="83" t="inlineStr"/>
-      <c r="R6" s="83" t="n">
+      <c r="B6" s="82" t="inlineStr"/>
+      <c r="C6" s="82" t="inlineStr"/>
+      <c r="D6" s="82" t="inlineStr"/>
+      <c r="E6" s="82" t="inlineStr"/>
+      <c r="F6" s="82" t="inlineStr"/>
+      <c r="G6" s="82" t="inlineStr"/>
+      <c r="H6" s="82" t="inlineStr"/>
+      <c r="I6" s="82" t="inlineStr"/>
+      <c r="J6" s="82" t="inlineStr"/>
+      <c r="K6" s="82" t="inlineStr"/>
+      <c r="L6" s="82" t="inlineStr"/>
+      <c r="M6" s="82" t="inlineStr"/>
+      <c r="N6" s="82" t="inlineStr"/>
+      <c r="O6" s="82" t="inlineStr"/>
+      <c r="P6" s="82" t="inlineStr"/>
+      <c r="Q6" s="82" t="inlineStr"/>
+      <c r="R6" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="S6" s="84" t="n">
+      <c r="S6" s="83" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="B7" s="85" t="n">
+      <c r="B7" s="84" t="n">
         <v>21</v>
       </c>
-      <c r="C7" s="85" t="n">
+      <c r="C7" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="85" t="n">
+      <c r="D7" s="84" t="n">
         <v>14</v>
       </c>
-      <c r="E7" s="85" t="n">
+      <c r="E7" s="84" t="n">
         <v>43</v>
       </c>
-      <c r="F7" s="85" t="n">
+      <c r="F7" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="85" t="inlineStr"/>
-      <c r="H7" s="85" t="n">
+      <c r="G7" s="84" t="inlineStr"/>
+      <c r="H7" s="84" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="85" t="n">
+      <c r="I7" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="85" t="n">
+      <c r="J7" s="84" t="n">
         <v>38</v>
       </c>
-      <c r="K7" s="85" t="n">
+      <c r="K7" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="L7" s="85" t="inlineStr"/>
-      <c r="M7" s="85" t="inlineStr"/>
-      <c r="N7" s="85" t="n">
+      <c r="L7" s="84" t="inlineStr"/>
+      <c r="M7" s="84" t="inlineStr"/>
+      <c r="N7" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="85" t="inlineStr"/>
-      <c r="P7" s="85" t="inlineStr"/>
-      <c r="Q7" s="85" t="inlineStr"/>
-      <c r="R7" s="85" t="n">
+      <c r="O7" s="84" t="inlineStr"/>
+      <c r="P7" s="84" t="inlineStr"/>
+      <c r="Q7" s="84" t="inlineStr"/>
+      <c r="R7" s="84" t="n">
         <v>9</v>
       </c>
-      <c r="S7" s="86" t="n">
+      <c r="S7" s="85" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
       </c>
-      <c r="B8" s="83" t="n">
+      <c r="B8" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="83" t="inlineStr"/>
-      <c r="D8" s="83" t="n">
+      <c r="C8" s="82" t="inlineStr"/>
+      <c r="D8" s="82" t="n">
         <v>37</v>
       </c>
-      <c r="E8" s="83" t="n">
+      <c r="E8" s="82" t="n">
         <v>47</v>
       </c>
-      <c r="F8" s="83" t="n">
+      <c r="F8" s="82" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="83" t="inlineStr"/>
-      <c r="H8" s="83" t="n">
+      <c r="G8" s="82" t="inlineStr"/>
+      <c r="H8" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="83" t="n">
+      <c r="I8" s="82" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="83" t="n">
+      <c r="J8" s="82" t="n">
         <v>30</v>
       </c>
-      <c r="K8" s="83" t="n">
+      <c r="K8" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="83" t="inlineStr"/>
-      <c r="M8" s="83" t="inlineStr"/>
-      <c r="N8" s="83" t="n">
+      <c r="L8" s="82" t="inlineStr"/>
+      <c r="M8" s="82" t="inlineStr"/>
+      <c r="N8" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="O8" s="83" t="inlineStr"/>
-      <c r="P8" s="83" t="inlineStr"/>
-      <c r="Q8" s="83" t="inlineStr"/>
-      <c r="R8" s="83" t="n">
+      <c r="O8" s="82" t="inlineStr"/>
+      <c r="P8" s="82" t="inlineStr"/>
+      <c r="Q8" s="82" t="inlineStr"/>
+      <c r="R8" s="82" t="n">
         <v>8</v>
       </c>
-      <c r="S8" s="84" t="n">
+      <c r="S8" s="83" t="n">
         <v>155</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
       </c>
-      <c r="B9" s="85" t="n">
+      <c r="B9" s="84" t="n">
         <v>25</v>
       </c>
-      <c r="C9" s="85" t="n">
+      <c r="C9" s="84" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="85" t="n">
+      <c r="D9" s="84" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="85" t="n">
+      <c r="E9" s="84" t="n">
         <v>33</v>
       </c>
-      <c r="F9" s="85" t="n">
+      <c r="F9" s="84" t="n">
         <v>11</v>
       </c>
-      <c r="G9" s="85" t="n">
+      <c r="G9" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="85" t="inlineStr"/>
-      <c r="I9" s="85" t="n">
+      <c r="H9" s="84" t="inlineStr"/>
+      <c r="I9" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="85" t="n">
+      <c r="J9" s="84" t="n">
         <v>32</v>
       </c>
-      <c r="K9" s="85" t="inlineStr"/>
-      <c r="L9" s="85" t="inlineStr"/>
-      <c r="M9" s="85" t="inlineStr"/>
-      <c r="N9" s="85" t="n">
+      <c r="K9" s="84" t="inlineStr"/>
+      <c r="L9" s="84" t="inlineStr"/>
+      <c r="M9" s="84" t="inlineStr"/>
+      <c r="N9" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="O9" s="85" t="inlineStr"/>
-      <c r="P9" s="85" t="inlineStr"/>
-      <c r="Q9" s="85" t="inlineStr"/>
-      <c r="R9" s="85" t="n">
+      <c r="O9" s="84" t="inlineStr"/>
+      <c r="P9" s="84" t="inlineStr"/>
+      <c r="Q9" s="84" t="inlineStr"/>
+      <c r="R9" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="S9" s="86" t="n">
+      <c r="S9" s="85" t="n">
         <v>147</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
       </c>
-      <c r="B10" s="83" t="n">
+      <c r="B10" s="82" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="83" t="n">
+      <c r="C10" s="82" t="n">
         <v>17</v>
       </c>
-      <c r="D10" s="83" t="n">
+      <c r="D10" s="82" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="83" t="n">
+      <c r="E10" s="82" t="n">
         <v>39</v>
       </c>
-      <c r="F10" s="83" t="inlineStr"/>
-      <c r="G10" s="83" t="inlineStr"/>
-      <c r="H10" s="83" t="inlineStr"/>
-      <c r="I10" s="83" t="n">
+      <c r="F10" s="82" t="inlineStr"/>
+      <c r="G10" s="82" t="inlineStr"/>
+      <c r="H10" s="82" t="inlineStr"/>
+      <c r="I10" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="83" t="n">
+      <c r="J10" s="82" t="n">
         <v>18</v>
       </c>
-      <c r="K10" s="83" t="inlineStr"/>
-      <c r="L10" s="83" t="inlineStr"/>
-      <c r="M10" s="83" t="inlineStr"/>
-      <c r="N10" s="83" t="n">
+      <c r="K10" s="82" t="inlineStr"/>
+      <c r="L10" s="82" t="inlineStr"/>
+      <c r="M10" s="82" t="inlineStr"/>
+      <c r="N10" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="O10" s="83" t="inlineStr"/>
-      <c r="P10" s="83" t="inlineStr"/>
-      <c r="Q10" s="83" t="inlineStr"/>
-      <c r="R10" s="83" t="n">
+      <c r="O10" s="82" t="inlineStr"/>
+      <c r="P10" s="82" t="inlineStr"/>
+      <c r="Q10" s="82" t="inlineStr"/>
+      <c r="R10" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="S10" s="84" t="n">
+      <c r="S10" s="83" t="n">
         <v>118</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="82" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
       </c>
-      <c r="B11" s="85" t="inlineStr"/>
-      <c r="C11" s="85" t="n">
+      <c r="B11" s="84" t="inlineStr"/>
+      <c r="C11" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="85" t="inlineStr"/>
-      <c r="E11" s="85" t="inlineStr"/>
-      <c r="F11" s="85" t="n">
+      <c r="D11" s="84" t="inlineStr"/>
+      <c r="E11" s="84" t="inlineStr"/>
+      <c r="F11" s="84" t="n">
         <v>13</v>
       </c>
-      <c r="G11" s="85" t="n">
+      <c r="G11" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="85" t="n">
+      <c r="H11" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="85" t="n">
+      <c r="I11" s="84" t="n">
         <v>39</v>
       </c>
-      <c r="J11" s="85" t="n">
+      <c r="J11" s="84" t="n">
         <v>33</v>
       </c>
-      <c r="K11" s="85" t="n">
+      <c r="K11" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="L11" s="85" t="inlineStr"/>
-      <c r="M11" s="85" t="inlineStr"/>
-      <c r="N11" s="85" t="n">
+      <c r="L11" s="84" t="inlineStr"/>
+      <c r="M11" s="84" t="inlineStr"/>
+      <c r="N11" s="84" t="n">
         <v>7</v>
       </c>
-      <c r="O11" s="85" t="n">
+      <c r="O11" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="P11" s="85" t="inlineStr"/>
-      <c r="Q11" s="85" t="inlineStr"/>
-      <c r="R11" s="85" t="inlineStr"/>
-      <c r="S11" s="86" t="n">
+      <c r="P11" s="84" t="inlineStr"/>
+      <c r="Q11" s="84" t="inlineStr"/>
+      <c r="R11" s="84" t="inlineStr"/>
+      <c r="S11" s="85" t="n">
         <v>106</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
       </c>
-      <c r="B12" s="83" t="n">
+      <c r="B12" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="83" t="inlineStr"/>
-      <c r="D12" s="83" t="inlineStr"/>
-      <c r="E12" s="83" t="inlineStr"/>
-      <c r="F12" s="83" t="inlineStr"/>
-      <c r="G12" s="83" t="inlineStr"/>
-      <c r="H12" s="83" t="inlineStr"/>
-      <c r="I12" s="83" t="n">
+      <c r="C12" s="82" t="inlineStr"/>
+      <c r="D12" s="82" t="inlineStr"/>
+      <c r="E12" s="82" t="inlineStr"/>
+      <c r="F12" s="82" t="inlineStr"/>
+      <c r="G12" s="82" t="inlineStr"/>
+      <c r="H12" s="82" t="inlineStr"/>
+      <c r="I12" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="83" t="n">
+      <c r="J12" s="82" t="n">
         <v>37</v>
       </c>
-      <c r="K12" s="83" t="n">
+      <c r="K12" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="83" t="n">
+      <c r="L12" s="82" t="n">
         <v>69</v>
       </c>
-      <c r="M12" s="83" t="inlineStr"/>
-      <c r="N12" s="83" t="n">
+      <c r="M12" s="82" t="inlineStr"/>
+      <c r="N12" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="O12" s="83" t="inlineStr"/>
-      <c r="P12" s="83" t="inlineStr"/>
-      <c r="Q12" s="83" t="inlineStr"/>
-      <c r="R12" s="83" t="inlineStr"/>
-      <c r="S12" s="84" t="n">
+      <c r="O12" s="82" t="inlineStr"/>
+      <c r="P12" s="82" t="inlineStr"/>
+      <c r="Q12" s="82" t="inlineStr"/>
+      <c r="R12" s="82" t="inlineStr"/>
+      <c r="S12" s="83" t="n">
         <v>113</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="82" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B13" s="85" t="inlineStr"/>
-      <c r="C13" s="85" t="inlineStr"/>
-      <c r="D13" s="85" t="inlineStr"/>
-      <c r="E13" s="85" t="inlineStr"/>
-      <c r="F13" s="85" t="n">
+      <c r="B13" s="84" t="inlineStr"/>
+      <c r="C13" s="84" t="inlineStr"/>
+      <c r="D13" s="84" t="inlineStr"/>
+      <c r="E13" s="84" t="inlineStr"/>
+      <c r="F13" s="84" t="n">
         <v>17</v>
       </c>
-      <c r="G13" s="85" t="inlineStr"/>
-      <c r="H13" s="85" t="inlineStr"/>
-      <c r="I13" s="85" t="inlineStr"/>
-      <c r="J13" s="85" t="inlineStr"/>
-      <c r="K13" s="85" t="inlineStr"/>
-      <c r="L13" s="85" t="inlineStr"/>
-      <c r="M13" s="85" t="inlineStr"/>
-      <c r="N13" s="85" t="inlineStr"/>
-      <c r="O13" s="85" t="inlineStr"/>
-      <c r="P13" s="85" t="inlineStr"/>
-      <c r="Q13" s="85" t="inlineStr"/>
-      <c r="R13" s="85" t="inlineStr"/>
-      <c r="S13" s="86" t="n">
+      <c r="G13" s="84" t="inlineStr"/>
+      <c r="H13" s="84" t="inlineStr"/>
+      <c r="I13" s="84" t="inlineStr"/>
+      <c r="J13" s="84" t="inlineStr"/>
+      <c r="K13" s="84" t="inlineStr"/>
+      <c r="L13" s="84" t="inlineStr"/>
+      <c r="M13" s="84" t="inlineStr"/>
+      <c r="N13" s="84" t="inlineStr"/>
+      <c r="O13" s="84" t="inlineStr"/>
+      <c r="P13" s="84" t="inlineStr"/>
+      <c r="Q13" s="84" t="inlineStr"/>
+      <c r="R13" s="84" t="inlineStr"/>
+      <c r="S13" s="85" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="82" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
       </c>
-      <c r="B14" s="83" t="inlineStr"/>
-      <c r="C14" s="83" t="inlineStr"/>
-      <c r="D14" s="83" t="inlineStr"/>
-      <c r="E14" s="83" t="inlineStr"/>
-      <c r="F14" s="83" t="inlineStr"/>
-      <c r="G14" s="83" t="inlineStr"/>
-      <c r="H14" s="83" t="inlineStr"/>
-      <c r="I14" s="83" t="inlineStr"/>
-      <c r="J14" s="83" t="n">
+      <c r="B14" s="82" t="inlineStr"/>
+      <c r="C14" s="82" t="inlineStr"/>
+      <c r="D14" s="82" t="inlineStr"/>
+      <c r="E14" s="82" t="inlineStr"/>
+      <c r="F14" s="82" t="inlineStr"/>
+      <c r="G14" s="82" t="inlineStr"/>
+      <c r="H14" s="82" t="inlineStr"/>
+      <c r="I14" s="82" t="inlineStr"/>
+      <c r="J14" s="82" t="n">
         <v>39</v>
       </c>
-      <c r="K14" s="83" t="inlineStr"/>
-      <c r="L14" s="83" t="inlineStr"/>
-      <c r="M14" s="83" t="inlineStr"/>
-      <c r="N14" s="83" t="inlineStr"/>
-      <c r="O14" s="83" t="inlineStr"/>
-      <c r="P14" s="83" t="inlineStr"/>
-      <c r="Q14" s="83" t="inlineStr"/>
-      <c r="R14" s="83" t="inlineStr"/>
-      <c r="S14" s="84" t="n">
+      <c r="K14" s="82" t="inlineStr"/>
+      <c r="L14" s="82" t="inlineStr"/>
+      <c r="M14" s="82" t="inlineStr"/>
+      <c r="N14" s="82" t="inlineStr"/>
+      <c r="O14" s="82" t="inlineStr"/>
+      <c r="P14" s="82" t="inlineStr"/>
+      <c r="Q14" s="82" t="inlineStr"/>
+      <c r="R14" s="82" t="inlineStr"/>
+      <c r="S14" s="83" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="82" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B15" s="85" t="inlineStr"/>
-      <c r="C15" s="85" t="inlineStr"/>
-      <c r="D15" s="85" t="inlineStr"/>
-      <c r="E15" s="85" t="inlineStr"/>
-      <c r="F15" s="85" t="inlineStr"/>
-      <c r="G15" s="85" t="inlineStr"/>
-      <c r="H15" s="85" t="inlineStr"/>
-      <c r="I15" s="85" t="inlineStr"/>
-      <c r="J15" s="85" t="n">
+      <c r="B15" s="84" t="inlineStr"/>
+      <c r="C15" s="84" t="inlineStr"/>
+      <c r="D15" s="84" t="inlineStr"/>
+      <c r="E15" s="84" t="inlineStr"/>
+      <c r="F15" s="84" t="inlineStr"/>
+      <c r="G15" s="84" t="inlineStr"/>
+      <c r="H15" s="84" t="inlineStr"/>
+      <c r="I15" s="84" t="inlineStr"/>
+      <c r="J15" s="84" t="n">
         <v>41</v>
       </c>
-      <c r="K15" s="85" t="inlineStr"/>
-      <c r="L15" s="85" t="inlineStr"/>
-      <c r="M15" s="85" t="inlineStr"/>
-      <c r="N15" s="85" t="inlineStr"/>
-      <c r="O15" s="85" t="inlineStr"/>
-      <c r="P15" s="85" t="inlineStr"/>
-      <c r="Q15" s="85" t="inlineStr"/>
-      <c r="R15" s="85" t="inlineStr"/>
-      <c r="S15" s="86" t="n">
+      <c r="K15" s="84" t="inlineStr"/>
+      <c r="L15" s="84" t="inlineStr"/>
+      <c r="M15" s="84" t="inlineStr"/>
+      <c r="N15" s="84" t="inlineStr"/>
+      <c r="O15" s="84" t="inlineStr"/>
+      <c r="P15" s="84" t="inlineStr"/>
+      <c r="Q15" s="84" t="inlineStr"/>
+      <c r="R15" s="84" t="inlineStr"/>
+      <c r="S15" s="85" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="87" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B16" s="88" t="n">
+      <c r="B16" s="87" t="n">
         <v>92</v>
       </c>
-      <c r="C16" s="88" t="n">
+      <c r="C16" s="87" t="n">
         <v>54</v>
       </c>
-      <c r="D16" s="88" t="n">
+      <c r="D16" s="87" t="n">
         <v>130</v>
       </c>
-      <c r="E16" s="88" t="n">
+      <c r="E16" s="87" t="n">
         <v>255</v>
       </c>
-      <c r="F16" s="88" t="n">
+      <c r="F16" s="87" t="n">
         <v>68</v>
       </c>
-      <c r="G16" s="88" t="n">
+      <c r="G16" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="88" t="n">
+      <c r="H16" s="87" t="n">
         <v>15</v>
       </c>
-      <c r="I16" s="88" t="n">
+      <c r="I16" s="87" t="n">
         <v>55</v>
       </c>
-      <c r="J16" s="88" t="n">
+      <c r="J16" s="87" t="n">
         <v>343</v>
       </c>
-      <c r="K16" s="88" t="n">
+      <c r="K16" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="L16" s="88" t="n">
+      <c r="L16" s="87" t="n">
         <v>69</v>
       </c>
-      <c r="M16" s="88" t="n">
+      <c r="M16" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="88" t="n">
+      <c r="N16" s="87" t="n">
         <v>33</v>
       </c>
-      <c r="O16" s="88" t="n">
+      <c r="O16" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="88" t="n">
+      <c r="P16" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="88" t="n">
+      <c r="Q16" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="R16" s="88" t="n">
+      <c r="R16" s="87" t="n">
         <v>53</v>
       </c>
-      <c r="S16" s="89" t="n">
+      <c r="S16" s="88" t="n">
         <v>1189</v>
       </c>
     </row>
@@ -27626,7 +27049,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D3" s="90" t="n">
+      <c r="D3" s="89" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -27634,7 +27057,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G3" s="90" t="n">
+      <c r="G3" s="89" t="n">
         <v>5</v>
       </c>
     </row>
@@ -27739,14 +27162,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U4" s="71" t="inlineStr">
+      <c r="U4" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -27789,7 +27212,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -27832,7 +27255,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -27865,7 +27288,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -27910,7 +27333,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -27951,7 +27374,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -27994,7 +27417,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -28027,7 +27450,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -28064,7 +27487,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr">
+      <c r="A13" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -28101,7 +27524,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -28134,7 +27557,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -28167,7 +27590,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -28277,7 +27700,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D19" s="90" t="n">
+      <c r="D19" s="89" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -28285,7 +27708,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G19" s="90" t="n">
+      <c r="G19" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -28390,14 +27813,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U20" s="71" t="inlineStr">
+      <c r="U20" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr">
+      <c r="A21" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -28444,7 +27867,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr">
+      <c r="A22" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -28489,7 +27912,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="inlineStr">
+      <c r="A23" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -28522,7 +27945,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -28571,7 +27994,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="inlineStr">
+      <c r="A25" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -28618,7 +28041,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="inlineStr">
+      <c r="A26" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -28661,7 +28084,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="inlineStr">
+      <c r="A27" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -28700,7 +28123,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr">
+      <c r="A28" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -28743,7 +28166,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="inlineStr">
+      <c r="A29" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -28784,7 +28207,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="inlineStr">
+      <c r="A30" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -28819,7 +28242,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="58" t="inlineStr">
+      <c r="A31" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -28852,7 +28275,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr">
+      <c r="A32" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -28962,7 +28385,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D35" s="90" t="n">
+      <c r="D35" s="89" t="n">
         <v>22</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -28970,7 +28393,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G35" s="90" t="n">
+      <c r="G35" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29075,14 +28498,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U36" s="71" t="inlineStr">
+      <c r="U36" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="58" t="inlineStr">
+      <c r="A37" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -29131,7 +28554,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="inlineStr">
+      <c r="A38" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -29178,7 +28601,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="58" t="inlineStr">
+      <c r="A39" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -29211,7 +28634,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="inlineStr">
+      <c r="A40" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -29258,7 +28681,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="58" t="inlineStr">
+      <c r="A41" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -29305,7 +28728,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="inlineStr">
+      <c r="A42" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -29356,7 +28779,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="58" t="inlineStr">
+      <c r="A43" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -29399,7 +28822,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="inlineStr">
+      <c r="A44" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -29442,7 +28865,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="inlineStr">
+      <c r="A45" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -29479,7 +28902,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="A46" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -29514,7 +28937,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="58" t="inlineStr">
+      <c r="A47" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -29549,7 +28972,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="58" t="inlineStr">
+      <c r="A48" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -29661,7 +29084,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D51" s="90" t="n">
+      <c r="D51" s="89" t="n">
         <v>20</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -29669,7 +29092,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G51" s="90" t="n">
+      <c r="G51" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29774,14 +29197,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U52" s="71" t="inlineStr">
+      <c r="U52" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="58" t="inlineStr">
+      <c r="A53" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -29824,7 +29247,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="58" t="inlineStr">
+      <c r="A54" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -29867,7 +29290,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="58" t="inlineStr">
+      <c r="A55" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -29902,7 +29325,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="58" t="inlineStr">
+      <c r="A56" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -29945,7 +29368,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="58" t="inlineStr">
+      <c r="A57" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -29990,7 +29413,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="58" t="inlineStr">
+      <c r="A58" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -30033,7 +29456,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="58" t="inlineStr">
+      <c r="A59" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -30076,7 +29499,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="58" t="inlineStr">
+      <c r="A60" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -30119,7 +29542,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="58" t="inlineStr">
+      <c r="A61" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -30158,7 +29581,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="58" t="inlineStr">
+      <c r="A62" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -30191,7 +29614,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="58" t="inlineStr">
+      <c r="A63" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -30224,7 +29647,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="58" t="inlineStr">
+      <c r="A64" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -30336,7 +29759,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D67" s="90" t="n">
+      <c r="D67" s="89" t="n">
         <v>18</v>
       </c>
       <c r="F67" t="inlineStr">
@@ -30344,7 +29767,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G67" s="90" t="n">
+      <c r="G67" s="89" t="n">
         <v>5</v>
       </c>
     </row>
@@ -30449,14 +29872,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U68" s="71" t="inlineStr">
+      <c r="U68" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="58" t="inlineStr">
+      <c r="A69" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -30497,7 +29920,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="58" t="inlineStr">
+      <c r="A70" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -30534,7 +29957,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="58" t="inlineStr">
+      <c r="A71" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -30567,7 +29990,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="58" t="inlineStr">
+      <c r="A72" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -30606,7 +30029,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="58" t="inlineStr">
+      <c r="A73" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -30645,7 +30068,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="58" t="inlineStr">
+      <c r="A74" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -30684,7 +30107,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="58" t="inlineStr">
+      <c r="A75" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -30717,7 +30140,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="58" t="inlineStr">
+      <c r="A76" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -30752,7 +30175,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="58" t="inlineStr">
+      <c r="A77" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -30787,7 +30210,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="58" t="inlineStr">
+      <c r="A78" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -30820,7 +30243,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="58" t="inlineStr">
+      <c r="A79" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -30855,7 +30278,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="58" t="inlineStr">
+      <c r="A80" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -30967,7 +30390,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D83" s="90" t="n">
+      <c r="D83" s="89" t="n">
         <v>21</v>
       </c>
       <c r="F83" t="inlineStr">
@@ -30975,7 +30398,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G83" s="90" t="n">
+      <c r="G83" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31080,14 +30503,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U84" s="71" t="inlineStr">
+      <c r="U84" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="58" t="inlineStr">
+      <c r="A85" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -31124,7 +30547,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="58" t="inlineStr">
+      <c r="A86" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -31165,7 +30588,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="58" t="inlineStr">
+      <c r="A87" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -31198,7 +30621,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="58" t="inlineStr">
+      <c r="A88" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -31235,7 +30658,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="58" t="inlineStr">
+      <c r="A89" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -31276,7 +30699,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="58" t="inlineStr">
+      <c r="A90" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -31315,7 +30738,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="58" t="inlineStr">
+      <c r="A91" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -31354,7 +30777,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="58" t="inlineStr">
+      <c r="A92" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -31391,7 +30814,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="58" t="inlineStr">
+      <c r="A93" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -31426,7 +30849,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="58" t="inlineStr">
+      <c r="A94" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -31459,7 +30882,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="58" t="inlineStr">
+      <c r="A95" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -31494,7 +30917,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="58" t="inlineStr">
+      <c r="A96" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -31606,7 +31029,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D99" s="90" t="n">
+      <c r="D99" s="89" t="n">
         <v>23</v>
       </c>
       <c r="F99" t="inlineStr">
@@ -31614,7 +31037,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G99" s="90" t="n">
+      <c r="G99" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31719,14 +31142,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U100" s="71" t="inlineStr">
+      <c r="U100" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="58" t="inlineStr">
+      <c r="A101" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -31767,7 +31190,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="58" t="inlineStr">
+      <c r="A102" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -31808,7 +31231,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="58" t="inlineStr">
+      <c r="A103" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -31841,7 +31264,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="58" t="inlineStr">
+      <c r="A104" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -31882,7 +31305,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="58" t="inlineStr">
+      <c r="A105" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -31921,7 +31344,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="58" t="inlineStr">
+      <c r="A106" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -31958,7 +31381,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="58" t="inlineStr">
+      <c r="A107" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -31997,7 +31420,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="58" t="inlineStr">
+      <c r="A108" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -32034,7 +31457,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="58" t="inlineStr">
+      <c r="A109" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -32069,7 +31492,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="58" t="inlineStr">
+      <c r="A110" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -32102,7 +31525,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="58" t="inlineStr">
+      <c r="A111" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -32137,7 +31560,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="58" t="inlineStr">
+      <c r="A112" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -32249,7 +31672,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D115" s="90" t="n">
+      <c r="D115" s="89" t="n">
         <v>21</v>
       </c>
       <c r="F115" t="inlineStr">
@@ -32257,7 +31680,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G115" s="90" t="n">
+      <c r="G115" s="89" t="n">
         <v>5</v>
       </c>
     </row>
@@ -32362,14 +31785,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U116" s="71" t="inlineStr">
+      <c r="U116" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="58" t="inlineStr">
+      <c r="A117" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -32408,7 +31831,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="58" t="inlineStr">
+      <c r="A118" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -32445,7 +31868,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="58" t="inlineStr">
+      <c r="A119" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -32478,7 +31901,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="58" t="inlineStr">
+      <c r="A120" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -32515,7 +31938,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="58" t="inlineStr">
+      <c r="A121" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -32550,7 +31973,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="58" t="inlineStr">
+      <c r="A122" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -32589,7 +32012,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="58" t="inlineStr">
+      <c r="A123" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -32628,7 +32051,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="58" t="inlineStr">
+      <c r="A124" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -32663,7 +32086,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="58" t="inlineStr">
+      <c r="A125" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -32700,7 +32123,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="58" t="inlineStr">
+      <c r="A126" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -32733,7 +32156,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="58" t="inlineStr">
+      <c r="A127" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -32768,7 +32191,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="58" t="inlineStr">
+      <c r="A128" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -32880,7 +32303,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D131" s="90" t="n">
+      <c r="D131" s="89" t="n">
         <v>22</v>
       </c>
       <c r="F131" t="inlineStr">
@@ -32888,7 +32311,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G131" s="90" t="n">
+      <c r="G131" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32993,14 +32416,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U132" s="71" t="inlineStr">
+      <c r="U132" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="58" t="inlineStr">
+      <c r="A133" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -33037,7 +32460,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="58" t="inlineStr">
+      <c r="A134" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -33074,7 +32497,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="58" t="inlineStr">
+      <c r="A135" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -33107,7 +32530,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="58" t="inlineStr">
+      <c r="A136" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -33146,7 +32569,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="58" t="inlineStr">
+      <c r="A137" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -33185,7 +32608,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="58" t="inlineStr">
+      <c r="A138" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -33222,7 +32645,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="58" t="inlineStr">
+      <c r="A139" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -33261,7 +32684,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="58" t="inlineStr">
+      <c r="A140" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -33294,7 +32717,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="58" t="inlineStr">
+      <c r="A141" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -33329,7 +32752,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="58" t="inlineStr">
+      <c r="A142" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -33362,7 +32785,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="58" t="inlineStr">
+      <c r="A143" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -33397,7 +32820,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="58" t="inlineStr">
+      <c r="A144" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -33509,7 +32932,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D147" s="90" t="n">
+      <c r="D147" s="89" t="n">
         <v>22</v>
       </c>
       <c r="F147" t="inlineStr">
@@ -33517,7 +32940,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G147" s="90" t="n">
+      <c r="G147" s="89" t="n">
         <v>5</v>
       </c>
     </row>
@@ -33622,14 +33045,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U148" s="71" t="inlineStr">
+      <c r="U148" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="58" t="inlineStr">
+      <c r="A149" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -33666,7 +33089,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="58" t="inlineStr">
+      <c r="A150" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -33701,7 +33124,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="58" t="inlineStr">
+      <c r="A151" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -33734,7 +33157,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="58" t="inlineStr">
+      <c r="A152" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -33773,7 +33196,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="58" t="inlineStr">
+      <c r="A153" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -33810,7 +33233,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="58" t="inlineStr">
+      <c r="A154" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -33849,7 +33272,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="58" t="inlineStr">
+      <c r="A155" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -33888,7 +33311,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="58" t="inlineStr">
+      <c r="A156" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -33921,7 +33344,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="58" t="inlineStr">
+      <c r="A157" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -33956,7 +33379,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="58" t="inlineStr">
+      <c r="A158" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -33989,7 +33412,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="58" t="inlineStr">
+      <c r="A159" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -34024,7 +33447,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="58" t="inlineStr">
+      <c r="A160" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -34136,7 +33559,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D163" s="90" t="n">
+      <c r="D163" s="89" t="n">
         <v>21</v>
       </c>
       <c r="F163" t="inlineStr">
@@ -34144,7 +33567,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G163" s="90" t="n">
+      <c r="G163" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -34249,14 +33672,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U164" s="71" t="inlineStr">
+      <c r="U164" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="58" t="inlineStr">
+      <c r="A165" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -34293,7 +33716,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="58" t="inlineStr">
+      <c r="A166" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -34330,7 +33753,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="58" t="inlineStr">
+      <c r="A167" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -34363,7 +33786,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="58" t="inlineStr">
+      <c r="A168" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -34402,7 +33825,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="58" t="inlineStr">
+      <c r="A169" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -34439,7 +33862,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="58" t="inlineStr">
+      <c r="A170" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -34472,7 +33895,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="58" t="inlineStr">
+      <c r="A171" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -34509,7 +33932,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="58" t="inlineStr">
+      <c r="A172" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -34542,7 +33965,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="58" t="inlineStr">
+      <c r="A173" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -34575,7 +33998,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="58" t="inlineStr">
+      <c r="A174" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -34608,7 +34031,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="58" t="inlineStr">
+      <c r="A175" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -34643,7 +34066,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="58" t="inlineStr">
+      <c r="A176" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -34753,7 +34176,7 @@
           <t>AT:</t>
         </is>
       </c>
-      <c r="D179" s="90" t="n">
+      <c r="D179" s="89" t="n">
         <v>22</v>
       </c>
       <c r="F179" t="inlineStr">
@@ -34761,7 +34184,7 @@
           <t>Sa:</t>
         </is>
       </c>
-      <c r="G179" s="90" t="n">
+      <c r="G179" s="89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -34866,14 +34289,14 @@
           <t>Ist</t>
         </is>
       </c>
-      <c r="U180" s="71" t="inlineStr">
+      <c r="U180" s="70" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="58" t="inlineStr">
+      <c r="A181" s="90" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
@@ -34908,7 +34331,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="58" t="inlineStr">
+      <c r="A182" s="90" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
@@ -34947,7 +34370,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="58" t="inlineStr">
+      <c r="A183" s="90" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
@@ -34980,7 +34403,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="58" t="inlineStr">
+      <c r="A184" s="90" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
@@ -35015,7 +34438,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="58" t="inlineStr">
+      <c r="A185" s="90" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
@@ -35054,7 +34477,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="58" t="inlineStr">
+      <c r="A186" s="90" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
@@ -35091,7 +34514,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="58" t="inlineStr">
+      <c r="A187" s="90" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
@@ -35124,7 +34547,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="58" t="inlineStr">
+      <c r="A188" s="90" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
@@ -35161,7 +34584,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="58" t="inlineStr">
+      <c r="A189" s="90" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
@@ -35196,7 +34619,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="58" t="inlineStr">
+      <c r="A190" s="90" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
@@ -35229,7 +34652,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="58" t="inlineStr">
+      <c r="A191" s="90" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -35264,7 +34687,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="58" t="inlineStr">
+      <c r="A192" s="90" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
@@ -35404,121 +34827,121 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="79" t="inlineStr">
+      <c r="A3" s="78" t="inlineStr">
         <is>
           <t>Mitarbeiter</t>
         </is>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="79" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C3" s="80" t="inlineStr">
+      <c r="C3" s="79" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D3" s="80" t="inlineStr">
+      <c r="D3" s="79" t="inlineStr">
         <is>
           <t>Mär</t>
         </is>
       </c>
-      <c r="E3" s="80" t="inlineStr">
+      <c r="E3" s="79" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F3" s="80" t="inlineStr">
+      <c r="F3" s="79" t="inlineStr">
         <is>
           <t>Mai</t>
         </is>
       </c>
-      <c r="G3" s="80" t="inlineStr">
+      <c r="G3" s="79" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr">
+      <c r="H3" s="79" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I3" s="80" t="inlineStr">
+      <c r="I3" s="79" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J3" s="80" t="inlineStr">
+      <c r="J3" s="79" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K3" s="80" t="inlineStr">
+      <c r="K3" s="79" t="inlineStr">
         <is>
           <t>Okt</t>
         </is>
       </c>
-      <c r="L3" s="80" t="inlineStr">
+      <c r="L3" s="79" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M3" s="80" t="inlineStr">
+      <c r="M3" s="79" t="inlineStr">
         <is>
           <t>Dez</t>
         </is>
       </c>
-      <c r="N3" s="80" t="inlineStr">
+      <c r="N3" s="79" t="inlineStr">
         <is>
           <t>Genommen</t>
         </is>
       </c>
-      <c r="O3" s="80" t="inlineStr">
+      <c r="O3" s="79" t="inlineStr">
         <is>
           <t>Anspruch</t>
         </is>
       </c>
-      <c r="P3" s="81" t="inlineStr">
+      <c r="P3" s="80" t="inlineStr">
         <is>
           <t>Rest</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>Breig</t>
         </is>
       </c>
-      <c r="B4" s="83" t="n">
+      <c r="B4" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="83" t="inlineStr"/>
-      <c r="D4" s="83" t="inlineStr"/>
-      <c r="E4" s="83" t="inlineStr"/>
-      <c r="F4" s="83" t="n">
+      <c r="C4" s="82" t="inlineStr"/>
+      <c r="D4" s="82" t="inlineStr"/>
+      <c r="E4" s="82" t="inlineStr"/>
+      <c r="F4" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="83" t="n">
+      <c r="G4" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="83" t="n">
+      <c r="H4" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="83" t="n">
+      <c r="I4" s="82" t="n">
         <v>11</v>
       </c>
-      <c r="J4" s="83" t="n">
+      <c r="J4" s="82" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="83" t="inlineStr"/>
-      <c r="L4" s="83" t="inlineStr"/>
-      <c r="M4" s="83" t="inlineStr"/>
+      <c r="K4" s="82" t="inlineStr"/>
+      <c r="L4" s="82" t="inlineStr"/>
+      <c r="M4" s="82" t="inlineStr"/>
       <c r="N4" s="100" t="n">
         <v>35</v>
       </c>
-      <c r="O4" s="83" t="n">
+      <c r="O4" s="82" t="n">
         <v>30</v>
       </c>
       <c r="P4" s="101" t="n">
@@ -35526,41 +34949,41 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="82" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>Siebert</t>
         </is>
       </c>
-      <c r="B5" s="85" t="n">
+      <c r="B5" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="85" t="inlineStr"/>
-      <c r="D5" s="85" t="n">
+      <c r="C5" s="84" t="inlineStr"/>
+      <c r="D5" s="84" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="85" t="n">
+      <c r="E5" s="84" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="85" t="inlineStr"/>
-      <c r="G5" s="85" t="n">
+      <c r="F5" s="84" t="inlineStr"/>
+      <c r="G5" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="85" t="n">
+      <c r="H5" s="84" t="n">
         <v>8</v>
       </c>
-      <c r="I5" s="85" t="inlineStr"/>
-      <c r="J5" s="85" t="inlineStr"/>
-      <c r="K5" s="85" t="n">
+      <c r="I5" s="84" t="inlineStr"/>
+      <c r="J5" s="84" t="inlineStr"/>
+      <c r="K5" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="85" t="inlineStr"/>
-      <c r="M5" s="85" t="n">
+      <c r="L5" s="84" t="inlineStr"/>
+      <c r="M5" s="84" t="n">
         <v>7</v>
       </c>
       <c r="N5" s="102" t="n">
         <v>43</v>
       </c>
-      <c r="O5" s="85" t="n">
+      <c r="O5" s="84" t="n">
         <v>30</v>
       </c>
       <c r="P5" s="103" t="n">
@@ -35568,27 +34991,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>Jochim</t>
         </is>
       </c>
-      <c r="B6" s="83" t="inlineStr"/>
-      <c r="C6" s="83" t="inlineStr"/>
-      <c r="D6" s="83" t="inlineStr"/>
-      <c r="E6" s="83" t="inlineStr"/>
-      <c r="F6" s="83" t="inlineStr"/>
-      <c r="G6" s="83" t="inlineStr"/>
-      <c r="H6" s="83" t="inlineStr"/>
-      <c r="I6" s="83" t="inlineStr"/>
-      <c r="J6" s="83" t="inlineStr"/>
-      <c r="K6" s="83" t="inlineStr"/>
-      <c r="L6" s="83" t="inlineStr"/>
-      <c r="M6" s="83" t="inlineStr"/>
+      <c r="B6" s="82" t="inlineStr"/>
+      <c r="C6" s="82" t="inlineStr"/>
+      <c r="D6" s="82" t="inlineStr"/>
+      <c r="E6" s="82" t="inlineStr"/>
+      <c r="F6" s="82" t="inlineStr"/>
+      <c r="G6" s="82" t="inlineStr"/>
+      <c r="H6" s="82" t="inlineStr"/>
+      <c r="I6" s="82" t="inlineStr"/>
+      <c r="J6" s="82" t="inlineStr"/>
+      <c r="K6" s="82" t="inlineStr"/>
+      <c r="L6" s="82" t="inlineStr"/>
+      <c r="M6" s="82" t="inlineStr"/>
       <c r="N6" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="83" t="n">
+      <c r="O6" s="82" t="n">
         <v>30</v>
       </c>
       <c r="P6" s="104" t="n">
@@ -35596,45 +35019,45 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>Wunsch</t>
         </is>
       </c>
-      <c r="B7" s="85" t="inlineStr"/>
-      <c r="C7" s="85" t="inlineStr"/>
-      <c r="D7" s="85" t="n">
+      <c r="B7" s="84" t="inlineStr"/>
+      <c r="C7" s="84" t="inlineStr"/>
+      <c r="D7" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="85" t="inlineStr"/>
-      <c r="F7" s="85" t="n">
+      <c r="E7" s="84" t="inlineStr"/>
+      <c r="F7" s="84" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="85" t="n">
+      <c r="G7" s="84" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="85" t="n">
+      <c r="H7" s="84" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="85" t="n">
+      <c r="I7" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="85" t="n">
+      <c r="J7" s="84" t="n">
         <v>8</v>
       </c>
-      <c r="K7" s="85" t="n">
+      <c r="K7" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="85" t="n">
+      <c r="L7" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="85" t="n">
+      <c r="M7" s="84" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="102" t="n">
         <v>38</v>
       </c>
-      <c r="O7" s="85" t="n">
+      <c r="O7" s="84" t="n">
         <v>30</v>
       </c>
       <c r="P7" s="103" t="n">
@@ -35642,39 +35065,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>Göpfrich</t>
         </is>
       </c>
-      <c r="B8" s="83" t="n">
+      <c r="B8" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="83" t="inlineStr"/>
-      <c r="D8" s="83" t="inlineStr"/>
-      <c r="E8" s="83" t="n">
+      <c r="C8" s="82" t="inlineStr"/>
+      <c r="D8" s="82" t="inlineStr"/>
+      <c r="E8" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="83" t="inlineStr"/>
-      <c r="G8" s="83" t="inlineStr"/>
-      <c r="H8" s="83" t="n">
+      <c r="F8" s="82" t="inlineStr"/>
+      <c r="G8" s="82" t="inlineStr"/>
+      <c r="H8" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="83" t="inlineStr"/>
-      <c r="J8" s="83" t="n">
+      <c r="I8" s="82" t="inlineStr"/>
+      <c r="J8" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="K8" s="83" t="inlineStr"/>
-      <c r="L8" s="83" t="n">
+      <c r="K8" s="82" t="inlineStr"/>
+      <c r="L8" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="M8" s="83" t="n">
+      <c r="M8" s="82" t="n">
         <v>6</v>
       </c>
       <c r="N8" s="100" t="n">
         <v>32</v>
       </c>
-      <c r="O8" s="83" t="n">
+      <c r="O8" s="82" t="n">
         <v>30</v>
       </c>
       <c r="P8" s="101" t="n">
@@ -35682,39 +35105,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Zeller</t>
         </is>
       </c>
-      <c r="B9" s="85" t="n">
+      <c r="B9" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="85" t="inlineStr"/>
-      <c r="D9" s="85" t="n">
+      <c r="C9" s="84" t="inlineStr"/>
+      <c r="D9" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="85" t="n">
+      <c r="E9" s="84" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="85" t="n">
+      <c r="F9" s="84" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="85" t="inlineStr"/>
-      <c r="H9" s="85" t="n">
+      <c r="G9" s="84" t="inlineStr"/>
+      <c r="H9" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="85" t="inlineStr"/>
-      <c r="J9" s="85" t="n">
+      <c r="I9" s="84" t="inlineStr"/>
+      <c r="J9" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="K9" s="85" t="inlineStr"/>
-      <c r="L9" s="85" t="inlineStr"/>
-      <c r="M9" s="85" t="inlineStr"/>
+      <c r="K9" s="84" t="inlineStr"/>
+      <c r="L9" s="84" t="inlineStr"/>
+      <c r="M9" s="84" t="inlineStr"/>
       <c r="N9" s="102" t="n">
         <v>33</v>
       </c>
-      <c r="O9" s="85" t="n">
+      <c r="O9" s="84" t="n">
         <v>30</v>
       </c>
       <c r="P9" s="103" t="n">
@@ -35722,33 +35145,33 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>Behrendt</t>
         </is>
       </c>
-      <c r="B10" s="83" t="inlineStr"/>
-      <c r="C10" s="83" t="inlineStr"/>
-      <c r="D10" s="83" t="n">
+      <c r="B10" s="82" t="inlineStr"/>
+      <c r="C10" s="82" t="inlineStr"/>
+      <c r="D10" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="83" t="inlineStr"/>
-      <c r="F10" s="83" t="inlineStr"/>
-      <c r="G10" s="83" t="inlineStr"/>
-      <c r="H10" s="83" t="n">
+      <c r="E10" s="82" t="inlineStr"/>
+      <c r="F10" s="82" t="inlineStr"/>
+      <c r="G10" s="82" t="inlineStr"/>
+      <c r="H10" s="82" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="83" t="n">
+      <c r="I10" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="J10" s="83" t="inlineStr"/>
-      <c r="K10" s="83" t="inlineStr"/>
-      <c r="L10" s="83" t="inlineStr"/>
-      <c r="M10" s="83" t="inlineStr"/>
+      <c r="J10" s="82" t="inlineStr"/>
+      <c r="K10" s="82" t="inlineStr"/>
+      <c r="L10" s="82" t="inlineStr"/>
+      <c r="M10" s="82" t="inlineStr"/>
       <c r="N10" s="100" t="n">
         <v>18</v>
       </c>
-      <c r="O10" s="83" t="n">
+      <c r="O10" s="82" t="n">
         <v>30</v>
       </c>
       <c r="P10" s="104" t="n">
@@ -35756,39 +35179,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="82" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>Krempl</t>
         </is>
       </c>
-      <c r="B11" s="85" t="n">
+      <c r="B11" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="85" t="inlineStr"/>
-      <c r="D11" s="85" t="inlineStr"/>
-      <c r="E11" s="85" t="n">
+      <c r="C11" s="84" t="inlineStr"/>
+      <c r="D11" s="84" t="inlineStr"/>
+      <c r="E11" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="85" t="n">
+      <c r="F11" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="85" t="n">
+      <c r="G11" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="85" t="inlineStr"/>
-      <c r="I11" s="85" t="n">
+      <c r="H11" s="84" t="inlineStr"/>
+      <c r="I11" s="84" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="85" t="inlineStr"/>
-      <c r="K11" s="85" t="inlineStr"/>
-      <c r="L11" s="85" t="inlineStr"/>
-      <c r="M11" s="85" t="n">
+      <c r="J11" s="84" t="inlineStr"/>
+      <c r="K11" s="84" t="inlineStr"/>
+      <c r="L11" s="84" t="inlineStr"/>
+      <c r="M11" s="84" t="n">
         <v>6</v>
       </c>
       <c r="N11" s="102" t="n">
         <v>35</v>
       </c>
-      <c r="O11" s="85" t="n">
+      <c r="O11" s="84" t="n">
         <v>30</v>
       </c>
       <c r="P11" s="103" t="n">
@@ -35796,45 +35219,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>Putschler</t>
         </is>
       </c>
-      <c r="B12" s="83" t="n">
+      <c r="B12" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="83" t="n">
+      <c r="C12" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="83" t="inlineStr"/>
-      <c r="E12" s="83" t="n">
+      <c r="D12" s="82" t="inlineStr"/>
+      <c r="E12" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="83" t="n">
+      <c r="F12" s="82" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="83" t="n">
+      <c r="G12" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="83" t="inlineStr"/>
-      <c r="I12" s="83" t="n">
+      <c r="H12" s="82" t="inlineStr"/>
+      <c r="I12" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="83" t="n">
+      <c r="J12" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="83" t="n">
+      <c r="K12" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="83" t="inlineStr"/>
-      <c r="M12" s="83" t="n">
+      <c r="L12" s="82" t="inlineStr"/>
+      <c r="M12" s="82" t="n">
         <v>6</v>
       </c>
       <c r="N12" s="100" t="n">
         <v>39</v>
       </c>
-      <c r="O12" s="83" t="n">
+      <c r="O12" s="82" t="n">
         <v>30</v>
       </c>
       <c r="P12" s="101" t="n">
@@ -35842,27 +35265,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="82" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B13" s="85" t="inlineStr"/>
-      <c r="C13" s="85" t="inlineStr"/>
-      <c r="D13" s="85" t="inlineStr"/>
-      <c r="E13" s="85" t="inlineStr"/>
-      <c r="F13" s="85" t="inlineStr"/>
-      <c r="G13" s="85" t="inlineStr"/>
-      <c r="H13" s="85" t="inlineStr"/>
-      <c r="I13" s="85" t="inlineStr"/>
-      <c r="J13" s="85" t="inlineStr"/>
-      <c r="K13" s="85" t="inlineStr"/>
-      <c r="L13" s="85" t="inlineStr"/>
-      <c r="M13" s="85" t="inlineStr"/>
+      <c r="B13" s="84" t="inlineStr"/>
+      <c r="C13" s="84" t="inlineStr"/>
+      <c r="D13" s="84" t="inlineStr"/>
+      <c r="E13" s="84" t="inlineStr"/>
+      <c r="F13" s="84" t="inlineStr"/>
+      <c r="G13" s="84" t="inlineStr"/>
+      <c r="H13" s="84" t="inlineStr"/>
+      <c r="I13" s="84" t="inlineStr"/>
+      <c r="J13" s="84" t="inlineStr"/>
+      <c r="K13" s="84" t="inlineStr"/>
+      <c r="L13" s="84" t="inlineStr"/>
+      <c r="M13" s="84" t="inlineStr"/>
       <c r="N13" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="85" t="n">
+      <c r="O13" s="84" t="n">
         <v>30</v>
       </c>
       <c r="P13" s="105" t="n">
@@ -35870,45 +35293,45 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="82" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
       </c>
-      <c r="B14" s="83" t="inlineStr"/>
-      <c r="C14" s="83" t="inlineStr"/>
-      <c r="D14" s="83" t="n">
+      <c r="B14" s="82" t="inlineStr"/>
+      <c r="C14" s="82" t="inlineStr"/>
+      <c r="D14" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="83" t="inlineStr"/>
-      <c r="F14" s="83" t="n">
+      <c r="E14" s="82" t="inlineStr"/>
+      <c r="F14" s="82" t="n">
         <v>6</v>
       </c>
-      <c r="G14" s="83" t="n">
+      <c r="G14" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="83" t="n">
+      <c r="H14" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="83" t="n">
+      <c r="I14" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="83" t="n">
+      <c r="J14" s="82" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="83" t="n">
+      <c r="K14" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="L14" s="83" t="n">
+      <c r="L14" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="83" t="n">
+      <c r="M14" s="82" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="100" t="n">
         <v>39</v>
       </c>
-      <c r="O14" s="83" t="n">
+      <c r="O14" s="82" t="n">
         <v>30</v>
       </c>
       <c r="P14" s="101" t="n">
@@ -35916,43 +35339,43 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="82" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B15" s="85" t="inlineStr"/>
-      <c r="C15" s="85" t="inlineStr"/>
-      <c r="D15" s="85" t="n">
+      <c r="B15" s="84" t="inlineStr"/>
+      <c r="C15" s="84" t="inlineStr"/>
+      <c r="D15" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="85" t="n">
+      <c r="E15" s="84" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="85" t="n">
+      <c r="F15" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="85" t="n">
+      <c r="G15" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="85" t="n">
+      <c r="H15" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="85" t="n">
+      <c r="I15" s="84" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="85" t="n">
+      <c r="J15" s="84" t="n">
         <v>9</v>
       </c>
-      <c r="K15" s="85" t="n">
+      <c r="K15" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="85" t="inlineStr"/>
-      <c r="M15" s="85" t="inlineStr"/>
+      <c r="L15" s="84" t="inlineStr"/>
+      <c r="M15" s="84" t="inlineStr"/>
       <c r="N15" s="102" t="n">
         <v>41</v>
       </c>
-      <c r="O15" s="85" t="n">
+      <c r="O15" s="84" t="n">
         <v>30</v>
       </c>
       <c r="P15" s="103" t="n">
@@ -35960,55 +35383,55 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="87" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B16" s="88" t="n">
+      <c r="B16" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="C16" s="88" t="n">
+      <c r="C16" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="88" t="n">
+      <c r="D16" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="E16" s="88" t="n">
+      <c r="E16" s="87" t="n">
         <v>33</v>
       </c>
-      <c r="F16" s="88" t="n">
+      <c r="F16" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="G16" s="88" t="n">
+      <c r="G16" s="87" t="n">
         <v>27</v>
       </c>
-      <c r="H16" s="88" t="n">
+      <c r="H16" s="87" t="n">
         <v>48</v>
       </c>
-      <c r="I16" s="88" t="n">
+      <c r="I16" s="87" t="n">
         <v>53</v>
       </c>
-      <c r="J16" s="88" t="n">
+      <c r="J16" s="87" t="n">
         <v>54</v>
       </c>
-      <c r="K16" s="88" t="n">
+      <c r="K16" s="87" t="n">
         <v>28</v>
       </c>
-      <c r="L16" s="88" t="n">
+      <c r="L16" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="M16" s="88" t="n">
+      <c r="M16" s="87" t="n">
         <v>27</v>
       </c>
-      <c r="N16" s="88" t="n">
+      <c r="N16" s="87" t="n">
         <v>353</v>
       </c>
-      <c r="O16" s="66" t="n"/>
-      <c r="P16" s="67" t="n"/>
+      <c r="O16" s="106" t="n"/>
+      <c r="P16" s="107" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="106" t="inlineStr">
+      <c r="A18" s="108" t="inlineStr">
         <is>
           <t>Anspruch: 30 Tage/Jahr (anpassbar in Spalte O)</t>
         </is>
@@ -38023,387 +37446,226 @@
       <c r="AF18" s="50" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="Y20" s="29" t="inlineStr">
+      <c r="Y20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="51" t="n"/>
-      <c r="AF20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="Y21" s="58" t="inlineStr">
+      <c r="Y21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="Y22" s="60" t="inlineStr"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="57" t="n"/>
+      <c r="Y22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="Y23" s="62" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="57" t="n"/>
+      <c r="Y24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="Y25" s="58" t="inlineStr">
+      <c r="Y25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="Y26" s="60" t="inlineStr"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="57" t="n"/>
+      <c r="Y26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="Y27" s="65" t="inlineStr">
+      <c r="Y27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="66" t="n"/>
-      <c r="AF27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="D25:G25"/>
@@ -38411,6 +37673,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="Y24:AF24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="K28:N28"/>
@@ -40299,387 +39562,226 @@
       <c r="AC18" s="50" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="V20" s="29" t="inlineStr">
+      <c r="V20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="W20" s="51" t="n"/>
-      <c r="X20" s="51" t="n"/>
-      <c r="Y20" s="51" t="n"/>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="V21" s="58" t="inlineStr">
+      <c r="V21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="W21" s="54" t="n"/>
-      <c r="X21" s="54" t="n"/>
-      <c r="Y21" s="54" t="n"/>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="V22" s="60" t="inlineStr"/>
-      <c r="W22" s="54" t="n"/>
-      <c r="X22" s="54" t="n"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="57" t="n"/>
+      <c r="V22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="V23" s="62" t="inlineStr">
+      <c r="V23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="W23" s="54" t="n"/>
-      <c r="X23" s="54" t="n"/>
-      <c r="Y23" s="54" t="n"/>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="V24" s="60" t="n"/>
-      <c r="W24" s="54" t="n"/>
-      <c r="X24" s="54" t="n"/>
-      <c r="Y24" s="54" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="57" t="n"/>
+      <c r="V24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="V25" s="58" t="inlineStr">
+      <c r="V25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="W25" s="54" t="n"/>
-      <c r="X25" s="54" t="n"/>
-      <c r="Y25" s="54" t="n"/>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="V26" s="60" t="inlineStr"/>
-      <c r="W26" s="54" t="n"/>
-      <c r="X26" s="54" t="n"/>
-      <c r="Y26" s="54" t="n"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="57" t="n"/>
+      <c r="V26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="V27" s="65" t="inlineStr">
+      <c r="V27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="W27" s="66" t="n"/>
-      <c r="X27" s="66" t="n"/>
-      <c r="Y27" s="66" t="n"/>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="V21:AC21"/>
@@ -40700,6 +39802,7 @@
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="K25:N25"/>
     <mergeCell ref="H27:J27"/>
+    <mergeCell ref="V24:AC24"/>
     <mergeCell ref="K24:N24"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="D22:G22"/>
@@ -40907,7 +40010,7 @@
       <c r="AE3" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="AF3" s="71" t="n">
+      <c r="AF3" s="70" t="n">
         <v>31</v>
       </c>
     </row>
@@ -41067,7 +40170,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="AF4" s="72" t="inlineStr">
+      <c r="AF4" s="71" t="inlineStr">
         <is>
           <t>Di</t>
         </is>
@@ -41121,7 +40224,7 @@
       <c r="AE5" s="38" t="n">
         <v>14</v>
       </c>
-      <c r="AF5" s="73" t="n"/>
+      <c r="AF5" s="72" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
@@ -41249,7 +40352,7 @@
         <f>IF(Dienstplan!AE45="","",Dienstplan!AE45)</f>
         <v/>
       </c>
-      <c r="AF6" s="74">
+      <c r="AF6" s="73">
         <f>IF(Dienstplan!AF45="","",Dienstplan!AF45)</f>
         <v/>
       </c>
@@ -41380,7 +40483,7 @@
         <f>IF(Dienstplan!AE46="","",Dienstplan!AE46)</f>
         <v/>
       </c>
-      <c r="AF7" s="75">
+      <c r="AF7" s="74">
         <f>IF(Dienstplan!AF46="","",Dienstplan!AF46)</f>
         <v/>
       </c>
@@ -41511,7 +40614,7 @@
         <f>IF(Dienstplan!AE47="","",Dienstplan!AE47)</f>
         <v/>
       </c>
-      <c r="AF8" s="74">
+      <c r="AF8" s="73">
         <f>IF(Dienstplan!AF47="","",Dienstplan!AF47)</f>
         <v/>
       </c>
@@ -41642,7 +40745,7 @@
         <f>IF(Dienstplan!AE48="","",Dienstplan!AE48)</f>
         <v/>
       </c>
-      <c r="AF9" s="75">
+      <c r="AF9" s="74">
         <f>IF(Dienstplan!AF48="","",Dienstplan!AF48)</f>
         <v/>
       </c>
@@ -41773,7 +40876,7 @@
         <f>IF(Dienstplan!AE49="","",Dienstplan!AE49)</f>
         <v/>
       </c>
-      <c r="AF10" s="74">
+      <c r="AF10" s="73">
         <f>IF(Dienstplan!AF49="","",Dienstplan!AF49)</f>
         <v/>
       </c>
@@ -41904,7 +41007,7 @@
         <f>IF(Dienstplan!AE50="","",Dienstplan!AE50)</f>
         <v/>
       </c>
-      <c r="AF11" s="75">
+      <c r="AF11" s="74">
         <f>IF(Dienstplan!AF50="","",Dienstplan!AF50)</f>
         <v/>
       </c>
@@ -42035,7 +41138,7 @@
         <f>IF(Dienstplan!AE51="","",Dienstplan!AE51)</f>
         <v/>
       </c>
-      <c r="AF12" s="74">
+      <c r="AF12" s="73">
         <f>IF(Dienstplan!AF51="","",Dienstplan!AF51)</f>
         <v/>
       </c>
@@ -42166,7 +41269,7 @@
         <f>IF(Dienstplan!AE52="","",Dienstplan!AE52)</f>
         <v/>
       </c>
-      <c r="AF13" s="75">
+      <c r="AF13" s="74">
         <f>IF(Dienstplan!AF52="","",Dienstplan!AF52)</f>
         <v/>
       </c>
@@ -42297,7 +41400,7 @@
         <f>IF(Dienstplan!AE53="","",Dienstplan!AE53)</f>
         <v/>
       </c>
-      <c r="AF14" s="74">
+      <c r="AF14" s="73">
         <f>IF(Dienstplan!AF53="","",Dienstplan!AF53)</f>
         <v/>
       </c>
@@ -42428,7 +41531,7 @@
         <f>IF(Dienstplan!AE54="","",Dienstplan!AE54)</f>
         <v/>
       </c>
-      <c r="AF15" s="75">
+      <c r="AF15" s="74">
         <f>IF(Dienstplan!AF54="","",Dienstplan!AF54)</f>
         <v/>
       </c>
@@ -42559,7 +41662,7 @@
         <f>IF(Dienstplan!AE55="","",Dienstplan!AE55)</f>
         <v/>
       </c>
-      <c r="AF16" s="74">
+      <c r="AF16" s="73">
         <f>IF(Dienstplan!AF55="","",Dienstplan!AF55)</f>
         <v/>
       </c>
@@ -42690,7 +41793,7 @@
         <f>IF(Dienstplan!AE56="","",Dienstplan!AE56)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="74">
         <f>IF(Dienstplan!AF56="","",Dienstplan!AF56)</f>
         <v/>
       </c>
@@ -42743,390 +41846,229 @@
       <c r="AC18" s="47" t="n"/>
       <c r="AD18" s="47" t="n"/>
       <c r="AE18" s="49" t="n"/>
-      <c r="AF18" s="76" t="n"/>
+      <c r="AF18" s="75" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="Y20" s="29" t="inlineStr">
+      <c r="Y20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="51" t="n"/>
-      <c r="AF20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="Y21" s="58" t="inlineStr">
+      <c r="Y21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="Y22" s="60" t="inlineStr"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="57" t="n"/>
+      <c r="Y22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="Y23" s="62" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="57" t="n"/>
+      <c r="Y24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="Y25" s="58" t="inlineStr">
+      <c r="Y25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="Y26" s="60" t="inlineStr"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="57" t="n"/>
+      <c r="Y26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="Y27" s="65" t="inlineStr">
+      <c r="Y27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="66" t="n"/>
-      <c r="AF27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="44">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="D25:G25"/>
@@ -43134,6 +42076,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="Y24:AF24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="K28:N28"/>
@@ -43356,7 +42299,7 @@
       <c r="AD3" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="AE3" s="71" t="n">
+      <c r="AE3" s="70" t="n">
         <v>30</v>
       </c>
     </row>
@@ -43511,7 +42454,7 @@
           <t>Mi</t>
         </is>
       </c>
-      <c r="AE4" s="72" t="inlineStr">
+      <c r="AE4" s="71" t="inlineStr">
         <is>
           <t>Do</t>
         </is>
@@ -43562,7 +42505,7 @@
       </c>
       <c r="AC5" s="37" t="n"/>
       <c r="AD5" s="37" t="n"/>
-      <c r="AE5" s="73" t="n"/>
+      <c r="AE5" s="72" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
@@ -43686,7 +42629,7 @@
         <f>IF(Dienstplan!AD64="","",Dienstplan!AD64)</f>
         <v/>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="73">
         <f>IF(Dienstplan!AE64="","",Dienstplan!AE64)</f>
         <v/>
       </c>
@@ -43813,7 +42756,7 @@
         <f>IF(Dienstplan!AD65="","",Dienstplan!AD65)</f>
         <v/>
       </c>
-      <c r="AE7" s="75">
+      <c r="AE7" s="74">
         <f>IF(Dienstplan!AE65="","",Dienstplan!AE65)</f>
         <v/>
       </c>
@@ -43940,7 +42883,7 @@
         <f>IF(Dienstplan!AD66="","",Dienstplan!AD66)</f>
         <v/>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="73">
         <f>IF(Dienstplan!AE66="","",Dienstplan!AE66)</f>
         <v/>
       </c>
@@ -44067,7 +43010,7 @@
         <f>IF(Dienstplan!AD67="","",Dienstplan!AD67)</f>
         <v/>
       </c>
-      <c r="AE9" s="75">
+      <c r="AE9" s="74">
         <f>IF(Dienstplan!AE67="","",Dienstplan!AE67)</f>
         <v/>
       </c>
@@ -44194,7 +43137,7 @@
         <f>IF(Dienstplan!AD68="","",Dienstplan!AD68)</f>
         <v/>
       </c>
-      <c r="AE10" s="74">
+      <c r="AE10" s="73">
         <f>IF(Dienstplan!AE68="","",Dienstplan!AE68)</f>
         <v/>
       </c>
@@ -44321,7 +43264,7 @@
         <f>IF(Dienstplan!AD69="","",Dienstplan!AD69)</f>
         <v/>
       </c>
-      <c r="AE11" s="75">
+      <c r="AE11" s="74">
         <f>IF(Dienstplan!AE69="","",Dienstplan!AE69)</f>
         <v/>
       </c>
@@ -44448,7 +43391,7 @@
         <f>IF(Dienstplan!AD70="","",Dienstplan!AD70)</f>
         <v/>
       </c>
-      <c r="AE12" s="74">
+      <c r="AE12" s="73">
         <f>IF(Dienstplan!AE70="","",Dienstplan!AE70)</f>
         <v/>
       </c>
@@ -44575,7 +43518,7 @@
         <f>IF(Dienstplan!AD71="","",Dienstplan!AD71)</f>
         <v/>
       </c>
-      <c r="AE13" s="75">
+      <c r="AE13" s="74">
         <f>IF(Dienstplan!AE71="","",Dienstplan!AE71)</f>
         <v/>
       </c>
@@ -44702,7 +43645,7 @@
         <f>IF(Dienstplan!AD72="","",Dienstplan!AD72)</f>
         <v/>
       </c>
-      <c r="AE14" s="74">
+      <c r="AE14" s="73">
         <f>IF(Dienstplan!AE72="","",Dienstplan!AE72)</f>
         <v/>
       </c>
@@ -44829,7 +43772,7 @@
         <f>IF(Dienstplan!AD73="","",Dienstplan!AD73)</f>
         <v/>
       </c>
-      <c r="AE15" s="75">
+      <c r="AE15" s="74">
         <f>IF(Dienstplan!AE73="","",Dienstplan!AE73)</f>
         <v/>
       </c>
@@ -44956,7 +43899,7 @@
         <f>IF(Dienstplan!AD74="","",Dienstplan!AD74)</f>
         <v/>
       </c>
-      <c r="AE16" s="74">
+      <c r="AE16" s="73">
         <f>IF(Dienstplan!AE74="","",Dienstplan!AE74)</f>
         <v/>
       </c>
@@ -45083,7 +44026,7 @@
         <f>IF(Dienstplan!AD75="","",Dienstplan!AD75)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="74">
         <f>IF(Dienstplan!AE75="","",Dienstplan!AE75)</f>
         <v/>
       </c>
@@ -45135,390 +44078,229 @@
       <c r="AB18" s="49" t="n"/>
       <c r="AC18" s="49" t="n"/>
       <c r="AD18" s="49" t="n"/>
-      <c r="AE18" s="76" t="n"/>
+      <c r="AE18" s="75" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="X20" s="29" t="inlineStr">
+      <c r="X20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Y20" s="51" t="n"/>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="X21" s="58" t="inlineStr">
+      <c r="X21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Y21" s="54" t="n"/>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="X22" s="60" t="inlineStr"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="57" t="n"/>
+      <c r="X22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="X23" s="62" t="inlineStr">
+      <c r="X23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y23" s="54" t="n"/>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="X24" s="60" t="n"/>
-      <c r="Y24" s="54" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="57" t="n"/>
+      <c r="X24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="X25" s="58" t="inlineStr">
+      <c r="X25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Y25" s="54" t="n"/>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="X26" s="60" t="inlineStr"/>
-      <c r="Y26" s="54" t="n"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="57" t="n"/>
+      <c r="X26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="X27" s="65" t="inlineStr">
+      <c r="X27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y27" s="66" t="n"/>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="X21:AE21"/>
@@ -45547,6 +44329,7 @@
     <mergeCell ref="K26:N26"/>
     <mergeCell ref="K21:N21"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="X24:AE24"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="X20:AE20"/>
     <mergeCell ref="H26:J26"/>
@@ -47651,387 +46434,226 @@
       <c r="AF18" s="50" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="Y20" s="29" t="inlineStr">
+      <c r="Y20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="51" t="n"/>
-      <c r="AF20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="Y21" s="58" t="inlineStr">
+      <c r="Y21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="Y22" s="60" t="inlineStr"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="57" t="n"/>
+      <c r="Y22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="Y23" s="62" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="57" t="n"/>
+      <c r="Y24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="Y25" s="58" t="inlineStr">
+      <c r="Y25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="Y26" s="60" t="inlineStr"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="57" t="n"/>
+      <c r="Y26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="Y27" s="65" t="inlineStr">
+      <c r="Y27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="66" t="n"/>
-      <c r="AF27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="D25:G25"/>
@@ -48039,6 +46661,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="Y24:AF24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="K28:N28"/>
@@ -48263,7 +46886,7 @@
       <c r="AD3" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="AE3" s="71" t="n">
+      <c r="AE3" s="70" t="n">
         <v>30</v>
       </c>
     </row>
@@ -48418,7 +47041,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="AE4" s="72" t="inlineStr">
+      <c r="AE4" s="71" t="inlineStr">
         <is>
           <t>Di</t>
         </is>
@@ -48469,7 +47092,7 @@
       <c r="AD5" s="38" t="n">
         <v>27</v>
       </c>
-      <c r="AE5" s="73" t="n"/>
+      <c r="AE5" s="72" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
@@ -48593,7 +47216,7 @@
         <f>IF(Dienstplan!AD102="","",Dienstplan!AD102)</f>
         <v/>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="73">
         <f>IF(Dienstplan!AE102="","",Dienstplan!AE102)</f>
         <v/>
       </c>
@@ -48720,7 +47343,7 @@
         <f>IF(Dienstplan!AD103="","",Dienstplan!AD103)</f>
         <v/>
       </c>
-      <c r="AE7" s="75">
+      <c r="AE7" s="74">
         <f>IF(Dienstplan!AE103="","",Dienstplan!AE103)</f>
         <v/>
       </c>
@@ -48847,7 +47470,7 @@
         <f>IF(Dienstplan!AD104="","",Dienstplan!AD104)</f>
         <v/>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="73">
         <f>IF(Dienstplan!AE104="","",Dienstplan!AE104)</f>
         <v/>
       </c>
@@ -48974,7 +47597,7 @@
         <f>IF(Dienstplan!AD105="","",Dienstplan!AD105)</f>
         <v/>
       </c>
-      <c r="AE9" s="75">
+      <c r="AE9" s="74">
         <f>IF(Dienstplan!AE105="","",Dienstplan!AE105)</f>
         <v/>
       </c>
@@ -49101,7 +47724,7 @@
         <f>IF(Dienstplan!AD106="","",Dienstplan!AD106)</f>
         <v/>
       </c>
-      <c r="AE10" s="74">
+      <c r="AE10" s="73">
         <f>IF(Dienstplan!AE106="","",Dienstplan!AE106)</f>
         <v/>
       </c>
@@ -49228,7 +47851,7 @@
         <f>IF(Dienstplan!AD107="","",Dienstplan!AD107)</f>
         <v/>
       </c>
-      <c r="AE11" s="75">
+      <c r="AE11" s="74">
         <f>IF(Dienstplan!AE107="","",Dienstplan!AE107)</f>
         <v/>
       </c>
@@ -49355,7 +47978,7 @@
         <f>IF(Dienstplan!AD108="","",Dienstplan!AD108)</f>
         <v/>
       </c>
-      <c r="AE12" s="74">
+      <c r="AE12" s="73">
         <f>IF(Dienstplan!AE108="","",Dienstplan!AE108)</f>
         <v/>
       </c>
@@ -49482,7 +48105,7 @@
         <f>IF(Dienstplan!AD109="","",Dienstplan!AD109)</f>
         <v/>
       </c>
-      <c r="AE13" s="75">
+      <c r="AE13" s="74">
         <f>IF(Dienstplan!AE109="","",Dienstplan!AE109)</f>
         <v/>
       </c>
@@ -49609,7 +48232,7 @@
         <f>IF(Dienstplan!AD110="","",Dienstplan!AD110)</f>
         <v/>
       </c>
-      <c r="AE14" s="74">
+      <c r="AE14" s="73">
         <f>IF(Dienstplan!AE110="","",Dienstplan!AE110)</f>
         <v/>
       </c>
@@ -49736,7 +48359,7 @@
         <f>IF(Dienstplan!AD111="","",Dienstplan!AD111)</f>
         <v/>
       </c>
-      <c r="AE15" s="75">
+      <c r="AE15" s="74">
         <f>IF(Dienstplan!AE111="","",Dienstplan!AE111)</f>
         <v/>
       </c>
@@ -49863,7 +48486,7 @@
         <f>IF(Dienstplan!AD112="","",Dienstplan!AD112)</f>
         <v/>
       </c>
-      <c r="AE16" s="74">
+      <c r="AE16" s="73">
         <f>IF(Dienstplan!AE112="","",Dienstplan!AE112)</f>
         <v/>
       </c>
@@ -49990,7 +48613,7 @@
         <f>IF(Dienstplan!AD113="","",Dienstplan!AD113)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="74">
         <f>IF(Dienstplan!AE113="","",Dienstplan!AE113)</f>
         <v/>
       </c>
@@ -50110,394 +48733,233 @@
           <t>!FI</t>
         </is>
       </c>
-      <c r="AE18" s="77" t="inlineStr">
+      <c r="AE18" s="76" t="inlineStr">
         <is>
           <t>!FI</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="X20" s="29" t="inlineStr">
+      <c r="X20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Y20" s="51" t="n"/>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="X21" s="58" t="inlineStr">
+      <c r="X21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Y21" s="54" t="n"/>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="X22" s="60" t="inlineStr"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="57" t="n"/>
+      <c r="X22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="X23" s="62" t="inlineStr">
+      <c r="X23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y23" s="54" t="n"/>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="X24" s="60" t="n"/>
-      <c r="Y24" s="54" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="57" t="n"/>
+      <c r="X24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="X25" s="58" t="inlineStr">
+      <c r="X25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Y25" s="54" t="n"/>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="X26" s="60" t="inlineStr"/>
-      <c r="Y26" s="54" t="n"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="57" t="n"/>
+      <c r="X26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="X27" s="65" t="inlineStr">
+      <c r="X27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Y27" s="66" t="n"/>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="A25:C25"/>
@@ -50527,6 +48989,7 @@
     <mergeCell ref="K26:N26"/>
     <mergeCell ref="K21:N21"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="X24:AE24"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="X20:AE20"/>
     <mergeCell ref="H26:J26"/>
@@ -50733,7 +49196,7 @@
       <c r="AE3" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="AF3" s="71" t="n">
+      <c r="AF3" s="70" t="n">
         <v>31</v>
       </c>
     </row>
@@ -50893,7 +49356,7 @@
           <t>Do</t>
         </is>
       </c>
-      <c r="AF4" s="72" t="inlineStr">
+      <c r="AF4" s="71" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
@@ -50945,7 +49408,7 @@
       <c r="AC5" s="37" t="n"/>
       <c r="AD5" s="37" t="n"/>
       <c r="AE5" s="37" t="n"/>
-      <c r="AF5" s="73" t="n"/>
+      <c r="AF5" s="72" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="40" t="inlineStr">
@@ -51073,7 +49536,7 @@
         <f>IF(Dienstplan!AE121="","",Dienstplan!AE121)</f>
         <v/>
       </c>
-      <c r="AF6" s="74">
+      <c r="AF6" s="73">
         <f>IF(Dienstplan!AF121="","",Dienstplan!AF121)</f>
         <v/>
       </c>
@@ -51204,7 +49667,7 @@
         <f>IF(Dienstplan!AE122="","",Dienstplan!AE122)</f>
         <v/>
       </c>
-      <c r="AF7" s="75">
+      <c r="AF7" s="74">
         <f>IF(Dienstplan!AF122="","",Dienstplan!AF122)</f>
         <v/>
       </c>
@@ -51335,7 +49798,7 @@
         <f>IF(Dienstplan!AE123="","",Dienstplan!AE123)</f>
         <v/>
       </c>
-      <c r="AF8" s="74">
+      <c r="AF8" s="73">
         <f>IF(Dienstplan!AF123="","",Dienstplan!AF123)</f>
         <v/>
       </c>
@@ -51466,7 +49929,7 @@
         <f>IF(Dienstplan!AE124="","",Dienstplan!AE124)</f>
         <v/>
       </c>
-      <c r="AF9" s="75">
+      <c r="AF9" s="74">
         <f>IF(Dienstplan!AF124="","",Dienstplan!AF124)</f>
         <v/>
       </c>
@@ -51597,7 +50060,7 @@
         <f>IF(Dienstplan!AE125="","",Dienstplan!AE125)</f>
         <v/>
       </c>
-      <c r="AF10" s="74">
+      <c r="AF10" s="73">
         <f>IF(Dienstplan!AF125="","",Dienstplan!AF125)</f>
         <v/>
       </c>
@@ -51728,7 +50191,7 @@
         <f>IF(Dienstplan!AE126="","",Dienstplan!AE126)</f>
         <v/>
       </c>
-      <c r="AF11" s="75">
+      <c r="AF11" s="74">
         <f>IF(Dienstplan!AF126="","",Dienstplan!AF126)</f>
         <v/>
       </c>
@@ -51859,7 +50322,7 @@
         <f>IF(Dienstplan!AE127="","",Dienstplan!AE127)</f>
         <v/>
       </c>
-      <c r="AF12" s="74">
+      <c r="AF12" s="73">
         <f>IF(Dienstplan!AF127="","",Dienstplan!AF127)</f>
         <v/>
       </c>
@@ -51990,7 +50453,7 @@
         <f>IF(Dienstplan!AE128="","",Dienstplan!AE128)</f>
         <v/>
       </c>
-      <c r="AF13" s="75">
+      <c r="AF13" s="74">
         <f>IF(Dienstplan!AF128="","",Dienstplan!AF128)</f>
         <v/>
       </c>
@@ -52121,7 +50584,7 @@
         <f>IF(Dienstplan!AE129="","",Dienstplan!AE129)</f>
         <v/>
       </c>
-      <c r="AF14" s="74">
+      <c r="AF14" s="73">
         <f>IF(Dienstplan!AF129="","",Dienstplan!AF129)</f>
         <v/>
       </c>
@@ -52252,7 +50715,7 @@
         <f>IF(Dienstplan!AE130="","",Dienstplan!AE130)</f>
         <v/>
       </c>
-      <c r="AF15" s="75">
+      <c r="AF15" s="74">
         <f>IF(Dienstplan!AF130="","",Dienstplan!AF130)</f>
         <v/>
       </c>
@@ -52383,7 +50846,7 @@
         <f>IF(Dienstplan!AE131="","",Dienstplan!AE131)</f>
         <v/>
       </c>
-      <c r="AF16" s="74">
+      <c r="AF16" s="73">
         <f>IF(Dienstplan!AF131="","",Dienstplan!AF131)</f>
         <v/>
       </c>
@@ -52514,7 +50977,7 @@
         <f>IF(Dienstplan!AE132="","",Dienstplan!AE132)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="74">
         <f>IF(Dienstplan!AF132="","",Dienstplan!AF132)</f>
         <v/>
       </c>
@@ -52627,394 +51090,233 @@
           <t>!FI</t>
         </is>
       </c>
-      <c r="AF18" s="77" t="inlineStr">
+      <c r="AF18" s="76" t="inlineStr">
         <is>
           <t>!FI/NI</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="Y20" s="29" t="inlineStr">
+      <c r="Y20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="51" t="n"/>
-      <c r="AF20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="Y21" s="58" t="inlineStr">
+      <c r="Y21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="Y22" s="60" t="inlineStr"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="57" t="n"/>
+      <c r="Y22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="Y23" s="62" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="57" t="n"/>
+      <c r="Y24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="Y25" s="58" t="inlineStr">
+      <c r="Y25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="Y26" s="60" t="inlineStr"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="57" t="n"/>
+      <c r="Y26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="Y27" s="65" t="inlineStr">
+      <c r="Y27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="66" t="n"/>
-      <c r="AF27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="D25:G25"/>
@@ -53022,6 +51324,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="Y24:AF24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="K28:N28"/>
@@ -53249,7 +51552,7 @@
       <c r="AE3" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="AF3" s="71" t="n">
+      <c r="AF3" s="70" t="n">
         <v>31</v>
       </c>
     </row>
@@ -53409,7 +51712,7 @@
           <t>So</t>
         </is>
       </c>
-      <c r="AF4" s="72" t="inlineStr">
+      <c r="AF4" s="71" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -53461,7 +51764,7 @@
       <c r="AC5" s="37" t="n"/>
       <c r="AD5" s="7" t="n"/>
       <c r="AE5" s="7" t="n"/>
-      <c r="AF5" s="78" t="n">
+      <c r="AF5" s="77" t="n">
         <v>36</v>
       </c>
     </row>
@@ -53591,7 +51894,7 @@
         <f>IF(Dienstplan!AE140="","",Dienstplan!AE140)</f>
         <v/>
       </c>
-      <c r="AF6" s="74">
+      <c r="AF6" s="73">
         <f>IF(Dienstplan!AF140="","",Dienstplan!AF140)</f>
         <v/>
       </c>
@@ -53722,7 +52025,7 @@
         <f>IF(Dienstplan!AE141="","",Dienstplan!AE141)</f>
         <v/>
       </c>
-      <c r="AF7" s="75">
+      <c r="AF7" s="74">
         <f>IF(Dienstplan!AF141="","",Dienstplan!AF141)</f>
         <v/>
       </c>
@@ -53853,7 +52156,7 @@
         <f>IF(Dienstplan!AE142="","",Dienstplan!AE142)</f>
         <v/>
       </c>
-      <c r="AF8" s="74">
+      <c r="AF8" s="73">
         <f>IF(Dienstplan!AF142="","",Dienstplan!AF142)</f>
         <v/>
       </c>
@@ -53984,7 +52287,7 @@
         <f>IF(Dienstplan!AE143="","",Dienstplan!AE143)</f>
         <v/>
       </c>
-      <c r="AF9" s="75">
+      <c r="AF9" s="74">
         <f>IF(Dienstplan!AF143="","",Dienstplan!AF143)</f>
         <v/>
       </c>
@@ -54115,7 +52418,7 @@
         <f>IF(Dienstplan!AE144="","",Dienstplan!AE144)</f>
         <v/>
       </c>
-      <c r="AF10" s="74">
+      <c r="AF10" s="73">
         <f>IF(Dienstplan!AF144="","",Dienstplan!AF144)</f>
         <v/>
       </c>
@@ -54246,7 +52549,7 @@
         <f>IF(Dienstplan!AE145="","",Dienstplan!AE145)</f>
         <v/>
       </c>
-      <c r="AF11" s="75">
+      <c r="AF11" s="74">
         <f>IF(Dienstplan!AF145="","",Dienstplan!AF145)</f>
         <v/>
       </c>
@@ -54377,7 +52680,7 @@
         <f>IF(Dienstplan!AE146="","",Dienstplan!AE146)</f>
         <v/>
       </c>
-      <c r="AF12" s="74">
+      <c r="AF12" s="73">
         <f>IF(Dienstplan!AF146="","",Dienstplan!AF146)</f>
         <v/>
       </c>
@@ -54508,7 +52811,7 @@
         <f>IF(Dienstplan!AE147="","",Dienstplan!AE147)</f>
         <v/>
       </c>
-      <c r="AF13" s="75">
+      <c r="AF13" s="74">
         <f>IF(Dienstplan!AF147="","",Dienstplan!AF147)</f>
         <v/>
       </c>
@@ -54639,7 +52942,7 @@
         <f>IF(Dienstplan!AE148="","",Dienstplan!AE148)</f>
         <v/>
       </c>
-      <c r="AF14" s="74">
+      <c r="AF14" s="73">
         <f>IF(Dienstplan!AF148="","",Dienstplan!AF148)</f>
         <v/>
       </c>
@@ -54770,7 +53073,7 @@
         <f>IF(Dienstplan!AE149="","",Dienstplan!AE149)</f>
         <v/>
       </c>
-      <c r="AF15" s="75">
+      <c r="AF15" s="74">
         <f>IF(Dienstplan!AF149="","",Dienstplan!AF149)</f>
         <v/>
       </c>
@@ -54901,7 +53204,7 @@
         <f>IF(Dienstplan!AE150="","",Dienstplan!AE150)</f>
         <v/>
       </c>
-      <c r="AF16" s="74">
+      <c r="AF16" s="73">
         <f>IF(Dienstplan!AF150="","",Dienstplan!AF150)</f>
         <v/>
       </c>
@@ -55032,7 +53335,7 @@
         <f>IF(Dienstplan!AE151="","",Dienstplan!AE151)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="74">
         <f>IF(Dienstplan!AF151="","",Dienstplan!AF151)</f>
         <v/>
       </c>
@@ -55153,394 +53456,233 @@
       </c>
       <c r="AD18" s="47" t="n"/>
       <c r="AE18" s="47" t="n"/>
-      <c r="AF18" s="77" t="inlineStr">
+      <c r="AF18" s="76" t="inlineStr">
         <is>
           <t>!FI/SI</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Legende</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="Y20" s="29" t="inlineStr">
+      <c r="Y20" s="51" t="inlineStr">
         <is>
           <t>Unterschriften</t>
         </is>
       </c>
-      <c r="Z20" s="51" t="n"/>
-      <c r="AA20" s="51" t="n"/>
-      <c r="AB20" s="51" t="n"/>
-      <c r="AC20" s="51" t="n"/>
-      <c r="AD20" s="51" t="n"/>
-      <c r="AE20" s="51" t="n"/>
-      <c r="AF20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="56" t="inlineStr">
+      <c r="H21" s="54" t="inlineStr">
         <is>
           <t>FII 06:00-14:00</t>
         </is>
       </c>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="54" t="n"/>
       <c r="K21" s="55" t="inlineStr">
         <is>
           <t>Frühschicht II</t>
         </is>
       </c>
-      <c r="L21" s="54" t="n"/>
-      <c r="M21" s="54" t="n"/>
-      <c r="N21" s="57" t="n"/>
-      <c r="Y21" s="58" t="inlineStr">
+      <c r="Y21" s="56" t="inlineStr">
         <is>
           <t>Erstellt von:</t>
         </is>
       </c>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="54" t="n"/>
-      <c r="AB21" s="54" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="54" t="n"/>
-      <c r="AF21" s="57" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>EH 08:00-17:00</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Erste Hilfe</t>
         </is>
       </c>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="56" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>SI 14:00-22:00</t>
         </is>
       </c>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
       <c r="K22" s="55" t="inlineStr">
         <is>
           <t>Spätschicht I</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="57" t="n"/>
-      <c r="Y22" s="60" t="inlineStr"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="54" t="n"/>
-      <c r="AF22" s="57" t="n"/>
+      <c r="Y22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>KU 08:30-16:30</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="55" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Kuppenheim</t>
         </is>
       </c>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="56" t="inlineStr">
+      <c r="H23" s="54" t="inlineStr">
         <is>
           <t>SII 14:00-21:00</t>
         </is>
       </c>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
       <c r="K23" s="55" t="inlineStr">
         <is>
           <t>Spätschicht II</t>
         </is>
       </c>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="Y23" s="62" t="inlineStr">
+      <c r="Y23" s="60" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="54" t="n"/>
-      <c r="AB23" s="54" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="57" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="56" t="inlineStr">
+      <c r="H24" s="54" t="inlineStr">
         <is>
           <t>NI 22:00-06:00</t>
         </is>
       </c>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
       <c r="K24" s="55" t="inlineStr">
         <is>
           <t>Nachtschicht I</t>
         </is>
       </c>
-      <c r="L24" s="54" t="n"/>
-      <c r="M24" s="54" t="n"/>
-      <c r="N24" s="57" t="n"/>
-      <c r="Y24" s="60" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="54" t="n"/>
-      <c r="AB24" s="54" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="54" t="n"/>
-      <c r="AF24" s="57" t="n"/>
+      <c r="Y24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="55" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Gleittag</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-      <c r="H25" s="56" t="inlineStr">
+      <c r="H25" s="54" t="inlineStr">
         <is>
           <t>DI 08:00-15:30</t>
         </is>
       </c>
-      <c r="I25" s="54" t="n"/>
-      <c r="J25" s="54" t="n"/>
       <c r="K25" s="55" t="inlineStr">
         <is>
           <t>Dienst I</t>
         </is>
       </c>
-      <c r="L25" s="54" t="n"/>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="Y25" s="58" t="inlineStr">
+      <c r="Y25" s="56" t="inlineStr">
         <is>
           <t>Genehmigt von:</t>
         </is>
       </c>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="54" t="n"/>
-      <c r="AB25" s="54" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="54" t="n"/>
-      <c r="AF25" s="57" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Ausgleichstag</t>
         </is>
       </c>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="56" t="inlineStr">
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>DII 08:30-16:00</t>
         </is>
       </c>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
       <c r="K26" s="55" t="inlineStr">
         <is>
           <t>Dienst II</t>
         </is>
       </c>
-      <c r="L26" s="54" t="n"/>
-      <c r="M26" s="54" t="n"/>
-      <c r="N26" s="57" t="n"/>
-      <c r="Y26" s="60" t="inlineStr"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="54" t="n"/>
-      <c r="AB26" s="54" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="57" t="n"/>
+      <c r="Y26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>Fobi</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="55" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="56" t="inlineStr">
+      <c r="H27" s="54" t="inlineStr">
         <is>
           <t>KT IRTAZ</t>
         </is>
       </c>
-      <c r="I27" s="54" t="n"/>
-      <c r="J27" s="54" t="n"/>
       <c r="K27" s="55" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="L27" s="54" t="n"/>
-      <c r="M27" s="54" t="n"/>
-      <c r="N27" s="57" t="n"/>
-      <c r="Y27" s="65" t="inlineStr">
+      <c r="Y27" s="64" t="inlineStr">
         <is>
           <t>Datum / Unterschrift</t>
         </is>
       </c>
-      <c r="Z27" s="66" t="n"/>
-      <c r="AA27" s="66" t="n"/>
-      <c r="AB27" s="66" t="n"/>
-      <c r="AC27" s="66" t="n"/>
-      <c r="AD27" s="66" t="n"/>
-      <c r="AE27" s="66" t="n"/>
-      <c r="AF27" s="67" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>FI 06:00-14:00</t>
         </is>
       </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Frühschicht I</t>
         </is>
       </c>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="56" t="inlineStr">
+      <c r="H28" s="67" t="inlineStr">
         <is>
           <t>SD Individuell</t>
         </is>
       </c>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="55" t="inlineStr">
+      <c r="K28" s="68" t="inlineStr">
         <is>
           <t>Sonderdienst</t>
         </is>
       </c>
-      <c r="L28" s="54" t="n"/>
-      <c r="M28" s="54" t="n"/>
-      <c r="N28" s="57" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="69" t="inlineStr"/>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="70" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>Wochenende / Feiertag</t>
         </is>
       </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="66" t="n"/>
-      <c r="J29" s="66" t="n"/>
-      <c r="K29" s="66" t="n"/>
-      <c r="L29" s="66" t="n"/>
-      <c r="M29" s="66" t="n"/>
-      <c r="N29" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="K23:N23"/>
     <mergeCell ref="D25:G25"/>
@@ -55548,6 +53690,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="Y24:AF24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="K28:N28"/>

--- a/Dienstplan_2026_neu.xlsx
+++ b/Dienstplan_2026_neu.xlsx
@@ -513,7 +513,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -16941,36 +16941,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19249,37 +19249,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21617,36 +21617,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23916,37 +23916,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35413,37 +35413,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37713,34 +37713,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39827,37 +39827,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42112,36 +42112,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44345,37 +44345,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46697,36 +46697,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49002,37 +49002,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -51357,37 +51357,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="3.8" customWidth="1" min="2" max="2"/>
-    <col width="3.8" customWidth="1" min="3" max="3"/>
-    <col width="3.8" customWidth="1" min="4" max="4"/>
-    <col width="3.8" customWidth="1" min="5" max="5"/>
-    <col width="3.8" customWidth="1" min="6" max="6"/>
-    <col width="3.8" customWidth="1" min="7" max="7"/>
-    <col width="3.8" customWidth="1" min="8" max="8"/>
-    <col width="3.8" customWidth="1" min="9" max="9"/>
-    <col width="3.8" customWidth="1" min="10" max="10"/>
-    <col width="3.8" customWidth="1" min="11" max="11"/>
-    <col width="3.8" customWidth="1" min="12" max="12"/>
-    <col width="3.8" customWidth="1" min="13" max="13"/>
-    <col width="3.8" customWidth="1" min="14" max="14"/>
-    <col width="3.8" customWidth="1" min="15" max="15"/>
-    <col width="3.8" customWidth="1" min="16" max="16"/>
-    <col width="3.8" customWidth="1" min="17" max="17"/>
-    <col width="3.8" customWidth="1" min="18" max="18"/>
-    <col width="3.8" customWidth="1" min="19" max="19"/>
-    <col width="3.8" customWidth="1" min="20" max="20"/>
-    <col width="3.8" customWidth="1" min="21" max="21"/>
-    <col width="3.8" customWidth="1" min="22" max="22"/>
-    <col width="3.8" customWidth="1" min="23" max="23"/>
-    <col width="3.8" customWidth="1" min="24" max="24"/>
-    <col width="3.8" customWidth="1" min="25" max="25"/>
-    <col width="3.8" customWidth="1" min="26" max="26"/>
-    <col width="3.8" customWidth="1" min="27" max="27"/>
-    <col width="3.8" customWidth="1" min="28" max="28"/>
-    <col width="3.8" customWidth="1" min="29" max="29"/>
-    <col width="3.8" customWidth="1" min="30" max="30"/>
-    <col width="3.8" customWidth="1" min="31" max="31"/>
-    <col width="3.8" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Dienstplan_2026_neu.xlsx
+++ b/Dienstplan_2026_neu.xlsx
@@ -405,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -542,10 +542,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -556,6 +553,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -666,9 +666,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -18865,35 +18862,35 @@
     <mergeCell ref="E61:L61"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:AF18">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B7="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B7="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B7="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B7="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B7="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B7="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B7="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B7="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B7="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B7="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:AF19">
@@ -18907,35 +18904,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:AC38">
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
+      <formula>B27="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="14" dxfId="0" stopIfTrue="1">
+      <formula>B27="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="15" dxfId="1" stopIfTrue="1">
+      <formula>B27="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="16" dxfId="2" stopIfTrue="1">
+      <formula>B27="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="17" dxfId="3" stopIfTrue="1">
+      <formula>B27="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="18" dxfId="0" stopIfTrue="1">
+      <formula>B27="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
+      <formula>B27="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="20" dxfId="4" stopIfTrue="1">
+      <formula>B27="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="21" dxfId="0" stopIfTrue="1">
+      <formula>B27="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="22" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="22" dxfId="4" stopIfTrue="1">
+      <formula>B27="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:AC39">
@@ -18949,35 +18946,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46:AF57">
-    <cfRule type="cellIs" priority="25" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="25" dxfId="0" stopIfTrue="1">
+      <formula>B46="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="26" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="26" dxfId="0" stopIfTrue="1">
+      <formula>B46="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="27" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="27" dxfId="1" stopIfTrue="1">
+      <formula>B46="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="28" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="28" dxfId="2" stopIfTrue="1">
+      <formula>B46="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="29" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="29" dxfId="3" stopIfTrue="1">
+      <formula>B46="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="30" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="30" dxfId="0" stopIfTrue="1">
+      <formula>B46="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="31" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
+      <formula>B46="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="32" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="32" dxfId="4" stopIfTrue="1">
+      <formula>B46="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="33" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="33" dxfId="0" stopIfTrue="1">
+      <formula>B46="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="34" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="34" dxfId="4" stopIfTrue="1">
+      <formula>B46="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AF58">
@@ -18991,35 +18988,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66:AE77">
-    <cfRule type="cellIs" priority="37" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="37" dxfId="0" stopIfTrue="1">
+      <formula>B66="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="38" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="38" dxfId="0" stopIfTrue="1">
+      <formula>B66="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="39" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="39" dxfId="1" stopIfTrue="1">
+      <formula>B66="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="40" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="40" dxfId="2" stopIfTrue="1">
+      <formula>B66="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="41" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="41" dxfId="3" stopIfTrue="1">
+      <formula>B66="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="42" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="42" dxfId="0" stopIfTrue="1">
+      <formula>B66="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="43" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="43" dxfId="0" stopIfTrue="1">
+      <formula>B66="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="44" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="44" dxfId="4" stopIfTrue="1">
+      <formula>B66="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="45" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="45" dxfId="0" stopIfTrue="1">
+      <formula>B66="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="46" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="46" dxfId="4" stopIfTrue="1">
+      <formula>B66="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78:AE78">
@@ -19033,35 +19030,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86:AF97">
-    <cfRule type="cellIs" priority="49" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="49" dxfId="0" stopIfTrue="1">
+      <formula>B86="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="50" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="50" dxfId="0" stopIfTrue="1">
+      <formula>B86="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="51" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="51" dxfId="1" stopIfTrue="1">
+      <formula>B86="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="52" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="52" dxfId="2" stopIfTrue="1">
+      <formula>B86="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="53" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="53" dxfId="3" stopIfTrue="1">
+      <formula>B86="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="54" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="54" dxfId="0" stopIfTrue="1">
+      <formula>B86="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="55" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="55" dxfId="0" stopIfTrue="1">
+      <formula>B86="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="56" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="56" dxfId="4" stopIfTrue="1">
+      <formula>B86="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="57" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="57" dxfId="0" stopIfTrue="1">
+      <formula>B86="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="58" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="58" dxfId="4" stopIfTrue="1">
+      <formula>B86="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98:AF98">
@@ -19075,35 +19072,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:AE117">
-    <cfRule type="cellIs" priority="61" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="61" dxfId="0" stopIfTrue="1">
+      <formula>B106="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="62" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="62" dxfId="0" stopIfTrue="1">
+      <formula>B106="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="63" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="63" dxfId="1" stopIfTrue="1">
+      <formula>B106="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="64" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="64" dxfId="2" stopIfTrue="1">
+      <formula>B106="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="65" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="65" dxfId="3" stopIfTrue="1">
+      <formula>B106="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="66" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="66" dxfId="0" stopIfTrue="1">
+      <formula>B106="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="67" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="67" dxfId="0" stopIfTrue="1">
+      <formula>B106="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="68" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="68" dxfId="4" stopIfTrue="1">
+      <formula>B106="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="69" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="69" dxfId="0" stopIfTrue="1">
+      <formula>B106="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="70" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="70" dxfId="4" stopIfTrue="1">
+      <formula>B106="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118:AE118">
@@ -19117,35 +19114,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126:AF137">
-    <cfRule type="cellIs" priority="73" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="73" dxfId="0" stopIfTrue="1">
+      <formula>B126="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="74" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="74" dxfId="0" stopIfTrue="1">
+      <formula>B126="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="75" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="75" dxfId="1" stopIfTrue="1">
+      <formula>B126="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="76" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="76" dxfId="2" stopIfTrue="1">
+      <formula>B126="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="77" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="77" dxfId="3" stopIfTrue="1">
+      <formula>B126="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="78" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="78" dxfId="0" stopIfTrue="1">
+      <formula>B126="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="79" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="79" dxfId="0" stopIfTrue="1">
+      <formula>B126="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="80" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="80" dxfId="4" stopIfTrue="1">
+      <formula>B126="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="81" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="81" dxfId="0" stopIfTrue="1">
+      <formula>B126="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="82" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="82" dxfId="4" stopIfTrue="1">
+      <formula>B126="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138:AF138">
@@ -19159,35 +19156,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B146:AF157">
-    <cfRule type="cellIs" priority="85" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="85" dxfId="0" stopIfTrue="1">
+      <formula>B146="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="86" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="86" dxfId="0" stopIfTrue="1">
+      <formula>B146="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="87" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="87" dxfId="1" stopIfTrue="1">
+      <formula>B146="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="88" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="88" dxfId="2" stopIfTrue="1">
+      <formula>B146="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="89" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="89" dxfId="3" stopIfTrue="1">
+      <formula>B146="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="90" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="90" dxfId="0" stopIfTrue="1">
+      <formula>B146="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="91" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="91" dxfId="0" stopIfTrue="1">
+      <formula>B146="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="92" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="92" dxfId="4" stopIfTrue="1">
+      <formula>B146="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="93" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="93" dxfId="0" stopIfTrue="1">
+      <formula>B146="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="94" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="94" dxfId="4" stopIfTrue="1">
+      <formula>B146="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158:AF158">
@@ -19201,35 +19198,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B166:AE177">
-    <cfRule type="cellIs" priority="97" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="97" dxfId="0" stopIfTrue="1">
+      <formula>B166="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="98" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="98" dxfId="0" stopIfTrue="1">
+      <formula>B166="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="99" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="99" dxfId="1" stopIfTrue="1">
+      <formula>B166="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="100" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="100" dxfId="2" stopIfTrue="1">
+      <formula>B166="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="101" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="101" dxfId="3" stopIfTrue="1">
+      <formula>B166="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="102" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="102" dxfId="0" stopIfTrue="1">
+      <formula>B166="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="103" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="103" dxfId="0" stopIfTrue="1">
+      <formula>B166="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="104" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="104" dxfId="4" stopIfTrue="1">
+      <formula>B166="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="105" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="105" dxfId="0" stopIfTrue="1">
+      <formula>B166="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="106" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="106" dxfId="4" stopIfTrue="1">
+      <formula>B166="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B178:AE178">
@@ -19243,35 +19240,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186:AF197">
-    <cfRule type="cellIs" priority="109" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="109" dxfId="0" stopIfTrue="1">
+      <formula>B186="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="110" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="110" dxfId="0" stopIfTrue="1">
+      <formula>B186="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="111" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="111" dxfId="1" stopIfTrue="1">
+      <formula>B186="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="112" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="112" dxfId="2" stopIfTrue="1">
+      <formula>B186="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="113" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="113" dxfId="3" stopIfTrue="1">
+      <formula>B186="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="114" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="114" dxfId="0" stopIfTrue="1">
+      <formula>B186="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="115" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="115" dxfId="0" stopIfTrue="1">
+      <formula>B186="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="116" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="116" dxfId="4" stopIfTrue="1">
+      <formula>B186="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="117" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="117" dxfId="0" stopIfTrue="1">
+      <formula>B186="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="118" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="118" dxfId="4" stopIfTrue="1">
+      <formula>B186="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198:AF198">
@@ -19285,35 +19282,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205:AE216">
-    <cfRule type="cellIs" priority="121" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="121" dxfId="0" stopIfTrue="1">
+      <formula>B205="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="122" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="122" dxfId="0" stopIfTrue="1">
+      <formula>B205="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="123" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="123" dxfId="1" stopIfTrue="1">
+      <formula>B205="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="124" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="124" dxfId="2" stopIfTrue="1">
+      <formula>B205="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="125" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="125" dxfId="3" stopIfTrue="1">
+      <formula>B205="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="126" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="126" dxfId="0" stopIfTrue="1">
+      <formula>B205="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="127" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="127" dxfId="0" stopIfTrue="1">
+      <formula>B205="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="128" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="128" dxfId="4" stopIfTrue="1">
+      <formula>B205="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="129" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="129" dxfId="0" stopIfTrue="1">
+      <formula>B205="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="130" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="130" dxfId="4" stopIfTrue="1">
+      <formula>B205="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B217:AE217">
@@ -19327,35 +19324,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225:AF236">
-    <cfRule type="cellIs" priority="133" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="133" dxfId="0" stopIfTrue="1">
+      <formula>B225="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="134" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="134" dxfId="0" stopIfTrue="1">
+      <formula>B225="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="135" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="135" dxfId="1" stopIfTrue="1">
+      <formula>B225="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="136" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="136" dxfId="2" stopIfTrue="1">
+      <formula>B225="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="137" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="137" dxfId="3" stopIfTrue="1">
+      <formula>B225="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="138" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="138" dxfId="0" stopIfTrue="1">
+      <formula>B225="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="139" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="139" dxfId="0" stopIfTrue="1">
+      <formula>B225="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="140" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="140" dxfId="4" stopIfTrue="1">
+      <formula>B225="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="141" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="141" dxfId="0" stopIfTrue="1">
+      <formula>B225="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="142" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="142" dxfId="4" stopIfTrue="1">
+      <formula>B225="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237:AF237">
@@ -20885,134 +20882,134 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="50">
         <f>IF(Dienstplan!B175="","",Dienstplan!B175)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C175="","",Dienstplan!C175)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D175="","",Dienstplan!D175)</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="50">
         <f>IF(Dienstplan!E175="","",Dienstplan!E175)</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="49">
         <f>IF(Dienstplan!F175="","",Dienstplan!F175)</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="49">
         <f>IF(Dienstplan!G175="","",Dienstplan!G175)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H175="","",Dienstplan!H175)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I175="","",Dienstplan!I175)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J175="","",Dienstplan!J175)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K175="","",Dienstplan!K175)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L175="","",Dienstplan!L175)</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="49">
         <f>IF(Dienstplan!M175="","",Dienstplan!M175)</f>
         <v/>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="49">
         <f>IF(Dienstplan!N175="","",Dienstplan!N175)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="50">
         <f>IF(Dienstplan!O175="","",Dienstplan!O175)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P175="","",Dienstplan!P175)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q175="","",Dienstplan!Q175)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R175="","",Dienstplan!R175)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S175="","",Dienstplan!S175)</f>
         <v/>
       </c>
-      <c r="T15" s="17">
+      <c r="T15" s="49">
         <f>IF(Dienstplan!T175="","",Dienstplan!T175)</f>
         <v/>
       </c>
-      <c r="U15" s="17">
+      <c r="U15" s="49">
         <f>IF(Dienstplan!U175="","",Dienstplan!U175)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V175="","",Dienstplan!V175)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W175="","",Dienstplan!W175)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X175="","",Dienstplan!X175)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y175="","",Dienstplan!Y175)</f>
         <v/>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="50">
         <f>IF(Dienstplan!Z175="","",Dienstplan!Z175)</f>
         <v/>
       </c>
-      <c r="AA15" s="17">
+      <c r="AA15" s="49">
         <f>IF(Dienstplan!AA175="","",Dienstplan!AA175)</f>
         <v/>
       </c>
-      <c r="AB15" s="17">
+      <c r="AB15" s="49">
         <f>IF(Dienstplan!AB175="","",Dienstplan!AB175)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC175="","",Dienstplan!AC175)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD175="","",Dienstplan!AD175)</f>
         <v/>
       </c>
-      <c r="AE15" s="35">
+      <c r="AE15" s="75">
         <f>IF(Dienstplan!AE175="","",Dienstplan!AE175)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -21133,134 +21130,134 @@
         <f>IF(Dienstplan!AD176="","",Dienstplan!AD176)</f>
         <v/>
       </c>
-      <c r="AE16" s="34">
+      <c r="AE16" s="18">
         <f>IF(Dienstplan!AE176="","",Dienstplan!AE176)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="21">
         <f>IF(Dienstplan!B177="","",Dienstplan!B177)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C177="","",Dienstplan!C177)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D177="","",Dienstplan!D177)</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="21">
         <f>IF(Dienstplan!E177="","",Dienstplan!E177)</f>
         <v/>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="17">
         <f>IF(Dienstplan!F177="","",Dienstplan!F177)</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="17">
         <f>IF(Dienstplan!G177="","",Dienstplan!G177)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H177="","",Dienstplan!H177)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I177="","",Dienstplan!I177)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J177="","",Dienstplan!J177)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K177="","",Dienstplan!K177)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L177="","",Dienstplan!L177)</f>
         <v/>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="17">
         <f>IF(Dienstplan!M177="","",Dienstplan!M177)</f>
         <v/>
       </c>
-      <c r="N17" s="50">
+      <c r="N17" s="17">
         <f>IF(Dienstplan!N177="","",Dienstplan!N177)</f>
         <v/>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="21">
         <f>IF(Dienstplan!O177="","",Dienstplan!O177)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P177="","",Dienstplan!P177)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q177="","",Dienstplan!Q177)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R177="","",Dienstplan!R177)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S177="","",Dienstplan!S177)</f>
         <v/>
       </c>
-      <c r="T17" s="50">
+      <c r="T17" s="17">
         <f>IF(Dienstplan!T177="","",Dienstplan!T177)</f>
         <v/>
       </c>
-      <c r="U17" s="50">
+      <c r="U17" s="17">
         <f>IF(Dienstplan!U177="","",Dienstplan!U177)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V177="","",Dienstplan!V177)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W177="","",Dienstplan!W177)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X177="","",Dienstplan!X177)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y177="","",Dienstplan!Y177)</f>
         <v/>
       </c>
-      <c r="Z17" s="51">
+      <c r="Z17" s="21">
         <f>IF(Dienstplan!Z177="","",Dienstplan!Z177)</f>
         <v/>
       </c>
-      <c r="AA17" s="50">
+      <c r="AA17" s="17">
         <f>IF(Dienstplan!AA177="","",Dienstplan!AA177)</f>
         <v/>
       </c>
-      <c r="AB17" s="50">
+      <c r="AB17" s="17">
         <f>IF(Dienstplan!AB177="","",Dienstplan!AB177)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC177="","",Dienstplan!AC177)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD177="","",Dienstplan!AD177)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE177="","",Dienstplan!AE177)</f>
         <v/>
       </c>
@@ -21587,35 +21584,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AE17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -23175,138 +23172,138 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="50">
         <f>IF(Dienstplan!B195="","",Dienstplan!B195)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C195="","",Dienstplan!C195)</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="49">
         <f>IF(Dienstplan!D195="","",Dienstplan!D195)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="49">
         <f>IF(Dienstplan!E195="","",Dienstplan!E195)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F195="","",Dienstplan!F195)</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="50">
         <f>IF(Dienstplan!G195="","",Dienstplan!G195)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H195="","",Dienstplan!H195)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I195="","",Dienstplan!I195)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J195="","",Dienstplan!J195)</f>
         <v/>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="49">
         <f>IF(Dienstplan!K195="","",Dienstplan!K195)</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="49">
         <f>IF(Dienstplan!L195="","",Dienstplan!L195)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M195="","",Dienstplan!M195)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N195="","",Dienstplan!N195)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="50">
         <f>IF(Dienstplan!O195="","",Dienstplan!O195)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P195="","",Dienstplan!P195)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q195="","",Dienstplan!Q195)</f>
         <v/>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="49">
         <f>IF(Dienstplan!R195="","",Dienstplan!R195)</f>
         <v/>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="49">
         <f>IF(Dienstplan!S195="","",Dienstplan!S195)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T195="","",Dienstplan!T195)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U195="","",Dienstplan!U195)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V195="","",Dienstplan!V195)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W195="","",Dienstplan!W195)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X195="","",Dienstplan!X195)</f>
         <v/>
       </c>
-      <c r="Y15" s="17">
+      <c r="Y15" s="49">
         <f>IF(Dienstplan!Y195="","",Dienstplan!Y195)</f>
         <v/>
       </c>
-      <c r="Z15" s="17">
+      <c r="Z15" s="49">
         <f>IF(Dienstplan!Z195="","",Dienstplan!Z195)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA195="","",Dienstplan!AA195)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB195="","",Dienstplan!AB195)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC195="","",Dienstplan!AC195)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD195="","",Dienstplan!AD195)</f>
         <v/>
       </c>
-      <c r="AE15" s="21">
+      <c r="AE15" s="50">
         <f>IF(Dienstplan!AE195="","",Dienstplan!AE195)</f>
         <v/>
       </c>
-      <c r="AF15" s="19">
+      <c r="AF15" s="51">
         <f>IF(Dienstplan!AF195="","",Dienstplan!AF195)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -23431,138 +23428,138 @@
         <f>IF(Dienstplan!AE196="","",Dienstplan!AE196)</f>
         <v/>
       </c>
-      <c r="AF16" s="19">
+      <c r="AF16" s="17">
         <f>IF(Dienstplan!AF196="","",Dienstplan!AF196)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="21">
         <f>IF(Dienstplan!B197="","",Dienstplan!B197)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C197="","",Dienstplan!C197)</f>
         <v/>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="17">
         <f>IF(Dienstplan!D197="","",Dienstplan!D197)</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="17">
         <f>IF(Dienstplan!E197="","",Dienstplan!E197)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F197="","",Dienstplan!F197)</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="21">
         <f>IF(Dienstplan!G197="","",Dienstplan!G197)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H197="","",Dienstplan!H197)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I197="","",Dienstplan!I197)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J197="","",Dienstplan!J197)</f>
         <v/>
       </c>
-      <c r="K17" s="50">
+      <c r="K17" s="17">
         <f>IF(Dienstplan!K197="","",Dienstplan!K197)</f>
         <v/>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="17">
         <f>IF(Dienstplan!L197="","",Dienstplan!L197)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M197="","",Dienstplan!M197)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N197="","",Dienstplan!N197)</f>
         <v/>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="21">
         <f>IF(Dienstplan!O197="","",Dienstplan!O197)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P197="","",Dienstplan!P197)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q197="","",Dienstplan!Q197)</f>
         <v/>
       </c>
-      <c r="R17" s="50">
+      <c r="R17" s="17">
         <f>IF(Dienstplan!R197="","",Dienstplan!R197)</f>
         <v/>
       </c>
-      <c r="S17" s="50">
+      <c r="S17" s="17">
         <f>IF(Dienstplan!S197="","",Dienstplan!S197)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T197="","",Dienstplan!T197)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U197="","",Dienstplan!U197)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V197="","",Dienstplan!V197)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W197="","",Dienstplan!W197)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X197="","",Dienstplan!X197)</f>
         <v/>
       </c>
-      <c r="Y17" s="50">
+      <c r="Y17" s="17">
         <f>IF(Dienstplan!Y197="","",Dienstplan!Y197)</f>
         <v/>
       </c>
-      <c r="Z17" s="50">
+      <c r="Z17" s="17">
         <f>IF(Dienstplan!Z197="","",Dienstplan!Z197)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA197="","",Dienstplan!AA197)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB197="","",Dienstplan!AB197)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC197="","",Dienstplan!AC197)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD197="","",Dienstplan!AD197)</f>
         <v/>
       </c>
-      <c r="AE17" s="51">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE197="","",Dienstplan!AE197)</f>
         <v/>
       </c>
-      <c r="AF17" s="52">
+      <c r="AF17" s="17">
         <f>IF(Dienstplan!AF197="","",Dienstplan!AF197)</f>
         <v/>
       </c>
@@ -23889,35 +23886,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AF17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -25427,134 +25424,134 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="49">
         <f>IF(Dienstplan!B214="","",Dienstplan!B214)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C214="","",Dienstplan!C214)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D214="","",Dienstplan!D214)</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="50">
         <f>IF(Dienstplan!E214="","",Dienstplan!E214)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F214="","",Dienstplan!F214)</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="50">
         <f>IF(Dienstplan!G214="","",Dienstplan!G214)</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="49">
         <f>IF(Dienstplan!H214="","",Dienstplan!H214)</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="49">
         <f>IF(Dienstplan!I214="","",Dienstplan!I214)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J214="","",Dienstplan!J214)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K214="","",Dienstplan!K214)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L214="","",Dienstplan!L214)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M214="","",Dienstplan!M214)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N214="","",Dienstplan!N214)</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="49">
         <f>IF(Dienstplan!O214="","",Dienstplan!O214)</f>
         <v/>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="49">
         <f>IF(Dienstplan!P214="","",Dienstplan!P214)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q214="","",Dienstplan!Q214)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R214="","",Dienstplan!R214)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S214="","",Dienstplan!S214)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T214="","",Dienstplan!T214)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U214="","",Dienstplan!U214)</f>
         <v/>
       </c>
-      <c r="V15" s="17">
+      <c r="V15" s="49">
         <f>IF(Dienstplan!V214="","",Dienstplan!V214)</f>
         <v/>
       </c>
-      <c r="W15" s="17">
+      <c r="W15" s="49">
         <f>IF(Dienstplan!W214="","",Dienstplan!W214)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X214="","",Dienstplan!X214)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y214="","",Dienstplan!Y214)</f>
         <v/>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="50">
         <f>IF(Dienstplan!Z214="","",Dienstplan!Z214)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA214="","",Dienstplan!AA214)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB214="","",Dienstplan!AB214)</f>
         <v/>
       </c>
-      <c r="AC15" s="17">
+      <c r="AC15" s="49">
         <f>IF(Dienstplan!AC214="","",Dienstplan!AC214)</f>
         <v/>
       </c>
-      <c r="AD15" s="17">
+      <c r="AD15" s="49">
         <f>IF(Dienstplan!AD214="","",Dienstplan!AD214)</f>
         <v/>
       </c>
-      <c r="AE15" s="35">
+      <c r="AE15" s="75">
         <f>IF(Dienstplan!AE214="","",Dienstplan!AE214)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -25675,134 +25672,134 @@
         <f>IF(Dienstplan!AD215="","",Dienstplan!AD215)</f>
         <v/>
       </c>
-      <c r="AE16" s="34">
+      <c r="AE16" s="18">
         <f>IF(Dienstplan!AE215="","",Dienstplan!AE215)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="17">
         <f>IF(Dienstplan!B216="","",Dienstplan!B216)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C216="","",Dienstplan!C216)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D216="","",Dienstplan!D216)</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="21">
         <f>IF(Dienstplan!E216="","",Dienstplan!E216)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F216="","",Dienstplan!F216)</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="21">
         <f>IF(Dienstplan!G216="","",Dienstplan!G216)</f>
         <v/>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="17">
         <f>IF(Dienstplan!H216="","",Dienstplan!H216)</f>
         <v/>
       </c>
-      <c r="I17" s="50">
+      <c r="I17" s="17">
         <f>IF(Dienstplan!I216="","",Dienstplan!I216)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J216="","",Dienstplan!J216)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K216="","",Dienstplan!K216)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L216="","",Dienstplan!L216)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M216="","",Dienstplan!M216)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N216="","",Dienstplan!N216)</f>
         <v/>
       </c>
-      <c r="O17" s="50">
+      <c r="O17" s="17">
         <f>IF(Dienstplan!O216="","",Dienstplan!O216)</f>
         <v/>
       </c>
-      <c r="P17" s="50">
+      <c r="P17" s="17">
         <f>IF(Dienstplan!P216="","",Dienstplan!P216)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q216="","",Dienstplan!Q216)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R216="","",Dienstplan!R216)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S216="","",Dienstplan!S216)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T216="","",Dienstplan!T216)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U216="","",Dienstplan!U216)</f>
         <v/>
       </c>
-      <c r="V17" s="50">
+      <c r="V17" s="17">
         <f>IF(Dienstplan!V216="","",Dienstplan!V216)</f>
         <v/>
       </c>
-      <c r="W17" s="50">
+      <c r="W17" s="17">
         <f>IF(Dienstplan!W216="","",Dienstplan!W216)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X216="","",Dienstplan!X216)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y216="","",Dienstplan!Y216)</f>
         <v/>
       </c>
-      <c r="Z17" s="51">
+      <c r="Z17" s="21">
         <f>IF(Dienstplan!Z216="","",Dienstplan!Z216)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA216="","",Dienstplan!AA216)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB216="","",Dienstplan!AB216)</f>
         <v/>
       </c>
-      <c r="AC17" s="50">
+      <c r="AC17" s="17">
         <f>IF(Dienstplan!AC216="","",Dienstplan!AC216)</f>
         <v/>
       </c>
-      <c r="AD17" s="50">
+      <c r="AD17" s="17">
         <f>IF(Dienstplan!AD216="","",Dienstplan!AD216)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE216="","",Dienstplan!AE216)</f>
         <v/>
       </c>
@@ -26128,35 +26125,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AE17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -27717,138 +27714,138 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="50">
         <f>IF(Dienstplan!B234="","",Dienstplan!B234)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C234="","",Dienstplan!C234)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D234="","",Dienstplan!D234)</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="50">
         <f>IF(Dienstplan!E234="","",Dienstplan!E234)</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="49">
         <f>IF(Dienstplan!F234="","",Dienstplan!F234)</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="49">
         <f>IF(Dienstplan!G234="","",Dienstplan!G234)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H234="","",Dienstplan!H234)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I234="","",Dienstplan!I234)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J234="","",Dienstplan!J234)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K234="","",Dienstplan!K234)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L234="","",Dienstplan!L234)</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="49">
         <f>IF(Dienstplan!M234="","",Dienstplan!M234)</f>
         <v/>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="49">
         <f>IF(Dienstplan!N234="","",Dienstplan!N234)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="50">
         <f>IF(Dienstplan!O234="","",Dienstplan!O234)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P234="","",Dienstplan!P234)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q234="","",Dienstplan!Q234)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R234="","",Dienstplan!R234)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S234="","",Dienstplan!S234)</f>
         <v/>
       </c>
-      <c r="T15" s="17">
+      <c r="T15" s="49">
         <f>IF(Dienstplan!T234="","",Dienstplan!T234)</f>
         <v/>
       </c>
-      <c r="U15" s="17">
+      <c r="U15" s="49">
         <f>IF(Dienstplan!U234="","",Dienstplan!U234)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V234="","",Dienstplan!V234)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W234="","",Dienstplan!W234)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X234="","",Dienstplan!X234)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y234="","",Dienstplan!Y234)</f>
         <v/>
       </c>
-      <c r="Z15" s="17">
+      <c r="Z15" s="49">
         <f>IF(Dienstplan!Z234="","",Dienstplan!Z234)</f>
         <v/>
       </c>
-      <c r="AA15" s="17">
+      <c r="AA15" s="49">
         <f>IF(Dienstplan!AA234="","",Dienstplan!AA234)</f>
         <v/>
       </c>
-      <c r="AB15" s="17">
+      <c r="AB15" s="49">
         <f>IF(Dienstplan!AB234="","",Dienstplan!AB234)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC234="","",Dienstplan!AC234)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD234="","",Dienstplan!AD234)</f>
         <v/>
       </c>
-      <c r="AE15" s="21">
+      <c r="AE15" s="50">
         <f>IF(Dienstplan!AE234="","",Dienstplan!AE234)</f>
         <v/>
       </c>
-      <c r="AF15" s="35">
+      <c r="AF15" s="75">
         <f>IF(Dienstplan!AF234="","",Dienstplan!AF234)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -27973,138 +27970,138 @@
         <f>IF(Dienstplan!AE235="","",Dienstplan!AE235)</f>
         <v/>
       </c>
-      <c r="AF16" s="34">
+      <c r="AF16" s="18">
         <f>IF(Dienstplan!AF235="","",Dienstplan!AF235)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="21">
         <f>IF(Dienstplan!B236="","",Dienstplan!B236)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C236="","",Dienstplan!C236)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D236="","",Dienstplan!D236)</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="21">
         <f>IF(Dienstplan!E236="","",Dienstplan!E236)</f>
         <v/>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="17">
         <f>IF(Dienstplan!F236="","",Dienstplan!F236)</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="17">
         <f>IF(Dienstplan!G236="","",Dienstplan!G236)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H236="","",Dienstplan!H236)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I236="","",Dienstplan!I236)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J236="","",Dienstplan!J236)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K236="","",Dienstplan!K236)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L236="","",Dienstplan!L236)</f>
         <v/>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="17">
         <f>IF(Dienstplan!M236="","",Dienstplan!M236)</f>
         <v/>
       </c>
-      <c r="N17" s="50">
+      <c r="N17" s="17">
         <f>IF(Dienstplan!N236="","",Dienstplan!N236)</f>
         <v/>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="21">
         <f>IF(Dienstplan!O236="","",Dienstplan!O236)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P236="","",Dienstplan!P236)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q236="","",Dienstplan!Q236)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R236="","",Dienstplan!R236)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S236="","",Dienstplan!S236)</f>
         <v/>
       </c>
-      <c r="T17" s="50">
+      <c r="T17" s="17">
         <f>IF(Dienstplan!T236="","",Dienstplan!T236)</f>
         <v/>
       </c>
-      <c r="U17" s="50">
+      <c r="U17" s="17">
         <f>IF(Dienstplan!U236="","",Dienstplan!U236)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V236="","",Dienstplan!V236)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W236="","",Dienstplan!W236)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X236="","",Dienstplan!X236)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y236="","",Dienstplan!Y236)</f>
         <v/>
       </c>
-      <c r="Z17" s="50">
+      <c r="Z17" s="17">
         <f>IF(Dienstplan!Z236="","",Dienstplan!Z236)</f>
         <v/>
       </c>
-      <c r="AA17" s="50">
+      <c r="AA17" s="17">
         <f>IF(Dienstplan!AA236="","",Dienstplan!AA236)</f>
         <v/>
       </c>
-      <c r="AB17" s="50">
+      <c r="AB17" s="17">
         <f>IF(Dienstplan!AB236="","",Dienstplan!AB236)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC236="","",Dienstplan!AC236)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD236="","",Dienstplan!AD236)</f>
         <v/>
       </c>
-      <c r="AE17" s="51">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE236="","",Dienstplan!AE236)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="21">
         <f>IF(Dienstplan!AF236="","",Dienstplan!AF236)</f>
         <v/>
       </c>
@@ -28431,35 +28428,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AF17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -30447,12 +30444,12 @@
         <f>U14</f>
         <v/>
       </c>
-      <c r="X14" s="95" t="inlineStr">
+      <c r="X14" s="48" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="Y14" s="96" t="n">
+      <c r="Y14" s="95" t="n">
         <v>8</v>
       </c>
       <c r="AA14" s="89" t="inlineStr">
@@ -30667,92 +30664,92 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="97" t="inlineStr">
+      <c r="A17" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B17" s="98">
+      <c r="B17" s="97">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="98">
+      <c r="C17" s="97">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="98">
+      <c r="D17" s="97">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="98">
+      <c r="E17" s="97">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="98">
+      <c r="F17" s="97">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="98">
+      <c r="G17" s="97">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="98">
+      <c r="H17" s="97">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="98">
+      <c r="I17" s="97">
         <f>SUM(I5:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="98">
+      <c r="J17" s="97">
         <f>SUM(J5:J16)</f>
         <v/>
       </c>
-      <c r="K17" s="98">
+      <c r="K17" s="97">
         <f>SUM(K5:K16)</f>
         <v/>
       </c>
-      <c r="L17" s="98">
+      <c r="L17" s="97">
         <f>SUM(L5:L16)</f>
         <v/>
       </c>
-      <c r="M17" s="98">
+      <c r="M17" s="97">
         <f>SUM(M5:M16)</f>
         <v/>
       </c>
-      <c r="N17" s="98">
+      <c r="N17" s="97">
         <f>SUM(N5:N16)</f>
         <v/>
       </c>
-      <c r="O17" s="98">
+      <c r="O17" s="97">
         <f>SUM(O5:O16)</f>
         <v/>
       </c>
-      <c r="P17" s="98">
+      <c r="P17" s="97">
         <f>SUM(P5:P16)</f>
         <v/>
       </c>
-      <c r="Q17" s="98">
+      <c r="Q17" s="97">
         <f>SUM(Q5:Q16)</f>
         <v/>
       </c>
-      <c r="R17" s="98">
+      <c r="R17" s="97">
         <f>SUM(R5:R16)</f>
         <v/>
       </c>
-      <c r="S17" s="98">
+      <c r="S17" s="97">
         <f>SUM(S5:S16)</f>
         <v/>
       </c>
-      <c r="T17" s="98">
+      <c r="T17" s="97">
         <f>SUM(T5:T16)</f>
         <v/>
       </c>
-      <c r="U17" s="98">
+      <c r="U17" s="97">
         <f>SUM(U5:U16)</f>
         <v/>
       </c>
-      <c r="V17" s="99">
+      <c r="V17" s="98">
         <f>SUM(V5:V16)</f>
         <v/>
       </c>
@@ -30801,12 +30798,12 @@
       <c r="G19" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="AA19" s="100" t="inlineStr">
+      <c r="AA19" s="99" t="inlineStr">
         <is>
           <t>NST</t>
         </is>
       </c>
-      <c r="AB19" s="101" t="inlineStr">
+      <c r="AB19" s="100" t="inlineStr">
         <is>
           <t>IRTAZ</t>
         </is>
@@ -31014,7 +31011,7 @@
         <f>V5+U21</f>
         <v/>
       </c>
-      <c r="X21" s="102" t="inlineStr">
+      <c r="X21" s="101" t="inlineStr">
         <is>
           <t>Soll AZ = IRTAZ × Arbeitstage</t>
         </is>
@@ -31110,7 +31107,7 @@
         <f>V6+U22</f>
         <v/>
       </c>
-      <c r="X22" s="102" t="inlineStr">
+      <c r="X22" s="101" t="inlineStr">
         <is>
           <t>"IRTAZ" = individuelle Tagesarbeitszeit</t>
         </is>
@@ -31206,7 +31203,7 @@
         <f>V7+U23</f>
         <v/>
       </c>
-      <c r="X23" s="102" t="inlineStr">
+      <c r="X23" s="101" t="inlineStr">
         <is>
           <t>Stunden/IRTAZ hier ändern → Formeln aktualisieren sich</t>
         </is>
@@ -32032,92 +32029,92 @@
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="97" t="inlineStr">
+      <c r="A33" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B33" s="98">
+      <c r="B33" s="97">
         <f>SUM(B21:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="98">
+      <c r="C33" s="97">
         <f>SUM(C21:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="98">
+      <c r="D33" s="97">
         <f>SUM(D21:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="98">
+      <c r="E33" s="97">
         <f>SUM(E21:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="98">
+      <c r="F33" s="97">
         <f>SUM(F21:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="98">
+      <c r="G33" s="97">
         <f>SUM(G21:G32)</f>
         <v/>
       </c>
-      <c r="H33" s="98">
+      <c r="H33" s="97">
         <f>SUM(H21:H32)</f>
         <v/>
       </c>
-      <c r="I33" s="98">
+      <c r="I33" s="97">
         <f>SUM(I21:I32)</f>
         <v/>
       </c>
-      <c r="J33" s="98">
+      <c r="J33" s="97">
         <f>SUM(J21:J32)</f>
         <v/>
       </c>
-      <c r="K33" s="98">
+      <c r="K33" s="97">
         <f>SUM(K21:K32)</f>
         <v/>
       </c>
-      <c r="L33" s="98">
+      <c r="L33" s="97">
         <f>SUM(L21:L32)</f>
         <v/>
       </c>
-      <c r="M33" s="98">
+      <c r="M33" s="97">
         <f>SUM(M21:M32)</f>
         <v/>
       </c>
-      <c r="N33" s="98">
+      <c r="N33" s="97">
         <f>SUM(N21:N32)</f>
         <v/>
       </c>
-      <c r="O33" s="98">
+      <c r="O33" s="97">
         <f>SUM(O21:O32)</f>
         <v/>
       </c>
-      <c r="P33" s="98">
+      <c r="P33" s="97">
         <f>SUM(P21:P32)</f>
         <v/>
       </c>
-      <c r="Q33" s="98">
+      <c r="Q33" s="97">
         <f>SUM(Q21:Q32)</f>
         <v/>
       </c>
-      <c r="R33" s="98">
+      <c r="R33" s="97">
         <f>SUM(R21:R32)</f>
         <v/>
       </c>
-      <c r="S33" s="98">
+      <c r="S33" s="97">
         <f>SUM(S21:S32)</f>
         <v/>
       </c>
-      <c r="T33" s="98">
+      <c r="T33" s="97">
         <f>SUM(T21:T32)</f>
         <v/>
       </c>
-      <c r="U33" s="98">
+      <c r="U33" s="97">
         <f>SUM(U21:U32)</f>
         <v/>
       </c>
-      <c r="V33" s="99">
+      <c r="V33" s="98">
         <f>SUM(V21:V32)</f>
         <v/>
       </c>
@@ -33350,92 +33347,92 @@
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="97" t="inlineStr">
+      <c r="A49" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B49" s="98">
+      <c r="B49" s="97">
         <f>SUM(B37:B48)</f>
         <v/>
       </c>
-      <c r="C49" s="98">
+      <c r="C49" s="97">
         <f>SUM(C37:C48)</f>
         <v/>
       </c>
-      <c r="D49" s="98">
+      <c r="D49" s="97">
         <f>SUM(D37:D48)</f>
         <v/>
       </c>
-      <c r="E49" s="98">
+      <c r="E49" s="97">
         <f>SUM(E37:E48)</f>
         <v/>
       </c>
-      <c r="F49" s="98">
+      <c r="F49" s="97">
         <f>SUM(F37:F48)</f>
         <v/>
       </c>
-      <c r="G49" s="98">
+      <c r="G49" s="97">
         <f>SUM(G37:G48)</f>
         <v/>
       </c>
-      <c r="H49" s="98">
+      <c r="H49" s="97">
         <f>SUM(H37:H48)</f>
         <v/>
       </c>
-      <c r="I49" s="98">
+      <c r="I49" s="97">
         <f>SUM(I37:I48)</f>
         <v/>
       </c>
-      <c r="J49" s="98">
+      <c r="J49" s="97">
         <f>SUM(J37:J48)</f>
         <v/>
       </c>
-      <c r="K49" s="98">
+      <c r="K49" s="97">
         <f>SUM(K37:K48)</f>
         <v/>
       </c>
-      <c r="L49" s="98">
+      <c r="L49" s="97">
         <f>SUM(L37:L48)</f>
         <v/>
       </c>
-      <c r="M49" s="98">
+      <c r="M49" s="97">
         <f>SUM(M37:M48)</f>
         <v/>
       </c>
-      <c r="N49" s="98">
+      <c r="N49" s="97">
         <f>SUM(N37:N48)</f>
         <v/>
       </c>
-      <c r="O49" s="98">
+      <c r="O49" s="97">
         <f>SUM(O37:O48)</f>
         <v/>
       </c>
-      <c r="P49" s="98">
+      <c r="P49" s="97">
         <f>SUM(P37:P48)</f>
         <v/>
       </c>
-      <c r="Q49" s="98">
+      <c r="Q49" s="97">
         <f>SUM(Q37:Q48)</f>
         <v/>
       </c>
-      <c r="R49" s="98">
+      <c r="R49" s="97">
         <f>SUM(R37:R48)</f>
         <v/>
       </c>
-      <c r="S49" s="98">
+      <c r="S49" s="97">
         <f>SUM(S37:S48)</f>
         <v/>
       </c>
-      <c r="T49" s="98">
+      <c r="T49" s="97">
         <f>SUM(T37:T48)</f>
         <v/>
       </c>
-      <c r="U49" s="98">
+      <c r="U49" s="97">
         <f>SUM(U37:U48)</f>
         <v/>
       </c>
-      <c r="V49" s="99">
+      <c r="V49" s="98">
         <f>SUM(V37:V48)</f>
         <v/>
       </c>
@@ -34668,92 +34665,92 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="97" t="inlineStr">
+      <c r="A65" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B65" s="98">
+      <c r="B65" s="97">
         <f>SUM(B53:B64)</f>
         <v/>
       </c>
-      <c r="C65" s="98">
+      <c r="C65" s="97">
         <f>SUM(C53:C64)</f>
         <v/>
       </c>
-      <c r="D65" s="98">
+      <c r="D65" s="97">
         <f>SUM(D53:D64)</f>
         <v/>
       </c>
-      <c r="E65" s="98">
+      <c r="E65" s="97">
         <f>SUM(E53:E64)</f>
         <v/>
       </c>
-      <c r="F65" s="98">
+      <c r="F65" s="97">
         <f>SUM(F53:F64)</f>
         <v/>
       </c>
-      <c r="G65" s="98">
+      <c r="G65" s="97">
         <f>SUM(G53:G64)</f>
         <v/>
       </c>
-      <c r="H65" s="98">
+      <c r="H65" s="97">
         <f>SUM(H53:H64)</f>
         <v/>
       </c>
-      <c r="I65" s="98">
+      <c r="I65" s="97">
         <f>SUM(I53:I64)</f>
         <v/>
       </c>
-      <c r="J65" s="98">
+      <c r="J65" s="97">
         <f>SUM(J53:J64)</f>
         <v/>
       </c>
-      <c r="K65" s="98">
+      <c r="K65" s="97">
         <f>SUM(K53:K64)</f>
         <v/>
       </c>
-      <c r="L65" s="98">
+      <c r="L65" s="97">
         <f>SUM(L53:L64)</f>
         <v/>
       </c>
-      <c r="M65" s="98">
+      <c r="M65" s="97">
         <f>SUM(M53:M64)</f>
         <v/>
       </c>
-      <c r="N65" s="98">
+      <c r="N65" s="97">
         <f>SUM(N53:N64)</f>
         <v/>
       </c>
-      <c r="O65" s="98">
+      <c r="O65" s="97">
         <f>SUM(O53:O64)</f>
         <v/>
       </c>
-      <c r="P65" s="98">
+      <c r="P65" s="97">
         <f>SUM(P53:P64)</f>
         <v/>
       </c>
-      <c r="Q65" s="98">
+      <c r="Q65" s="97">
         <f>SUM(Q53:Q64)</f>
         <v/>
       </c>
-      <c r="R65" s="98">
+      <c r="R65" s="97">
         <f>SUM(R53:R64)</f>
         <v/>
       </c>
-      <c r="S65" s="98">
+      <c r="S65" s="97">
         <f>SUM(S53:S64)</f>
         <v/>
       </c>
-      <c r="T65" s="98">
+      <c r="T65" s="97">
         <f>SUM(T53:T64)</f>
         <v/>
       </c>
-      <c r="U65" s="98">
+      <c r="U65" s="97">
         <f>SUM(U53:U64)</f>
         <v/>
       </c>
-      <c r="V65" s="99">
+      <c r="V65" s="98">
         <f>SUM(V53:V64)</f>
         <v/>
       </c>
@@ -35986,92 +35983,92 @@
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="97" t="inlineStr">
+      <c r="A81" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B81" s="98">
+      <c r="B81" s="97">
         <f>SUM(B69:B80)</f>
         <v/>
       </c>
-      <c r="C81" s="98">
+      <c r="C81" s="97">
         <f>SUM(C69:C80)</f>
         <v/>
       </c>
-      <c r="D81" s="98">
+      <c r="D81" s="97">
         <f>SUM(D69:D80)</f>
         <v/>
       </c>
-      <c r="E81" s="98">
+      <c r="E81" s="97">
         <f>SUM(E69:E80)</f>
         <v/>
       </c>
-      <c r="F81" s="98">
+      <c r="F81" s="97">
         <f>SUM(F69:F80)</f>
         <v/>
       </c>
-      <c r="G81" s="98">
+      <c r="G81" s="97">
         <f>SUM(G69:G80)</f>
         <v/>
       </c>
-      <c r="H81" s="98">
+      <c r="H81" s="97">
         <f>SUM(H69:H80)</f>
         <v/>
       </c>
-      <c r="I81" s="98">
+      <c r="I81" s="97">
         <f>SUM(I69:I80)</f>
         <v/>
       </c>
-      <c r="J81" s="98">
+      <c r="J81" s="97">
         <f>SUM(J69:J80)</f>
         <v/>
       </c>
-      <c r="K81" s="98">
+      <c r="K81" s="97">
         <f>SUM(K69:K80)</f>
         <v/>
       </c>
-      <c r="L81" s="98">
+      <c r="L81" s="97">
         <f>SUM(L69:L80)</f>
         <v/>
       </c>
-      <c r="M81" s="98">
+      <c r="M81" s="97">
         <f>SUM(M69:M80)</f>
         <v/>
       </c>
-      <c r="N81" s="98">
+      <c r="N81" s="97">
         <f>SUM(N69:N80)</f>
         <v/>
       </c>
-      <c r="O81" s="98">
+      <c r="O81" s="97">
         <f>SUM(O69:O80)</f>
         <v/>
       </c>
-      <c r="P81" s="98">
+      <c r="P81" s="97">
         <f>SUM(P69:P80)</f>
         <v/>
       </c>
-      <c r="Q81" s="98">
+      <c r="Q81" s="97">
         <f>SUM(Q69:Q80)</f>
         <v/>
       </c>
-      <c r="R81" s="98">
+      <c r="R81" s="97">
         <f>SUM(R69:R80)</f>
         <v/>
       </c>
-      <c r="S81" s="98">
+      <c r="S81" s="97">
         <f>SUM(S69:S80)</f>
         <v/>
       </c>
-      <c r="T81" s="98">
+      <c r="T81" s="97">
         <f>SUM(T69:T80)</f>
         <v/>
       </c>
-      <c r="U81" s="98">
+      <c r="U81" s="97">
         <f>SUM(U69:U80)</f>
         <v/>
       </c>
-      <c r="V81" s="99">
+      <c r="V81" s="98">
         <f>SUM(V69:V80)</f>
         <v/>
       </c>
@@ -37304,92 +37301,92 @@
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="97" t="inlineStr">
+      <c r="A97" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B97" s="98">
+      <c r="B97" s="97">
         <f>SUM(B85:B96)</f>
         <v/>
       </c>
-      <c r="C97" s="98">
+      <c r="C97" s="97">
         <f>SUM(C85:C96)</f>
         <v/>
       </c>
-      <c r="D97" s="98">
+      <c r="D97" s="97">
         <f>SUM(D85:D96)</f>
         <v/>
       </c>
-      <c r="E97" s="98">
+      <c r="E97" s="97">
         <f>SUM(E85:E96)</f>
         <v/>
       </c>
-      <c r="F97" s="98">
+      <c r="F97" s="97">
         <f>SUM(F85:F96)</f>
         <v/>
       </c>
-      <c r="G97" s="98">
+      <c r="G97" s="97">
         <f>SUM(G85:G96)</f>
         <v/>
       </c>
-      <c r="H97" s="98">
+      <c r="H97" s="97">
         <f>SUM(H85:H96)</f>
         <v/>
       </c>
-      <c r="I97" s="98">
+      <c r="I97" s="97">
         <f>SUM(I85:I96)</f>
         <v/>
       </c>
-      <c r="J97" s="98">
+      <c r="J97" s="97">
         <f>SUM(J85:J96)</f>
         <v/>
       </c>
-      <c r="K97" s="98">
+      <c r="K97" s="97">
         <f>SUM(K85:K96)</f>
         <v/>
       </c>
-      <c r="L97" s="98">
+      <c r="L97" s="97">
         <f>SUM(L85:L96)</f>
         <v/>
       </c>
-      <c r="M97" s="98">
+      <c r="M97" s="97">
         <f>SUM(M85:M96)</f>
         <v/>
       </c>
-      <c r="N97" s="98">
+      <c r="N97" s="97">
         <f>SUM(N85:N96)</f>
         <v/>
       </c>
-      <c r="O97" s="98">
+      <c r="O97" s="97">
         <f>SUM(O85:O96)</f>
         <v/>
       </c>
-      <c r="P97" s="98">
+      <c r="P97" s="97">
         <f>SUM(P85:P96)</f>
         <v/>
       </c>
-      <c r="Q97" s="98">
+      <c r="Q97" s="97">
         <f>SUM(Q85:Q96)</f>
         <v/>
       </c>
-      <c r="R97" s="98">
+      <c r="R97" s="97">
         <f>SUM(R85:R96)</f>
         <v/>
       </c>
-      <c r="S97" s="98">
+      <c r="S97" s="97">
         <f>SUM(S85:S96)</f>
         <v/>
       </c>
-      <c r="T97" s="98">
+      <c r="T97" s="97">
         <f>SUM(T85:T96)</f>
         <v/>
       </c>
-      <c r="U97" s="98">
+      <c r="U97" s="97">
         <f>SUM(U85:U96)</f>
         <v/>
       </c>
-      <c r="V97" s="99">
+      <c r="V97" s="98">
         <f>SUM(V85:V96)</f>
         <v/>
       </c>
@@ -38622,92 +38619,92 @@
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="97" t="inlineStr">
+      <c r="A113" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B113" s="98">
+      <c r="B113" s="97">
         <f>SUM(B101:B112)</f>
         <v/>
       </c>
-      <c r="C113" s="98">
+      <c r="C113" s="97">
         <f>SUM(C101:C112)</f>
         <v/>
       </c>
-      <c r="D113" s="98">
+      <c r="D113" s="97">
         <f>SUM(D101:D112)</f>
         <v/>
       </c>
-      <c r="E113" s="98">
+      <c r="E113" s="97">
         <f>SUM(E101:E112)</f>
         <v/>
       </c>
-      <c r="F113" s="98">
+      <c r="F113" s="97">
         <f>SUM(F101:F112)</f>
         <v/>
       </c>
-      <c r="G113" s="98">
+      <c r="G113" s="97">
         <f>SUM(G101:G112)</f>
         <v/>
       </c>
-      <c r="H113" s="98">
+      <c r="H113" s="97">
         <f>SUM(H101:H112)</f>
         <v/>
       </c>
-      <c r="I113" s="98">
+      <c r="I113" s="97">
         <f>SUM(I101:I112)</f>
         <v/>
       </c>
-      <c r="J113" s="98">
+      <c r="J113" s="97">
         <f>SUM(J101:J112)</f>
         <v/>
       </c>
-      <c r="K113" s="98">
+      <c r="K113" s="97">
         <f>SUM(K101:K112)</f>
         <v/>
       </c>
-      <c r="L113" s="98">
+      <c r="L113" s="97">
         <f>SUM(L101:L112)</f>
         <v/>
       </c>
-      <c r="M113" s="98">
+      <c r="M113" s="97">
         <f>SUM(M101:M112)</f>
         <v/>
       </c>
-      <c r="N113" s="98">
+      <c r="N113" s="97">
         <f>SUM(N101:N112)</f>
         <v/>
       </c>
-      <c r="O113" s="98">
+      <c r="O113" s="97">
         <f>SUM(O101:O112)</f>
         <v/>
       </c>
-      <c r="P113" s="98">
+      <c r="P113" s="97">
         <f>SUM(P101:P112)</f>
         <v/>
       </c>
-      <c r="Q113" s="98">
+      <c r="Q113" s="97">
         <f>SUM(Q101:Q112)</f>
         <v/>
       </c>
-      <c r="R113" s="98">
+      <c r="R113" s="97">
         <f>SUM(R101:R112)</f>
         <v/>
       </c>
-      <c r="S113" s="98">
+      <c r="S113" s="97">
         <f>SUM(S101:S112)</f>
         <v/>
       </c>
-      <c r="T113" s="98">
+      <c r="T113" s="97">
         <f>SUM(T101:T112)</f>
         <v/>
       </c>
-      <c r="U113" s="98">
+      <c r="U113" s="97">
         <f>SUM(U101:U112)</f>
         <v/>
       </c>
-      <c r="V113" s="99">
+      <c r="V113" s="98">
         <f>SUM(V101:V112)</f>
         <v/>
       </c>
@@ -39940,92 +39937,92 @@
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="97" t="inlineStr">
+      <c r="A129" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B129" s="98">
+      <c r="B129" s="97">
         <f>SUM(B117:B128)</f>
         <v/>
       </c>
-      <c r="C129" s="98">
+      <c r="C129" s="97">
         <f>SUM(C117:C128)</f>
         <v/>
       </c>
-      <c r="D129" s="98">
+      <c r="D129" s="97">
         <f>SUM(D117:D128)</f>
         <v/>
       </c>
-      <c r="E129" s="98">
+      <c r="E129" s="97">
         <f>SUM(E117:E128)</f>
         <v/>
       </c>
-      <c r="F129" s="98">
+      <c r="F129" s="97">
         <f>SUM(F117:F128)</f>
         <v/>
       </c>
-      <c r="G129" s="98">
+      <c r="G129" s="97">
         <f>SUM(G117:G128)</f>
         <v/>
       </c>
-      <c r="H129" s="98">
+      <c r="H129" s="97">
         <f>SUM(H117:H128)</f>
         <v/>
       </c>
-      <c r="I129" s="98">
+      <c r="I129" s="97">
         <f>SUM(I117:I128)</f>
         <v/>
       </c>
-      <c r="J129" s="98">
+      <c r="J129" s="97">
         <f>SUM(J117:J128)</f>
         <v/>
       </c>
-      <c r="K129" s="98">
+      <c r="K129" s="97">
         <f>SUM(K117:K128)</f>
         <v/>
       </c>
-      <c r="L129" s="98">
+      <c r="L129" s="97">
         <f>SUM(L117:L128)</f>
         <v/>
       </c>
-      <c r="M129" s="98">
+      <c r="M129" s="97">
         <f>SUM(M117:M128)</f>
         <v/>
       </c>
-      <c r="N129" s="98">
+      <c r="N129" s="97">
         <f>SUM(N117:N128)</f>
         <v/>
       </c>
-      <c r="O129" s="98">
+      <c r="O129" s="97">
         <f>SUM(O117:O128)</f>
         <v/>
       </c>
-      <c r="P129" s="98">
+      <c r="P129" s="97">
         <f>SUM(P117:P128)</f>
         <v/>
       </c>
-      <c r="Q129" s="98">
+      <c r="Q129" s="97">
         <f>SUM(Q117:Q128)</f>
         <v/>
       </c>
-      <c r="R129" s="98">
+      <c r="R129" s="97">
         <f>SUM(R117:R128)</f>
         <v/>
       </c>
-      <c r="S129" s="98">
+      <c r="S129" s="97">
         <f>SUM(S117:S128)</f>
         <v/>
       </c>
-      <c r="T129" s="98">
+      <c r="T129" s="97">
         <f>SUM(T117:T128)</f>
         <v/>
       </c>
-      <c r="U129" s="98">
+      <c r="U129" s="97">
         <f>SUM(U117:U128)</f>
         <v/>
       </c>
-      <c r="V129" s="99">
+      <c r="V129" s="98">
         <f>SUM(V117:V128)</f>
         <v/>
       </c>
@@ -41258,92 +41255,92 @@
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="97" t="inlineStr">
+      <c r="A145" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B145" s="98">
+      <c r="B145" s="97">
         <f>SUM(B133:B144)</f>
         <v/>
       </c>
-      <c r="C145" s="98">
+      <c r="C145" s="97">
         <f>SUM(C133:C144)</f>
         <v/>
       </c>
-      <c r="D145" s="98">
+      <c r="D145" s="97">
         <f>SUM(D133:D144)</f>
         <v/>
       </c>
-      <c r="E145" s="98">
+      <c r="E145" s="97">
         <f>SUM(E133:E144)</f>
         <v/>
       </c>
-      <c r="F145" s="98">
+      <c r="F145" s="97">
         <f>SUM(F133:F144)</f>
         <v/>
       </c>
-      <c r="G145" s="98">
+      <c r="G145" s="97">
         <f>SUM(G133:G144)</f>
         <v/>
       </c>
-      <c r="H145" s="98">
+      <c r="H145" s="97">
         <f>SUM(H133:H144)</f>
         <v/>
       </c>
-      <c r="I145" s="98">
+      <c r="I145" s="97">
         <f>SUM(I133:I144)</f>
         <v/>
       </c>
-      <c r="J145" s="98">
+      <c r="J145" s="97">
         <f>SUM(J133:J144)</f>
         <v/>
       </c>
-      <c r="K145" s="98">
+      <c r="K145" s="97">
         <f>SUM(K133:K144)</f>
         <v/>
       </c>
-      <c r="L145" s="98">
+      <c r="L145" s="97">
         <f>SUM(L133:L144)</f>
         <v/>
       </c>
-      <c r="M145" s="98">
+      <c r="M145" s="97">
         <f>SUM(M133:M144)</f>
         <v/>
       </c>
-      <c r="N145" s="98">
+      <c r="N145" s="97">
         <f>SUM(N133:N144)</f>
         <v/>
       </c>
-      <c r="O145" s="98">
+      <c r="O145" s="97">
         <f>SUM(O133:O144)</f>
         <v/>
       </c>
-      <c r="P145" s="98">
+      <c r="P145" s="97">
         <f>SUM(P133:P144)</f>
         <v/>
       </c>
-      <c r="Q145" s="98">
+      <c r="Q145" s="97">
         <f>SUM(Q133:Q144)</f>
         <v/>
       </c>
-      <c r="R145" s="98">
+      <c r="R145" s="97">
         <f>SUM(R133:R144)</f>
         <v/>
       </c>
-      <c r="S145" s="98">
+      <c r="S145" s="97">
         <f>SUM(S133:S144)</f>
         <v/>
       </c>
-      <c r="T145" s="98">
+      <c r="T145" s="97">
         <f>SUM(T133:T144)</f>
         <v/>
       </c>
-      <c r="U145" s="98">
+      <c r="U145" s="97">
         <f>SUM(U133:U144)</f>
         <v/>
       </c>
-      <c r="V145" s="99">
+      <c r="V145" s="98">
         <f>SUM(V133:V144)</f>
         <v/>
       </c>
@@ -42576,92 +42573,92 @@
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="97" t="inlineStr">
+      <c r="A161" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B161" s="98">
+      <c r="B161" s="97">
         <f>SUM(B149:B160)</f>
         <v/>
       </c>
-      <c r="C161" s="98">
+      <c r="C161" s="97">
         <f>SUM(C149:C160)</f>
         <v/>
       </c>
-      <c r="D161" s="98">
+      <c r="D161" s="97">
         <f>SUM(D149:D160)</f>
         <v/>
       </c>
-      <c r="E161" s="98">
+      <c r="E161" s="97">
         <f>SUM(E149:E160)</f>
         <v/>
       </c>
-      <c r="F161" s="98">
+      <c r="F161" s="97">
         <f>SUM(F149:F160)</f>
         <v/>
       </c>
-      <c r="G161" s="98">
+      <c r="G161" s="97">
         <f>SUM(G149:G160)</f>
         <v/>
       </c>
-      <c r="H161" s="98">
+      <c r="H161" s="97">
         <f>SUM(H149:H160)</f>
         <v/>
       </c>
-      <c r="I161" s="98">
+      <c r="I161" s="97">
         <f>SUM(I149:I160)</f>
         <v/>
       </c>
-      <c r="J161" s="98">
+      <c r="J161" s="97">
         <f>SUM(J149:J160)</f>
         <v/>
       </c>
-      <c r="K161" s="98">
+      <c r="K161" s="97">
         <f>SUM(K149:K160)</f>
         <v/>
       </c>
-      <c r="L161" s="98">
+      <c r="L161" s="97">
         <f>SUM(L149:L160)</f>
         <v/>
       </c>
-      <c r="M161" s="98">
+      <c r="M161" s="97">
         <f>SUM(M149:M160)</f>
         <v/>
       </c>
-      <c r="N161" s="98">
+      <c r="N161" s="97">
         <f>SUM(N149:N160)</f>
         <v/>
       </c>
-      <c r="O161" s="98">
+      <c r="O161" s="97">
         <f>SUM(O149:O160)</f>
         <v/>
       </c>
-      <c r="P161" s="98">
+      <c r="P161" s="97">
         <f>SUM(P149:P160)</f>
         <v/>
       </c>
-      <c r="Q161" s="98">
+      <c r="Q161" s="97">
         <f>SUM(Q149:Q160)</f>
         <v/>
       </c>
-      <c r="R161" s="98">
+      <c r="R161" s="97">
         <f>SUM(R149:R160)</f>
         <v/>
       </c>
-      <c r="S161" s="98">
+      <c r="S161" s="97">
         <f>SUM(S149:S160)</f>
         <v/>
       </c>
-      <c r="T161" s="98">
+      <c r="T161" s="97">
         <f>SUM(T149:T160)</f>
         <v/>
       </c>
-      <c r="U161" s="98">
+      <c r="U161" s="97">
         <f>SUM(U149:U160)</f>
         <v/>
       </c>
-      <c r="V161" s="99">
+      <c r="V161" s="98">
         <f>SUM(V149:V160)</f>
         <v/>
       </c>
@@ -43894,92 +43891,92 @@
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="97" t="inlineStr">
+      <c r="A177" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B177" s="98">
+      <c r="B177" s="97">
         <f>SUM(B165:B176)</f>
         <v/>
       </c>
-      <c r="C177" s="98">
+      <c r="C177" s="97">
         <f>SUM(C165:C176)</f>
         <v/>
       </c>
-      <c r="D177" s="98">
+      <c r="D177" s="97">
         <f>SUM(D165:D176)</f>
         <v/>
       </c>
-      <c r="E177" s="98">
+      <c r="E177" s="97">
         <f>SUM(E165:E176)</f>
         <v/>
       </c>
-      <c r="F177" s="98">
+      <c r="F177" s="97">
         <f>SUM(F165:F176)</f>
         <v/>
       </c>
-      <c r="G177" s="98">
+      <c r="G177" s="97">
         <f>SUM(G165:G176)</f>
         <v/>
       </c>
-      <c r="H177" s="98">
+      <c r="H177" s="97">
         <f>SUM(H165:H176)</f>
         <v/>
       </c>
-      <c r="I177" s="98">
+      <c r="I177" s="97">
         <f>SUM(I165:I176)</f>
         <v/>
       </c>
-      <c r="J177" s="98">
+      <c r="J177" s="97">
         <f>SUM(J165:J176)</f>
         <v/>
       </c>
-      <c r="K177" s="98">
+      <c r="K177" s="97">
         <f>SUM(K165:K176)</f>
         <v/>
       </c>
-      <c r="L177" s="98">
+      <c r="L177" s="97">
         <f>SUM(L165:L176)</f>
         <v/>
       </c>
-      <c r="M177" s="98">
+      <c r="M177" s="97">
         <f>SUM(M165:M176)</f>
         <v/>
       </c>
-      <c r="N177" s="98">
+      <c r="N177" s="97">
         <f>SUM(N165:N176)</f>
         <v/>
       </c>
-      <c r="O177" s="98">
+      <c r="O177" s="97">
         <f>SUM(O165:O176)</f>
         <v/>
       </c>
-      <c r="P177" s="98">
+      <c r="P177" s="97">
         <f>SUM(P165:P176)</f>
         <v/>
       </c>
-      <c r="Q177" s="98">
+      <c r="Q177" s="97">
         <f>SUM(Q165:Q176)</f>
         <v/>
       </c>
-      <c r="R177" s="98">
+      <c r="R177" s="97">
         <f>SUM(R165:R176)</f>
         <v/>
       </c>
-      <c r="S177" s="98">
+      <c r="S177" s="97">
         <f>SUM(S165:S176)</f>
         <v/>
       </c>
-      <c r="T177" s="98">
+      <c r="T177" s="97">
         <f>SUM(T165:T176)</f>
         <v/>
       </c>
-      <c r="U177" s="98">
+      <c r="U177" s="97">
         <f>SUM(U165:U176)</f>
         <v/>
       </c>
-      <c r="V177" s="99">
+      <c r="V177" s="98">
         <f>SUM(V165:V176)</f>
         <v/>
       </c>
@@ -45212,92 +45209,92 @@
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="A193" s="97" t="inlineStr">
+      <c r="A193" s="96" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B193" s="98">
+      <c r="B193" s="97">
         <f>SUM(B181:B192)</f>
         <v/>
       </c>
-      <c r="C193" s="98">
+      <c r="C193" s="97">
         <f>SUM(C181:C192)</f>
         <v/>
       </c>
-      <c r="D193" s="98">
+      <c r="D193" s="97">
         <f>SUM(D181:D192)</f>
         <v/>
       </c>
-      <c r="E193" s="98">
+      <c r="E193" s="97">
         <f>SUM(E181:E192)</f>
         <v/>
       </c>
-      <c r="F193" s="98">
+      <c r="F193" s="97">
         <f>SUM(F181:F192)</f>
         <v/>
       </c>
-      <c r="G193" s="98">
+      <c r="G193" s="97">
         <f>SUM(G181:G192)</f>
         <v/>
       </c>
-      <c r="H193" s="98">
+      <c r="H193" s="97">
         <f>SUM(H181:H192)</f>
         <v/>
       </c>
-      <c r="I193" s="98">
+      <c r="I193" s="97">
         <f>SUM(I181:I192)</f>
         <v/>
       </c>
-      <c r="J193" s="98">
+      <c r="J193" s="97">
         <f>SUM(J181:J192)</f>
         <v/>
       </c>
-      <c r="K193" s="98">
+      <c r="K193" s="97">
         <f>SUM(K181:K192)</f>
         <v/>
       </c>
-      <c r="L193" s="98">
+      <c r="L193" s="97">
         <f>SUM(L181:L192)</f>
         <v/>
       </c>
-      <c r="M193" s="98">
+      <c r="M193" s="97">
         <f>SUM(M181:M192)</f>
         <v/>
       </c>
-      <c r="N193" s="98">
+      <c r="N193" s="97">
         <f>SUM(N181:N192)</f>
         <v/>
       </c>
-      <c r="O193" s="98">
+      <c r="O193" s="97">
         <f>SUM(O181:O192)</f>
         <v/>
       </c>
-      <c r="P193" s="98">
+      <c r="P193" s="97">
         <f>SUM(P181:P192)</f>
         <v/>
       </c>
-      <c r="Q193" s="98">
+      <c r="Q193" s="97">
         <f>SUM(Q181:Q192)</f>
         <v/>
       </c>
-      <c r="R193" s="98">
+      <c r="R193" s="97">
         <f>SUM(R181:R192)</f>
         <v/>
       </c>
-      <c r="S193" s="98">
+      <c r="S193" s="97">
         <f>SUM(S181:S192)</f>
         <v/>
       </c>
-      <c r="T193" s="98">
+      <c r="T193" s="97">
         <f>SUM(T181:T192)</f>
         <v/>
       </c>
-      <c r="U193" s="98">
+      <c r="U193" s="97">
         <f>SUM(U181:U192)</f>
         <v/>
       </c>
-      <c r="V193" s="99">
+      <c r="V193" s="98">
         <f>SUM(V181:V192)</f>
         <v/>
       </c>
@@ -45671,7 +45668,7 @@
         <f>COUNTIF(Dienstplan!B225:AF225,"U")+COUNTIF(Dienstplan!B225:AF225,"U    alt")</f>
         <v/>
       </c>
-      <c r="N4" s="103">
+      <c r="N4" s="102">
         <f>SUM(B4:M4)</f>
         <v/>
       </c>
@@ -45737,7 +45734,7 @@
         <f>COUNTIF(Dienstplan!B226:AF226,"U")+COUNTIF(Dienstplan!B226:AF226,"U    alt")</f>
         <v/>
       </c>
-      <c r="N5" s="104">
+      <c r="N5" s="103">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
@@ -45803,7 +45800,7 @@
         <f>COUNTIF(Dienstplan!B227:AF227,"U")+COUNTIF(Dienstplan!B227:AF227,"U    alt")</f>
         <v/>
       </c>
-      <c r="N6" s="103">
+      <c r="N6" s="102">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -45869,7 +45866,7 @@
         <f>COUNTIF(Dienstplan!B228:AF228,"U")+COUNTIF(Dienstplan!B228:AF228,"U    alt")</f>
         <v/>
       </c>
-      <c r="N7" s="104">
+      <c r="N7" s="103">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -45935,7 +45932,7 @@
         <f>COUNTIF(Dienstplan!B229:AF229,"U")+COUNTIF(Dienstplan!B229:AF229,"U    alt")</f>
         <v/>
       </c>
-      <c r="N8" s="103">
+      <c r="N8" s="102">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -46001,7 +45998,7 @@
         <f>COUNTIF(Dienstplan!B230:AF230,"U")+COUNTIF(Dienstplan!B230:AF230,"U    alt")</f>
         <v/>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="103">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -46067,7 +46064,7 @@
         <f>COUNTIF(Dienstplan!B231:AF231,"U")+COUNTIF(Dienstplan!B231:AF231,"U    alt")</f>
         <v/>
       </c>
-      <c r="N10" s="103">
+      <c r="N10" s="102">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -46133,7 +46130,7 @@
         <f>COUNTIF(Dienstplan!B232:AF232,"U")+COUNTIF(Dienstplan!B232:AF232,"U    alt")</f>
         <v/>
       </c>
-      <c r="N11" s="104">
+      <c r="N11" s="103">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -46199,7 +46196,7 @@
         <f>COUNTIF(Dienstplan!B233:AF233,"U")+COUNTIF(Dienstplan!B233:AF233,"U    alt")</f>
         <v/>
       </c>
-      <c r="N12" s="103">
+      <c r="N12" s="102">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -46265,7 +46262,7 @@
         <f>COUNTIF(Dienstplan!B234:AF234,"U")+COUNTIF(Dienstplan!B234:AF234,"U    alt")</f>
         <v/>
       </c>
-      <c r="N13" s="104">
+      <c r="N13" s="103">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -46331,7 +46328,7 @@
         <f>COUNTIF(Dienstplan!B235:AF235,"U")+COUNTIF(Dienstplan!B235:AF235,"U    alt")</f>
         <v/>
       </c>
-      <c r="N14" s="103">
+      <c r="N14" s="102">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -46397,7 +46394,7 @@
         <f>COUNTIF(Dienstplan!B236:AF236,"U")+COUNTIF(Dienstplan!B236:AF236,"U    alt")</f>
         <v/>
       </c>
-      <c r="N15" s="104">
+      <c r="N15" s="103">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
@@ -46467,11 +46464,11 @@
         <f>SUM(N4:N15)</f>
         <v/>
       </c>
-      <c r="O16" s="105" t="n"/>
-      <c r="P16" s="106" t="n"/>
+      <c r="O16" s="104" t="n"/>
+      <c r="P16" s="105" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="107" t="inlineStr">
+      <c r="A18" s="106" t="inlineStr">
         <is>
           <t>Anspruch: 30 Tage/Jahr (anpassbar in Spalte O)</t>
         </is>
@@ -48039,138 +48036,138 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="49">
         <f>IF(Dienstplan!B16="","",Dienstplan!B16)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C16="","",Dienstplan!C16)</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="49">
         <f>IF(Dienstplan!D16="","",Dienstplan!D16)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="49">
         <f>IF(Dienstplan!E16="","",Dienstplan!E16)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F16="","",Dienstplan!F16)</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="49">
         <f>IF(Dienstplan!G16="","",Dienstplan!G16)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H16="","",Dienstplan!H16)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I16="","",Dienstplan!I16)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J16="","",Dienstplan!J16)</f>
         <v/>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="49">
         <f>IF(Dienstplan!K16="","",Dienstplan!K16)</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="49">
         <f>IF(Dienstplan!L16="","",Dienstplan!L16)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M16="","",Dienstplan!M16)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N16="","",Dienstplan!N16)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="50">
         <f>IF(Dienstplan!O16="","",Dienstplan!O16)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P16="","",Dienstplan!P16)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q16="","",Dienstplan!Q16)</f>
         <v/>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="49">
         <f>IF(Dienstplan!R16="","",Dienstplan!R16)</f>
         <v/>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="49">
         <f>IF(Dienstplan!S16="","",Dienstplan!S16)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T16="","",Dienstplan!T16)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U16="","",Dienstplan!U16)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V16="","",Dienstplan!V16)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W16="","",Dienstplan!W16)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X16="","",Dienstplan!X16)</f>
         <v/>
       </c>
-      <c r="Y15" s="17">
+      <c r="Y15" s="49">
         <f>IF(Dienstplan!Y16="","",Dienstplan!Y16)</f>
         <v/>
       </c>
-      <c r="Z15" s="17">
+      <c r="Z15" s="49">
         <f>IF(Dienstplan!Z16="","",Dienstplan!Z16)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA16="","",Dienstplan!AA16)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB16="","",Dienstplan!AB16)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC16="","",Dienstplan!AC16)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD16="","",Dienstplan!AD16)</f>
         <v/>
       </c>
-      <c r="AE15" s="21">
+      <c r="AE15" s="50">
         <f>IF(Dienstplan!AE16="","",Dienstplan!AE16)</f>
         <v/>
       </c>
-      <c r="AF15" s="19">
+      <c r="AF15" s="51">
         <f>IF(Dienstplan!AF16="","",Dienstplan!AF16)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -48295,138 +48292,138 @@
         <f>IF(Dienstplan!AE17="","",Dienstplan!AE17)</f>
         <v/>
       </c>
-      <c r="AF16" s="19">
+      <c r="AF16" s="17">
         <f>IF(Dienstplan!AF17="","",Dienstplan!AF17)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="17">
         <f>IF(Dienstplan!B18="","",Dienstplan!B18)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C18="","",Dienstplan!C18)</f>
         <v/>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="17">
         <f>IF(Dienstplan!D18="","",Dienstplan!D18)</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="17">
         <f>IF(Dienstplan!E18="","",Dienstplan!E18)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F18="","",Dienstplan!F18)</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="17">
         <f>IF(Dienstplan!G18="","",Dienstplan!G18)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H18="","",Dienstplan!H18)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I18="","",Dienstplan!I18)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J18="","",Dienstplan!J18)</f>
         <v/>
       </c>
-      <c r="K17" s="50">
+      <c r="K17" s="17">
         <f>IF(Dienstplan!K18="","",Dienstplan!K18)</f>
         <v/>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="17">
         <f>IF(Dienstplan!L18="","",Dienstplan!L18)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M18="","",Dienstplan!M18)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N18="","",Dienstplan!N18)</f>
         <v/>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="21">
         <f>IF(Dienstplan!O18="","",Dienstplan!O18)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P18="","",Dienstplan!P18)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q18="","",Dienstplan!Q18)</f>
         <v/>
       </c>
-      <c r="R17" s="50">
+      <c r="R17" s="17">
         <f>IF(Dienstplan!R18="","",Dienstplan!R18)</f>
         <v/>
       </c>
-      <c r="S17" s="50">
+      <c r="S17" s="17">
         <f>IF(Dienstplan!S18="","",Dienstplan!S18)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T18="","",Dienstplan!T18)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U18="","",Dienstplan!U18)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V18="","",Dienstplan!V18)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W18="","",Dienstplan!W18)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X18="","",Dienstplan!X18)</f>
         <v/>
       </c>
-      <c r="Y17" s="50">
+      <c r="Y17" s="17">
         <f>IF(Dienstplan!Y18="","",Dienstplan!Y18)</f>
         <v/>
       </c>
-      <c r="Z17" s="50">
+      <c r="Z17" s="17">
         <f>IF(Dienstplan!Z18="","",Dienstplan!Z18)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA18="","",Dienstplan!AA18)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB18="","",Dienstplan!AB18)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC18="","",Dienstplan!AC18)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD18="","",Dienstplan!AD18)</f>
         <v/>
       </c>
-      <c r="AE17" s="51">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE18="","",Dienstplan!AE18)</f>
         <v/>
       </c>
-      <c r="AF17" s="52">
+      <c r="AF17" s="17">
         <f>IF(Dienstplan!AF18="","",Dienstplan!AF18)</f>
         <v/>
       </c>
@@ -48752,35 +48749,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AF17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -50203,126 +50200,126 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="49">
         <f>IF(Dienstplan!B36="","",Dienstplan!B36)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C36="","",Dienstplan!C36)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D36="","",Dienstplan!D36)</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="50">
         <f>IF(Dienstplan!E36="","",Dienstplan!E36)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F36="","",Dienstplan!F36)</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="50">
         <f>IF(Dienstplan!G36="","",Dienstplan!G36)</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="49">
         <f>IF(Dienstplan!H36="","",Dienstplan!H36)</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="49">
         <f>IF(Dienstplan!I36="","",Dienstplan!I36)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J36="","",Dienstplan!J36)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K36="","",Dienstplan!K36)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L36="","",Dienstplan!L36)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M36="","",Dienstplan!M36)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N36="","",Dienstplan!N36)</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="49">
         <f>IF(Dienstplan!O36="","",Dienstplan!O36)</f>
         <v/>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="49">
         <f>IF(Dienstplan!P36="","",Dienstplan!P36)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q36="","",Dienstplan!Q36)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R36="","",Dienstplan!R36)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S36="","",Dienstplan!S36)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T36="","",Dienstplan!T36)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U36="","",Dienstplan!U36)</f>
         <v/>
       </c>
-      <c r="V15" s="17">
+      <c r="V15" s="49">
         <f>IF(Dienstplan!V36="","",Dienstplan!V36)</f>
         <v/>
       </c>
-      <c r="W15" s="17">
+      <c r="W15" s="49">
         <f>IF(Dienstplan!W36="","",Dienstplan!W36)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X36="","",Dienstplan!X36)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y36="","",Dienstplan!Y36)</f>
         <v/>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="50">
         <f>IF(Dienstplan!Z36="","",Dienstplan!Z36)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA36="","",Dienstplan!AA36)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB36="","",Dienstplan!AB36)</f>
         <v/>
       </c>
-      <c r="AC15" s="19">
+      <c r="AC15" s="51">
         <f>IF(Dienstplan!AC36="","",Dienstplan!AC36)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -50435,126 +50432,126 @@
         <f>IF(Dienstplan!AB37="","",Dienstplan!AB37)</f>
         <v/>
       </c>
-      <c r="AC16" s="19">
+      <c r="AC16" s="17">
         <f>IF(Dienstplan!AC37="","",Dienstplan!AC37)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="17">
         <f>IF(Dienstplan!B38="","",Dienstplan!B38)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C38="","",Dienstplan!C38)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D38="","",Dienstplan!D38)</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="21">
         <f>IF(Dienstplan!E38="","",Dienstplan!E38)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F38="","",Dienstplan!F38)</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="21">
         <f>IF(Dienstplan!G38="","",Dienstplan!G38)</f>
         <v/>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="17">
         <f>IF(Dienstplan!H38="","",Dienstplan!H38)</f>
         <v/>
       </c>
-      <c r="I17" s="50">
+      <c r="I17" s="17">
         <f>IF(Dienstplan!I38="","",Dienstplan!I38)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J38="","",Dienstplan!J38)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K38="","",Dienstplan!K38)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L38="","",Dienstplan!L38)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M38="","",Dienstplan!M38)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N38="","",Dienstplan!N38)</f>
         <v/>
       </c>
-      <c r="O17" s="50">
+      <c r="O17" s="17">
         <f>IF(Dienstplan!O38="","",Dienstplan!O38)</f>
         <v/>
       </c>
-      <c r="P17" s="50">
+      <c r="P17" s="17">
         <f>IF(Dienstplan!P38="","",Dienstplan!P38)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q38="","",Dienstplan!Q38)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R38="","",Dienstplan!R38)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S38="","",Dienstplan!S38)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T38="","",Dienstplan!T38)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U38="","",Dienstplan!U38)</f>
         <v/>
       </c>
-      <c r="V17" s="50">
+      <c r="V17" s="17">
         <f>IF(Dienstplan!V38="","",Dienstplan!V38)</f>
         <v/>
       </c>
-      <c r="W17" s="50">
+      <c r="W17" s="17">
         <f>IF(Dienstplan!W38="","",Dienstplan!W38)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X38="","",Dienstplan!X38)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y38="","",Dienstplan!Y38)</f>
         <v/>
       </c>
-      <c r="Z17" s="51">
+      <c r="Z17" s="21">
         <f>IF(Dienstplan!Z38="","",Dienstplan!Z38)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA38="","",Dienstplan!AA38)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB38="","",Dienstplan!AB38)</f>
         <v/>
       </c>
-      <c r="AC17" s="52">
+      <c r="AC17" s="17">
         <f>IF(Dienstplan!AC38="","",Dienstplan!AC38)</f>
         <v/>
       </c>
@@ -50881,35 +50878,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AC17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -52464,138 +52461,138 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="49">
         <f>IF(Dienstplan!B55="","",Dienstplan!B55)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C55="","",Dienstplan!C55)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D55="","",Dienstplan!D55)</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="50">
         <f>IF(Dienstplan!E55="","",Dienstplan!E55)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F55="","",Dienstplan!F55)</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="50">
         <f>IF(Dienstplan!G55="","",Dienstplan!G55)</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="49">
         <f>IF(Dienstplan!H55="","",Dienstplan!H55)</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="49">
         <f>IF(Dienstplan!I55="","",Dienstplan!I55)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J55="","",Dienstplan!J55)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K55="","",Dienstplan!K55)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L55="","",Dienstplan!L55)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M55="","",Dienstplan!M55)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N55="","",Dienstplan!N55)</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="49">
         <f>IF(Dienstplan!O55="","",Dienstplan!O55)</f>
         <v/>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="49">
         <f>IF(Dienstplan!P55="","",Dienstplan!P55)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q55="","",Dienstplan!Q55)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R55="","",Dienstplan!R55)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S55="","",Dienstplan!S55)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T55="","",Dienstplan!T55)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U55="","",Dienstplan!U55)</f>
         <v/>
       </c>
-      <c r="V15" s="17">
+      <c r="V15" s="49">
         <f>IF(Dienstplan!V55="","",Dienstplan!V55)</f>
         <v/>
       </c>
-      <c r="W15" s="17">
+      <c r="W15" s="49">
         <f>IF(Dienstplan!W55="","",Dienstplan!W55)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X55="","",Dienstplan!X55)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y55="","",Dienstplan!Y55)</f>
         <v/>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="50">
         <f>IF(Dienstplan!Z55="","",Dienstplan!Z55)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA55="","",Dienstplan!AA55)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB55="","",Dienstplan!AB55)</f>
         <v/>
       </c>
-      <c r="AC15" s="17">
+      <c r="AC15" s="49">
         <f>IF(Dienstplan!AC55="","",Dienstplan!AC55)</f>
         <v/>
       </c>
-      <c r="AD15" s="17">
+      <c r="AD15" s="49">
         <f>IF(Dienstplan!AD55="","",Dienstplan!AD55)</f>
         <v/>
       </c>
-      <c r="AE15" s="21">
+      <c r="AE15" s="50">
         <f>IF(Dienstplan!AE55="","",Dienstplan!AE55)</f>
         <v/>
       </c>
-      <c r="AF15" s="35">
+      <c r="AF15" s="75">
         <f>IF(Dienstplan!AF55="","",Dienstplan!AF55)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -52720,138 +52717,138 @@
         <f>IF(Dienstplan!AE56="","",Dienstplan!AE56)</f>
         <v/>
       </c>
-      <c r="AF16" s="34">
+      <c r="AF16" s="18">
         <f>IF(Dienstplan!AF56="","",Dienstplan!AF56)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="17">
         <f>IF(Dienstplan!B57="","",Dienstplan!B57)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C57="","",Dienstplan!C57)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D57="","",Dienstplan!D57)</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="21">
         <f>IF(Dienstplan!E57="","",Dienstplan!E57)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F57="","",Dienstplan!F57)</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="21">
         <f>IF(Dienstplan!G57="","",Dienstplan!G57)</f>
         <v/>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="17">
         <f>IF(Dienstplan!H57="","",Dienstplan!H57)</f>
         <v/>
       </c>
-      <c r="I17" s="50">
+      <c r="I17" s="17">
         <f>IF(Dienstplan!I57="","",Dienstplan!I57)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J57="","",Dienstplan!J57)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K57="","",Dienstplan!K57)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L57="","",Dienstplan!L57)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M57="","",Dienstplan!M57)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N57="","",Dienstplan!N57)</f>
         <v/>
       </c>
-      <c r="O17" s="50">
+      <c r="O17" s="17">
         <f>IF(Dienstplan!O57="","",Dienstplan!O57)</f>
         <v/>
       </c>
-      <c r="P17" s="50">
+      <c r="P17" s="17">
         <f>IF(Dienstplan!P57="","",Dienstplan!P57)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q57="","",Dienstplan!Q57)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R57="","",Dienstplan!R57)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S57="","",Dienstplan!S57)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T57="","",Dienstplan!T57)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U57="","",Dienstplan!U57)</f>
         <v/>
       </c>
-      <c r="V17" s="50">
+      <c r="V17" s="17">
         <f>IF(Dienstplan!V57="","",Dienstplan!V57)</f>
         <v/>
       </c>
-      <c r="W17" s="50">
+      <c r="W17" s="17">
         <f>IF(Dienstplan!W57="","",Dienstplan!W57)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X57="","",Dienstplan!X57)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y57="","",Dienstplan!Y57)</f>
         <v/>
       </c>
-      <c r="Z17" s="51">
+      <c r="Z17" s="21">
         <f>IF(Dienstplan!Z57="","",Dienstplan!Z57)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA57="","",Dienstplan!AA57)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB57="","",Dienstplan!AB57)</f>
         <v/>
       </c>
-      <c r="AC17" s="50">
+      <c r="AC17" s="17">
         <f>IF(Dienstplan!AC57="","",Dienstplan!AC57)</f>
         <v/>
       </c>
-      <c r="AD17" s="50">
+      <c r="AD17" s="17">
         <f>IF(Dienstplan!AD57="","",Dienstplan!AD57)</f>
         <v/>
       </c>
-      <c r="AE17" s="51">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE57="","",Dienstplan!AE57)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="21">
         <f>IF(Dienstplan!AF57="","",Dienstplan!AF57)</f>
         <v/>
       </c>
@@ -53177,35 +53174,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AF17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -54719,134 +54716,134 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="50">
         <f>IF(Dienstplan!B75="","",Dienstplan!B75)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C75="","",Dienstplan!C75)</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="49">
         <f>IF(Dienstplan!D75="","",Dienstplan!D75)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="49">
         <f>IF(Dienstplan!E75="","",Dienstplan!E75)</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="49">
         <f>IF(Dienstplan!F75="","",Dienstplan!F75)</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="49">
         <f>IF(Dienstplan!G75="","",Dienstplan!G75)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H75="","",Dienstplan!H75)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I75="","",Dienstplan!I75)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J75="","",Dienstplan!J75)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K75="","",Dienstplan!K75)</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="49">
         <f>IF(Dienstplan!L75="","",Dienstplan!L75)</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="49">
         <f>IF(Dienstplan!M75="","",Dienstplan!M75)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N75="","",Dienstplan!N75)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="50">
         <f>IF(Dienstplan!O75="","",Dienstplan!O75)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P75="","",Dienstplan!P75)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q75="","",Dienstplan!Q75)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R75="","",Dienstplan!R75)</f>
         <v/>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="49">
         <f>IF(Dienstplan!S75="","",Dienstplan!S75)</f>
         <v/>
       </c>
-      <c r="T15" s="17">
+      <c r="T15" s="49">
         <f>IF(Dienstplan!T75="","",Dienstplan!T75)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U75="","",Dienstplan!U75)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V75="","",Dienstplan!V75)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W75="","",Dienstplan!W75)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X75="","",Dienstplan!X75)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y75="","",Dienstplan!Y75)</f>
         <v/>
       </c>
-      <c r="Z15" s="17">
+      <c r="Z15" s="49">
         <f>IF(Dienstplan!Z75="","",Dienstplan!Z75)</f>
         <v/>
       </c>
-      <c r="AA15" s="17">
+      <c r="AA15" s="49">
         <f>IF(Dienstplan!AA75="","",Dienstplan!AA75)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB75="","",Dienstplan!AB75)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC75="","",Dienstplan!AC75)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD75="","",Dienstplan!AD75)</f>
         <v/>
       </c>
-      <c r="AE15" s="35">
+      <c r="AE15" s="75">
         <f>IF(Dienstplan!AE75="","",Dienstplan!AE75)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -54967,134 +54964,134 @@
         <f>IF(Dienstplan!AD76="","",Dienstplan!AD76)</f>
         <v/>
       </c>
-      <c r="AE16" s="34">
+      <c r="AE16" s="18">
         <f>IF(Dienstplan!AE76="","",Dienstplan!AE76)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="21">
         <f>IF(Dienstplan!B77="","",Dienstplan!B77)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C77="","",Dienstplan!C77)</f>
         <v/>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="17">
         <f>IF(Dienstplan!D77="","",Dienstplan!D77)</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="17">
         <f>IF(Dienstplan!E77="","",Dienstplan!E77)</f>
         <v/>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="17">
         <f>IF(Dienstplan!F77="","",Dienstplan!F77)</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="17">
         <f>IF(Dienstplan!G77="","",Dienstplan!G77)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H77="","",Dienstplan!H77)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I77="","",Dienstplan!I77)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J77="","",Dienstplan!J77)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K77="","",Dienstplan!K77)</f>
         <v/>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="17">
         <f>IF(Dienstplan!L77="","",Dienstplan!L77)</f>
         <v/>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="17">
         <f>IF(Dienstplan!M77="","",Dienstplan!M77)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N77="","",Dienstplan!N77)</f>
         <v/>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="21">
         <f>IF(Dienstplan!O77="","",Dienstplan!O77)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P77="","",Dienstplan!P77)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q77="","",Dienstplan!Q77)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R77="","",Dienstplan!R77)</f>
         <v/>
       </c>
-      <c r="S17" s="50">
+      <c r="S17" s="17">
         <f>IF(Dienstplan!S77="","",Dienstplan!S77)</f>
         <v/>
       </c>
-      <c r="T17" s="50">
+      <c r="T17" s="17">
         <f>IF(Dienstplan!T77="","",Dienstplan!T77)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U77="","",Dienstplan!U77)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V77="","",Dienstplan!V77)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W77="","",Dienstplan!W77)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X77="","",Dienstplan!X77)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y77="","",Dienstplan!Y77)</f>
         <v/>
       </c>
-      <c r="Z17" s="50">
+      <c r="Z17" s="17">
         <f>IF(Dienstplan!Z77="","",Dienstplan!Z77)</f>
         <v/>
       </c>
-      <c r="AA17" s="50">
+      <c r="AA17" s="17">
         <f>IF(Dienstplan!AA77="","",Dienstplan!AA77)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB77="","",Dienstplan!AB77)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC77="","",Dienstplan!AC77)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD77="","",Dienstplan!AD77)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE77="","",Dienstplan!AE77)</f>
         <v/>
       </c>
@@ -55421,35 +55418,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AE17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -57010,138 +57007,138 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="49">
         <f>IF(Dienstplan!B95="","",Dienstplan!B95)</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="49">
         <f>IF(Dienstplan!C95="","",Dienstplan!C95)</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="49">
         <f>IF(Dienstplan!D95="","",Dienstplan!D95)</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="50">
         <f>IF(Dienstplan!E95="","",Dienstplan!E95)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F95="","",Dienstplan!F95)</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="50">
         <f>IF(Dienstplan!G95="","",Dienstplan!G95)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H95="","",Dienstplan!H95)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I95="","",Dienstplan!I95)</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="49">
         <f>IF(Dienstplan!J95="","",Dienstplan!J95)</f>
         <v/>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="49">
         <f>IF(Dienstplan!K95="","",Dienstplan!K95)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L95="","",Dienstplan!L95)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M95="","",Dienstplan!M95)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N95="","",Dienstplan!N95)</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="49">
         <f>IF(Dienstplan!O95="","",Dienstplan!O95)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P95="","",Dienstplan!P95)</f>
         <v/>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="49">
         <f>IF(Dienstplan!Q95="","",Dienstplan!Q95)</f>
         <v/>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="49">
         <f>IF(Dienstplan!R95="","",Dienstplan!R95)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S95="","",Dienstplan!S95)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T95="","",Dienstplan!T95)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U95="","",Dienstplan!U95)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V95="","",Dienstplan!V95)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W95="","",Dienstplan!W95)</f>
         <v/>
       </c>
-      <c r="X15" s="17">
+      <c r="X15" s="49">
         <f>IF(Dienstplan!X95="","",Dienstplan!X95)</f>
         <v/>
       </c>
-      <c r="Y15" s="17">
+      <c r="Y15" s="49">
         <f>IF(Dienstplan!Y95="","",Dienstplan!Y95)</f>
         <v/>
       </c>
-      <c r="Z15" s="17">
+      <c r="Z15" s="49">
         <f>IF(Dienstplan!Z95="","",Dienstplan!Z95)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA95="","",Dienstplan!AA95)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB95="","",Dienstplan!AB95)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC95="","",Dienstplan!AC95)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD95="","",Dienstplan!AD95)</f>
         <v/>
       </c>
-      <c r="AE15" s="17">
+      <c r="AE15" s="49">
         <f>IF(Dienstplan!AE95="","",Dienstplan!AE95)</f>
         <v/>
       </c>
-      <c r="AF15" s="19">
+      <c r="AF15" s="51">
         <f>IF(Dienstplan!AF95="","",Dienstplan!AF95)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -57266,138 +57263,138 @@
         <f>IF(Dienstplan!AE96="","",Dienstplan!AE96)</f>
         <v/>
       </c>
-      <c r="AF16" s="19">
+      <c r="AF16" s="17">
         <f>IF(Dienstplan!AF96="","",Dienstplan!AF96)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="17">
         <f>IF(Dienstplan!B97="","",Dienstplan!B97)</f>
         <v/>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="17">
         <f>IF(Dienstplan!C97="","",Dienstplan!C97)</f>
         <v/>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="17">
         <f>IF(Dienstplan!D97="","",Dienstplan!D97)</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="21">
         <f>IF(Dienstplan!E97="","",Dienstplan!E97)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F97="","",Dienstplan!F97)</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="21">
         <f>IF(Dienstplan!G97="","",Dienstplan!G97)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H97="","",Dienstplan!H97)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I97="","",Dienstplan!I97)</f>
         <v/>
       </c>
-      <c r="J17" s="50">
+      <c r="J17" s="17">
         <f>IF(Dienstplan!J97="","",Dienstplan!J97)</f>
         <v/>
       </c>
-      <c r="K17" s="50">
+      <c r="K17" s="17">
         <f>IF(Dienstplan!K97="","",Dienstplan!K97)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L97="","",Dienstplan!L97)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M97="","",Dienstplan!M97)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N97="","",Dienstplan!N97)</f>
         <v/>
       </c>
-      <c r="O17" s="50">
+      <c r="O17" s="17">
         <f>IF(Dienstplan!O97="","",Dienstplan!O97)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P97="","",Dienstplan!P97)</f>
         <v/>
       </c>
-      <c r="Q17" s="50">
+      <c r="Q17" s="17">
         <f>IF(Dienstplan!Q97="","",Dienstplan!Q97)</f>
         <v/>
       </c>
-      <c r="R17" s="50">
+      <c r="R17" s="17">
         <f>IF(Dienstplan!R97="","",Dienstplan!R97)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S97="","",Dienstplan!S97)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T97="","",Dienstplan!T97)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U97="","",Dienstplan!U97)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V97="","",Dienstplan!V97)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W97="","",Dienstplan!W97)</f>
         <v/>
       </c>
-      <c r="X17" s="50">
+      <c r="X17" s="17">
         <f>IF(Dienstplan!X97="","",Dienstplan!X97)</f>
         <v/>
       </c>
-      <c r="Y17" s="50">
+      <c r="Y17" s="17">
         <f>IF(Dienstplan!Y97="","",Dienstplan!Y97)</f>
         <v/>
       </c>
-      <c r="Z17" s="50">
+      <c r="Z17" s="17">
         <f>IF(Dienstplan!Z97="","",Dienstplan!Z97)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA97="","",Dienstplan!AA97)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB97="","",Dienstplan!AB97)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC97="","",Dienstplan!AC97)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD97="","",Dienstplan!AD97)</f>
         <v/>
       </c>
-      <c r="AE17" s="50">
+      <c r="AE17" s="17">
         <f>IF(Dienstplan!AE97="","",Dienstplan!AE97)</f>
         <v/>
       </c>
-      <c r="AF17" s="52">
+      <c r="AF17" s="17">
         <f>IF(Dienstplan!AF97="","",Dienstplan!AF97)</f>
         <v/>
       </c>
@@ -57724,35 +57721,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AF17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -59267,134 +59264,134 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="50">
         <f>IF(Dienstplan!B115="","",Dienstplan!B115)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C115="","",Dienstplan!C115)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D115="","",Dienstplan!D115)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="49">
         <f>IF(Dienstplan!E115="","",Dienstplan!E115)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F115="","",Dienstplan!F115)</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="49">
         <f>IF(Dienstplan!G115="","",Dienstplan!G115)</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="49">
         <f>IF(Dienstplan!H115="","",Dienstplan!H115)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I115="","",Dienstplan!I115)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J115="","",Dienstplan!J115)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K115="","",Dienstplan!K115)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L115="","",Dienstplan!L115)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M115="","",Dienstplan!M115)</f>
         <v/>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="49">
         <f>IF(Dienstplan!N115="","",Dienstplan!N115)</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="49">
         <f>IF(Dienstplan!O115="","",Dienstplan!O115)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P115="","",Dienstplan!P115)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q115="","",Dienstplan!Q115)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R115="","",Dienstplan!R115)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S115="","",Dienstplan!S115)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T115="","",Dienstplan!T115)</f>
         <v/>
       </c>
-      <c r="U15" s="17">
+      <c r="U15" s="49">
         <f>IF(Dienstplan!U115="","",Dienstplan!U115)</f>
         <v/>
       </c>
-      <c r="V15" s="17">
+      <c r="V15" s="49">
         <f>IF(Dienstplan!V115="","",Dienstplan!V115)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W115="","",Dienstplan!W115)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X115="","",Dienstplan!X115)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y115="","",Dienstplan!Y115)</f>
         <v/>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="50">
         <f>IF(Dienstplan!Z115="","",Dienstplan!Z115)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA115="","",Dienstplan!AA115)</f>
         <v/>
       </c>
-      <c r="AB15" s="17">
+      <c r="AB15" s="49">
         <f>IF(Dienstplan!AB115="","",Dienstplan!AB115)</f>
         <v/>
       </c>
-      <c r="AC15" s="17">
+      <c r="AC15" s="49">
         <f>IF(Dienstplan!AC115="","",Dienstplan!AC115)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD115="","",Dienstplan!AD115)</f>
         <v/>
       </c>
-      <c r="AE15" s="35">
+      <c r="AE15" s="75">
         <f>IF(Dienstplan!AE115="","",Dienstplan!AE115)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -59515,134 +59512,134 @@
         <f>IF(Dienstplan!AD116="","",Dienstplan!AD116)</f>
         <v/>
       </c>
-      <c r="AE16" s="34">
+      <c r="AE16" s="18">
         <f>IF(Dienstplan!AE116="","",Dienstplan!AE116)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="21">
         <f>IF(Dienstplan!B117="","",Dienstplan!B117)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C117="","",Dienstplan!C117)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D117="","",Dienstplan!D117)</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="17">
         <f>IF(Dienstplan!E117="","",Dienstplan!E117)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F117="","",Dienstplan!F117)</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="17">
         <f>IF(Dienstplan!G117="","",Dienstplan!G117)</f>
         <v/>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="17">
         <f>IF(Dienstplan!H117="","",Dienstplan!H117)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I117="","",Dienstplan!I117)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J117="","",Dienstplan!J117)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K117="","",Dienstplan!K117)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L117="","",Dienstplan!L117)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M117="","",Dienstplan!M117)</f>
         <v/>
       </c>
-      <c r="N17" s="50">
+      <c r="N17" s="17">
         <f>IF(Dienstplan!N117="","",Dienstplan!N117)</f>
         <v/>
       </c>
-      <c r="O17" s="50">
+      <c r="O17" s="17">
         <f>IF(Dienstplan!O117="","",Dienstplan!O117)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P117="","",Dienstplan!P117)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q117="","",Dienstplan!Q117)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R117="","",Dienstplan!R117)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S117="","",Dienstplan!S117)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T117="","",Dienstplan!T117)</f>
         <v/>
       </c>
-      <c r="U17" s="50">
+      <c r="U17" s="17">
         <f>IF(Dienstplan!U117="","",Dienstplan!U117)</f>
         <v/>
       </c>
-      <c r="V17" s="50">
+      <c r="V17" s="17">
         <f>IF(Dienstplan!V117="","",Dienstplan!V117)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W117="","",Dienstplan!W117)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X117="","",Dienstplan!X117)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y117="","",Dienstplan!Y117)</f>
         <v/>
       </c>
-      <c r="Z17" s="51">
+      <c r="Z17" s="21">
         <f>IF(Dienstplan!Z117="","",Dienstplan!Z117)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA117="","",Dienstplan!AA117)</f>
         <v/>
       </c>
-      <c r="AB17" s="50">
+      <c r="AB17" s="17">
         <f>IF(Dienstplan!AB117="","",Dienstplan!AB117)</f>
         <v/>
       </c>
-      <c r="AC17" s="50">
+      <c r="AC17" s="17">
         <f>IF(Dienstplan!AC117="","",Dienstplan!AC117)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD117="","",Dienstplan!AD117)</f>
         <v/>
       </c>
-      <c r="AE17" s="75">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE117="","",Dienstplan!AE117)</f>
         <v/>
       </c>
@@ -59969,35 +59966,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AE17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -61558,138 +61555,138 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="50">
         <f>IF(Dienstplan!B135="","",Dienstplan!B135)</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="50">
         <f>IF(Dienstplan!C135="","",Dienstplan!C135)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D135="","",Dienstplan!D135)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="49">
         <f>IF(Dienstplan!E135="","",Dienstplan!E135)</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="49">
         <f>IF(Dienstplan!F135="","",Dienstplan!F135)</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="50">
         <f>IF(Dienstplan!G135="","",Dienstplan!G135)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H135="","",Dienstplan!H135)</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="50">
         <f>IF(Dienstplan!I135="","",Dienstplan!I135)</f>
         <v/>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="50">
         <f>IF(Dienstplan!J135="","",Dienstplan!J135)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K135="","",Dienstplan!K135)</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="49">
         <f>IF(Dienstplan!L135="","",Dienstplan!L135)</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="49">
         <f>IF(Dienstplan!M135="","",Dienstplan!M135)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N135="","",Dienstplan!N135)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="50">
         <f>IF(Dienstplan!O135="","",Dienstplan!O135)</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="50">
         <f>IF(Dienstplan!P135="","",Dienstplan!P135)</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="50">
         <f>IF(Dienstplan!Q135="","",Dienstplan!Q135)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R135="","",Dienstplan!R135)</f>
         <v/>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="49">
         <f>IF(Dienstplan!S135="","",Dienstplan!S135)</f>
         <v/>
       </c>
-      <c r="T15" s="17">
+      <c r="T15" s="49">
         <f>IF(Dienstplan!T135="","",Dienstplan!T135)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U135="","",Dienstplan!U135)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V135="","",Dienstplan!V135)</f>
         <v/>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="50">
         <f>IF(Dienstplan!W135="","",Dienstplan!W135)</f>
         <v/>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="50">
         <f>IF(Dienstplan!X135="","",Dienstplan!X135)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y135="","",Dienstplan!Y135)</f>
         <v/>
       </c>
-      <c r="Z15" s="17">
+      <c r="Z15" s="49">
         <f>IF(Dienstplan!Z135="","",Dienstplan!Z135)</f>
         <v/>
       </c>
-      <c r="AA15" s="17">
+      <c r="AA15" s="49">
         <f>IF(Dienstplan!AA135="","",Dienstplan!AA135)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB135="","",Dienstplan!AB135)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC135="","",Dienstplan!AC135)</f>
         <v/>
       </c>
-      <c r="AD15" s="21">
+      <c r="AD15" s="50">
         <f>IF(Dienstplan!AD135="","",Dienstplan!AD135)</f>
         <v/>
       </c>
-      <c r="AE15" s="21">
+      <c r="AE15" s="50">
         <f>IF(Dienstplan!AE135="","",Dienstplan!AE135)</f>
         <v/>
       </c>
-      <c r="AF15" s="35">
+      <c r="AF15" s="75">
         <f>IF(Dienstplan!AF135="","",Dienstplan!AF135)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -61814,138 +61811,138 @@
         <f>IF(Dienstplan!AE136="","",Dienstplan!AE136)</f>
         <v/>
       </c>
-      <c r="AF16" s="34">
+      <c r="AF16" s="18">
         <f>IF(Dienstplan!AF136="","",Dienstplan!AF136)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="21">
         <f>IF(Dienstplan!B137="","",Dienstplan!B137)</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="21">
         <f>IF(Dienstplan!C137="","",Dienstplan!C137)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D137="","",Dienstplan!D137)</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="17">
         <f>IF(Dienstplan!E137="","",Dienstplan!E137)</f>
         <v/>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="17">
         <f>IF(Dienstplan!F137="","",Dienstplan!F137)</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="21">
         <f>IF(Dienstplan!G137="","",Dienstplan!G137)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H137="","",Dienstplan!H137)</f>
         <v/>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="21">
         <f>IF(Dienstplan!I137="","",Dienstplan!I137)</f>
         <v/>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="21">
         <f>IF(Dienstplan!J137="","",Dienstplan!J137)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K137="","",Dienstplan!K137)</f>
         <v/>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="17">
         <f>IF(Dienstplan!L137="","",Dienstplan!L137)</f>
         <v/>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="17">
         <f>IF(Dienstplan!M137="","",Dienstplan!M137)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N137="","",Dienstplan!N137)</f>
         <v/>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="21">
         <f>IF(Dienstplan!O137="","",Dienstplan!O137)</f>
         <v/>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="21">
         <f>IF(Dienstplan!P137="","",Dienstplan!P137)</f>
         <v/>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="21">
         <f>IF(Dienstplan!Q137="","",Dienstplan!Q137)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R137="","",Dienstplan!R137)</f>
         <v/>
       </c>
-      <c r="S17" s="50">
+      <c r="S17" s="17">
         <f>IF(Dienstplan!S137="","",Dienstplan!S137)</f>
         <v/>
       </c>
-      <c r="T17" s="50">
+      <c r="T17" s="17">
         <f>IF(Dienstplan!T137="","",Dienstplan!T137)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U137="","",Dienstplan!U137)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V137="","",Dienstplan!V137)</f>
         <v/>
       </c>
-      <c r="W17" s="51">
+      <c r="W17" s="21">
         <f>IF(Dienstplan!W137="","",Dienstplan!W137)</f>
         <v/>
       </c>
-      <c r="X17" s="51">
+      <c r="X17" s="21">
         <f>IF(Dienstplan!X137="","",Dienstplan!X137)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y137="","",Dienstplan!Y137)</f>
         <v/>
       </c>
-      <c r="Z17" s="50">
+      <c r="Z17" s="17">
         <f>IF(Dienstplan!Z137="","",Dienstplan!Z137)</f>
         <v/>
       </c>
-      <c r="AA17" s="50">
+      <c r="AA17" s="17">
         <f>IF(Dienstplan!AA137="","",Dienstplan!AA137)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB137="","",Dienstplan!AB137)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC137="","",Dienstplan!AC137)</f>
         <v/>
       </c>
-      <c r="AD17" s="51">
+      <c r="AD17" s="21">
         <f>IF(Dienstplan!AD137="","",Dienstplan!AD137)</f>
         <v/>
       </c>
-      <c r="AE17" s="51">
+      <c r="AE17" s="21">
         <f>IF(Dienstplan!AE137="","",Dienstplan!AE137)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="21">
         <f>IF(Dienstplan!AF137="","",Dienstplan!AF137)</f>
         <v/>
       </c>
@@ -62272,35 +62269,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AF17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
@@ -63862,138 +63859,138 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>Kunz</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="49">
         <f>IF(Dienstplan!B155="","",Dienstplan!B155)</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="49">
         <f>IF(Dienstplan!C155="","",Dienstplan!C155)</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="50">
         <f>IF(Dienstplan!D155="","",Dienstplan!D155)</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="50">
         <f>IF(Dienstplan!E155="","",Dienstplan!E155)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="50">
         <f>IF(Dienstplan!F155="","",Dienstplan!F155)</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="50">
         <f>IF(Dienstplan!G155="","",Dienstplan!G155)</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="50">
         <f>IF(Dienstplan!H155="","",Dienstplan!H155)</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="49">
         <f>IF(Dienstplan!I155="","",Dienstplan!I155)</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="49">
         <f>IF(Dienstplan!J155="","",Dienstplan!J155)</f>
         <v/>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="50">
         <f>IF(Dienstplan!K155="","",Dienstplan!K155)</f>
         <v/>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="50">
         <f>IF(Dienstplan!L155="","",Dienstplan!L155)</f>
         <v/>
       </c>
-      <c r="M15" s="21">
+      <c r="M15" s="50">
         <f>IF(Dienstplan!M155="","",Dienstplan!M155)</f>
         <v/>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="50">
         <f>IF(Dienstplan!N155="","",Dienstplan!N155)</f>
         <v/>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="50">
         <f>IF(Dienstplan!O155="","",Dienstplan!O155)</f>
         <v/>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="49">
         <f>IF(Dienstplan!P155="","",Dienstplan!P155)</f>
         <v/>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="49">
         <f>IF(Dienstplan!Q155="","",Dienstplan!Q155)</f>
         <v/>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="50">
         <f>IF(Dienstplan!R155="","",Dienstplan!R155)</f>
         <v/>
       </c>
-      <c r="S15" s="21">
+      <c r="S15" s="50">
         <f>IF(Dienstplan!S155="","",Dienstplan!S155)</f>
         <v/>
       </c>
-      <c r="T15" s="21">
+      <c r="T15" s="50">
         <f>IF(Dienstplan!T155="","",Dienstplan!T155)</f>
         <v/>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="50">
         <f>IF(Dienstplan!U155="","",Dienstplan!U155)</f>
         <v/>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="50">
         <f>IF(Dienstplan!V155="","",Dienstplan!V155)</f>
         <v/>
       </c>
-      <c r="W15" s="17">
+      <c r="W15" s="49">
         <f>IF(Dienstplan!W155="","",Dienstplan!W155)</f>
         <v/>
       </c>
-      <c r="X15" s="17">
+      <c r="X15" s="49">
         <f>IF(Dienstplan!X155="","",Dienstplan!X155)</f>
         <v/>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="50">
         <f>IF(Dienstplan!Y155="","",Dienstplan!Y155)</f>
         <v/>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="50">
         <f>IF(Dienstplan!Z155="","",Dienstplan!Z155)</f>
         <v/>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="50">
         <f>IF(Dienstplan!AA155="","",Dienstplan!AA155)</f>
         <v/>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="50">
         <f>IF(Dienstplan!AB155="","",Dienstplan!AB155)</f>
         <v/>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="50">
         <f>IF(Dienstplan!AC155="","",Dienstplan!AC155)</f>
         <v/>
       </c>
-      <c r="AD15" s="17">
+      <c r="AD15" s="49">
         <f>IF(Dienstplan!AD155="","",Dienstplan!AD155)</f>
         <v/>
       </c>
-      <c r="AE15" s="17">
+      <c r="AE15" s="49">
         <f>IF(Dienstplan!AE155="","",Dienstplan!AE155)</f>
         <v/>
       </c>
-      <c r="AF15" s="35">
+      <c r="AF15" s="75">
         <f>IF(Dienstplan!AF155="","",Dienstplan!AF155)</f>
         <v/>
       </c>
     </row>
     <row r="16" hidden="1" ht="16" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Schmidt</t>
         </is>
@@ -64118,138 +64115,138 @@
         <f>IF(Dienstplan!AE156="","",Dienstplan!AE156)</f>
         <v/>
       </c>
-      <c r="AF16" s="34">
+      <c r="AF16" s="18">
         <f>IF(Dienstplan!AF156="","",Dienstplan!AF156)</f>
         <v/>
       </c>
     </row>
     <row r="17" hidden="1" ht="16" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Radimersky</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="17">
         <f>IF(Dienstplan!B157="","",Dienstplan!B157)</f>
         <v/>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="17">
         <f>IF(Dienstplan!C157="","",Dienstplan!C157)</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="21">
         <f>IF(Dienstplan!D157="","",Dienstplan!D157)</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="21">
         <f>IF(Dienstplan!E157="","",Dienstplan!E157)</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="21">
         <f>IF(Dienstplan!F157="","",Dienstplan!F157)</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="21">
         <f>IF(Dienstplan!G157="","",Dienstplan!G157)</f>
         <v/>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="21">
         <f>IF(Dienstplan!H157="","",Dienstplan!H157)</f>
         <v/>
       </c>
-      <c r="I17" s="50">
+      <c r="I17" s="17">
         <f>IF(Dienstplan!I157="","",Dienstplan!I157)</f>
         <v/>
       </c>
-      <c r="J17" s="50">
+      <c r="J17" s="17">
         <f>IF(Dienstplan!J157="","",Dienstplan!J157)</f>
         <v/>
       </c>
-      <c r="K17" s="51">
+      <c r="K17" s="21">
         <f>IF(Dienstplan!K157="","",Dienstplan!K157)</f>
         <v/>
       </c>
-      <c r="L17" s="51">
+      <c r="L17" s="21">
         <f>IF(Dienstplan!L157="","",Dienstplan!L157)</f>
         <v/>
       </c>
-      <c r="M17" s="51">
+      <c r="M17" s="21">
         <f>IF(Dienstplan!M157="","",Dienstplan!M157)</f>
         <v/>
       </c>
-      <c r="N17" s="51">
+      <c r="N17" s="21">
         <f>IF(Dienstplan!N157="","",Dienstplan!N157)</f>
         <v/>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="21">
         <f>IF(Dienstplan!O157="","",Dienstplan!O157)</f>
         <v/>
       </c>
-      <c r="P17" s="50">
+      <c r="P17" s="17">
         <f>IF(Dienstplan!P157="","",Dienstplan!P157)</f>
         <v/>
       </c>
-      <c r="Q17" s="50">
+      <c r="Q17" s="17">
         <f>IF(Dienstplan!Q157="","",Dienstplan!Q157)</f>
         <v/>
       </c>
-      <c r="R17" s="51">
+      <c r="R17" s="21">
         <f>IF(Dienstplan!R157="","",Dienstplan!R157)</f>
         <v/>
       </c>
-      <c r="S17" s="51">
+      <c r="S17" s="21">
         <f>IF(Dienstplan!S157="","",Dienstplan!S157)</f>
         <v/>
       </c>
-      <c r="T17" s="51">
+      <c r="T17" s="21">
         <f>IF(Dienstplan!T157="","",Dienstplan!T157)</f>
         <v/>
       </c>
-      <c r="U17" s="51">
+      <c r="U17" s="21">
         <f>IF(Dienstplan!U157="","",Dienstplan!U157)</f>
         <v/>
       </c>
-      <c r="V17" s="51">
+      <c r="V17" s="21">
         <f>IF(Dienstplan!V157="","",Dienstplan!V157)</f>
         <v/>
       </c>
-      <c r="W17" s="50">
+      <c r="W17" s="17">
         <f>IF(Dienstplan!W157="","",Dienstplan!W157)</f>
         <v/>
       </c>
-      <c r="X17" s="50">
+      <c r="X17" s="17">
         <f>IF(Dienstplan!X157="","",Dienstplan!X157)</f>
         <v/>
       </c>
-      <c r="Y17" s="51">
+      <c r="Y17" s="21">
         <f>IF(Dienstplan!Y157="","",Dienstplan!Y157)</f>
         <v/>
       </c>
-      <c r="Z17" s="51">
+      <c r="Z17" s="21">
         <f>IF(Dienstplan!Z157="","",Dienstplan!Z157)</f>
         <v/>
       </c>
-      <c r="AA17" s="51">
+      <c r="AA17" s="21">
         <f>IF(Dienstplan!AA157="","",Dienstplan!AA157)</f>
         <v/>
       </c>
-      <c r="AB17" s="51">
+      <c r="AB17" s="21">
         <f>IF(Dienstplan!AB157="","",Dienstplan!AB157)</f>
         <v/>
       </c>
-      <c r="AC17" s="51">
+      <c r="AC17" s="21">
         <f>IF(Dienstplan!AC157="","",Dienstplan!AC157)</f>
         <v/>
       </c>
-      <c r="AD17" s="50">
+      <c r="AD17" s="17">
         <f>IF(Dienstplan!AD157="","",Dienstplan!AD157)</f>
         <v/>
       </c>
-      <c r="AE17" s="50">
+      <c r="AE17" s="17">
         <f>IF(Dienstplan!AE157="","",Dienstplan!AE157)</f>
         <v/>
       </c>
-      <c r="AF17" s="75">
+      <c r="AF17" s="21">
         <f>IF(Dienstplan!AF157="","",Dienstplan!AF157)</f>
         <v/>
       </c>
@@ -64576,35 +64573,35 @@
     <mergeCell ref="H21:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:AF17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U"</formula>
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>B6="U"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"U    alt"</formula>
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>B6="U    alt"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
-      <formula>"EH"</formula>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>B6="EH"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
-      <formula>"KU"</formula>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+      <formula>B6="KU"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3" stopIfTrue="1">
-      <formula>"A"</formula>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="1">
+      <formula>B6="A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZUG"</formula>
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZUG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"T-ZG"</formula>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>B6="T-ZG"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"Fobi"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>B6="Fobi"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0" stopIfTrue="1">
-      <formula>"GT"</formula>
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
+      <formula>B6="GT"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4" stopIfTrue="1">
-      <formula>"NST"</formula>
+    <cfRule type="expression" priority="10" dxfId="4" stopIfTrue="1">
+      <formula>B6="NST"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.35" right="0.25" top="0.3" bottom="0.25" header="0.15" footer="0.15"/>
